--- a/output/ai-shinryou-db/text/2026/hosei-tsuuchi-i/2026_様式103・104（調剤）［96KB］_20260421.xlsx
+++ b/output/ai-shinryou-db/text/2026/hosei-tsuuchi-i/2026_様式103・104（調剤）［96KB］_20260421.xlsx
@@ -3,10 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="3012" documentId="8_{E3AB72A5-3263-48CF-892A-AB6E9C347A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B922C8D-3CD3-4B65-A8E2-6DDC59B052C4}"/>
-  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="9B6KwLN11+c++FFzxp9vCzdMgOSf4eXeAU1nTxe4H/aVpKAckPWdc2HeELb8a0tfCYV3jERO+TrVECqApgneRQ==" workbookSaltValue="Tgm4ULFKmvdyffoIdJ+QZQ==" workbookSpinCount="100000" lockStructure="1"/>
+  <xr:revisionPtr revIDLastSave="3342" documentId="8_{E3AB72A5-3263-48CF-892A-AB6E9C347A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{013F777E-7ECE-4394-8E06-A9D4C762372E}"/>
   <bookViews>
-    <workbookView xWindow="12375" yWindow="0" windowWidth="16425" windowHeight="15180" tabRatio="902" firstSheet="3" activeTab="4" xr2:uid="{660BDFD6-C435-4986-A101-19921E0E4C74}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="902" activeTab="4" xr2:uid="{660BDFD6-C435-4986-A101-19921E0E4C74}"/>
   </bookViews>
   <sheets>
     <sheet name="別添2" sheetId="22" r:id="rId1"/>
@@ -204,7 +203,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="361">
   <si>
     <t>別添２</t>
     <rPh sb="0" eb="2">
@@ -2973,6 +2972,10 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t xml:space="preserve">      (算定期間分）【（９）】</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -2983,7 +2986,7 @@
     <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="178" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="46">
+  <fonts count="47">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3289,6 +3292,14 @@
     <font>
       <sz val="10"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
@@ -3968,7 +3979,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="308">
+  <cellXfs count="309">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4604,6 +4615,9 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4849,11 +4863,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="38" fontId="12" fillId="3" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="40" fontId="12" fillId="3" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="38" fontId="12" fillId="3" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="40" fontId="12" fillId="3" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
@@ -4916,10 +4930,10 @@
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7608,37 +7622,37 @@
     </row>
     <row r="6" spans="1:16" ht="22.5" customHeight="1">
       <c r="A6" s="54"/>
-      <c r="B6" s="204" t="s">
+      <c r="B6" s="205" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="204"/>
-      <c r="D6" s="204"/>
-      <c r="E6" s="206"/>
-      <c r="F6" s="207"/>
-      <c r="G6" s="208"/>
+      <c r="C6" s="205"/>
+      <c r="D6" s="205"/>
+      <c r="E6" s="207"/>
+      <c r="F6" s="208"/>
+      <c r="G6" s="209"/>
       <c r="H6" s="50"/>
-      <c r="I6" s="203" t="s">
+      <c r="I6" s="204" t="s">
         <v>3</v>
       </c>
-      <c r="J6" s="203"/>
-      <c r="K6" s="203"/>
+      <c r="J6" s="204"/>
+      <c r="K6" s="204"/>
       <c r="L6" s="50"/>
       <c r="M6" s="55"/>
     </row>
     <row r="7" spans="1:16" ht="22.5" customHeight="1">
       <c r="A7" s="56"/>
-      <c r="B7" s="205" t="s">
+      <c r="B7" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="205"/>
-      <c r="D7" s="205"/>
-      <c r="E7" s="209"/>
-      <c r="F7" s="210"/>
-      <c r="G7" s="211"/>
+      <c r="C7" s="206"/>
+      <c r="D7" s="206"/>
+      <c r="E7" s="210"/>
+      <c r="F7" s="211"/>
+      <c r="G7" s="212"/>
       <c r="H7" s="50"/>
-      <c r="I7" s="203"/>
-      <c r="J7" s="203"/>
-      <c r="K7" s="203"/>
+      <c r="I7" s="204"/>
+      <c r="J7" s="204"/>
+      <c r="K7" s="204"/>
       <c r="L7" s="50"/>
       <c r="M7" s="55"/>
     </row>
@@ -7659,11 +7673,11 @@
     </row>
     <row r="9" spans="1:16" ht="22.5" customHeight="1">
       <c r="A9" s="57"/>
-      <c r="B9" s="212" t="s">
+      <c r="B9" s="213" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="212"/>
-      <c r="D9" s="212"/>
+      <c r="C9" s="213"/>
+      <c r="D9" s="213"/>
       <c r="E9" s="38"/>
       <c r="F9" s="38"/>
       <c r="G9" s="38"/>
@@ -7676,15 +7690,15 @@
     </row>
     <row r="10" spans="1:16" ht="22.5" customHeight="1">
       <c r="A10" s="57"/>
-      <c r="B10" s="215" t="s">
+      <c r="B10" s="216" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="215"/>
-      <c r="D10" s="215"/>
-      <c r="E10" s="216"/>
-      <c r="F10" s="216"/>
-      <c r="G10" s="216"/>
-      <c r="H10" s="216"/>
+      <c r="C10" s="216"/>
+      <c r="D10" s="216"/>
+      <c r="E10" s="217"/>
+      <c r="F10" s="217"/>
+      <c r="G10" s="217"/>
+      <c r="H10" s="217"/>
       <c r="I10" s="38"/>
       <c r="J10" s="38"/>
       <c r="K10" s="38"/>
@@ -7693,15 +7707,15 @@
     </row>
     <row r="11" spans="1:16" ht="22.5" customHeight="1">
       <c r="A11" s="57"/>
-      <c r="B11" s="215" t="s">
+      <c r="B11" s="216" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="215"/>
-      <c r="D11" s="215"/>
-      <c r="E11" s="216"/>
-      <c r="F11" s="216"/>
-      <c r="G11" s="216"/>
-      <c r="H11" s="216"/>
+      <c r="C11" s="216"/>
+      <c r="D11" s="216"/>
+      <c r="E11" s="217"/>
+      <c r="F11" s="217"/>
+      <c r="G11" s="217"/>
+      <c r="H11" s="217"/>
       <c r="I11" s="38"/>
       <c r="J11" s="38"/>
       <c r="K11" s="38"/>
@@ -7732,35 +7746,31 @@
     <row r="14" spans="1:16" ht="15" customHeight="1">
       <c r="A14" s="54"/>
       <c r="B14" s="71"/>
-      <c r="C14" s="217" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="217"/>
-      <c r="E14" s="217"/>
-      <c r="F14" s="217"/>
-      <c r="G14" s="217"/>
-      <c r="H14" s="217"/>
-      <c r="I14" s="217"/>
+      <c r="C14" s="218"/>
+      <c r="D14" s="218"/>
+      <c r="E14" s="218"/>
+      <c r="F14" s="218"/>
+      <c r="G14" s="218"/>
+      <c r="H14" s="218"/>
+      <c r="I14" s="218"/>
       <c r="L14" s="82"/>
       <c r="M14" s="60"/>
     </row>
     <row r="15" spans="1:16" ht="33.75" customHeight="1">
       <c r="A15" s="54"/>
       <c r="B15" s="71"/>
-      <c r="C15" s="228" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="228"/>
-      <c r="E15" s="228"/>
-      <c r="F15" s="228"/>
-      <c r="G15" s="228"/>
-      <c r="H15" s="228"/>
-      <c r="I15" s="228"/>
-      <c r="J15" s="221" t="s">
+      <c r="C15" s="229"/>
+      <c r="D15" s="229"/>
+      <c r="E15" s="229"/>
+      <c r="F15" s="229"/>
+      <c r="G15" s="229"/>
+      <c r="H15" s="229"/>
+      <c r="I15" s="229"/>
+      <c r="J15" s="222" t="s">
         <v>10</v>
       </c>
-      <c r="K15" s="221"/>
-      <c r="L15" s="222"/>
+      <c r="K15" s="222"/>
+      <c r="L15" s="223"/>
       <c r="M15" s="76"/>
       <c r="P15" s="37" t="s">
         <v>9</v>
@@ -7804,18 +7814,18 @@
     <row r="18" spans="1:16" ht="36.75" customHeight="1">
       <c r="A18" s="54"/>
       <c r="B18" s="83"/>
-      <c r="C18" s="213" t="s">
+      <c r="C18" s="214" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="213"/>
-      <c r="E18" s="213"/>
-      <c r="F18" s="213"/>
-      <c r="G18" s="213"/>
-      <c r="H18" s="213"/>
-      <c r="I18" s="213"/>
-      <c r="J18" s="213"/>
-      <c r="K18" s="213"/>
-      <c r="L18" s="214"/>
+      <c r="D18" s="214"/>
+      <c r="E18" s="214"/>
+      <c r="F18" s="214"/>
+      <c r="G18" s="214"/>
+      <c r="H18" s="214"/>
+      <c r="I18" s="214"/>
+      <c r="J18" s="214"/>
+      <c r="K18" s="214"/>
+      <c r="L18" s="215"/>
       <c r="M18" s="77"/>
       <c r="O18" s="88" t="b">
         <v>0</v>
@@ -7827,18 +7837,18 @@
     <row r="19" spans="1:16" ht="36.75" customHeight="1">
       <c r="A19" s="54"/>
       <c r="B19" s="83"/>
-      <c r="C19" s="213" t="s">
+      <c r="C19" s="214" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="213"/>
-      <c r="E19" s="213"/>
-      <c r="F19" s="213"/>
-      <c r="G19" s="213"/>
-      <c r="H19" s="213"/>
-      <c r="I19" s="213"/>
-      <c r="J19" s="213"/>
-      <c r="K19" s="213"/>
-      <c r="L19" s="214"/>
+      <c r="D19" s="214"/>
+      <c r="E19" s="214"/>
+      <c r="F19" s="214"/>
+      <c r="G19" s="214"/>
+      <c r="H19" s="214"/>
+      <c r="I19" s="214"/>
+      <c r="J19" s="214"/>
+      <c r="K19" s="214"/>
+      <c r="L19" s="215"/>
       <c r="M19" s="77"/>
       <c r="O19" s="88" t="b">
         <v>0</v>
@@ -7847,18 +7857,18 @@
     <row r="20" spans="1:16" ht="36.75" customHeight="1">
       <c r="A20" s="54"/>
       <c r="B20" s="83"/>
-      <c r="C20" s="213" t="s">
+      <c r="C20" s="214" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="213"/>
-      <c r="E20" s="213"/>
-      <c r="F20" s="213"/>
-      <c r="G20" s="213"/>
-      <c r="H20" s="213"/>
-      <c r="I20" s="213"/>
-      <c r="J20" s="213"/>
-      <c r="K20" s="213"/>
-      <c r="L20" s="214"/>
+      <c r="D20" s="214"/>
+      <c r="E20" s="214"/>
+      <c r="F20" s="214"/>
+      <c r="G20" s="214"/>
+      <c r="H20" s="214"/>
+      <c r="I20" s="214"/>
+      <c r="J20" s="214"/>
+      <c r="K20" s="214"/>
+      <c r="L20" s="215"/>
       <c r="M20" s="77"/>
       <c r="O20" s="88" t="b">
         <v>0</v>
@@ -7867,18 +7877,18 @@
     <row r="21" spans="1:16" ht="36.75" customHeight="1">
       <c r="A21" s="54"/>
       <c r="B21" s="83"/>
-      <c r="C21" s="213" t="s">
+      <c r="C21" s="214" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="213"/>
-      <c r="E21" s="213"/>
-      <c r="F21" s="213"/>
-      <c r="G21" s="213"/>
-      <c r="H21" s="213"/>
-      <c r="I21" s="213"/>
-      <c r="J21" s="213"/>
-      <c r="K21" s="213"/>
-      <c r="L21" s="214"/>
+      <c r="D21" s="214"/>
+      <c r="E21" s="214"/>
+      <c r="F21" s="214"/>
+      <c r="G21" s="214"/>
+      <c r="H21" s="214"/>
+      <c r="I21" s="214"/>
+      <c r="J21" s="214"/>
+      <c r="K21" s="214"/>
+      <c r="L21" s="215"/>
       <c r="M21" s="77"/>
       <c r="O21" s="88" t="b">
         <v>0</v>
@@ -7887,32 +7897,32 @@
     <row r="22" spans="1:16" ht="15" customHeight="1">
       <c r="A22" s="54"/>
       <c r="B22" s="71"/>
-      <c r="D22" s="223"/>
-      <c r="E22" s="223"/>
-      <c r="F22" s="223"/>
-      <c r="G22" s="223"/>
-      <c r="H22" s="223"/>
-      <c r="I22" s="223"/>
-      <c r="J22" s="223"/>
-      <c r="K22" s="223"/>
-      <c r="L22" s="224"/>
+      <c r="D22" s="224"/>
+      <c r="E22" s="224"/>
+      <c r="F22" s="224"/>
+      <c r="G22" s="224"/>
+      <c r="H22" s="224"/>
+      <c r="I22" s="224"/>
+      <c r="J22" s="224"/>
+      <c r="K22" s="224"/>
+      <c r="L22" s="225"/>
       <c r="M22" s="60"/>
     </row>
     <row r="23" spans="1:16" ht="22.5" customHeight="1">
       <c r="A23" s="54"/>
-      <c r="B23" s="225" t="s">
+      <c r="B23" s="226" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="226"/>
-      <c r="D23" s="226"/>
-      <c r="E23" s="226"/>
-      <c r="F23" s="226"/>
-      <c r="G23" s="226"/>
-      <c r="H23" s="226"/>
-      <c r="I23" s="226"/>
-      <c r="J23" s="226"/>
-      <c r="K23" s="226"/>
-      <c r="L23" s="227"/>
+      <c r="C23" s="227"/>
+      <c r="D23" s="227"/>
+      <c r="E23" s="227"/>
+      <c r="F23" s="227"/>
+      <c r="G23" s="227"/>
+      <c r="H23" s="227"/>
+      <c r="I23" s="227"/>
+      <c r="J23" s="227"/>
+      <c r="K23" s="227"/>
+      <c r="L23" s="228"/>
       <c r="M23" s="78"/>
     </row>
     <row r="24" spans="1:16" ht="15" customHeight="1">
@@ -7954,9 +7964,9 @@
         <v>20</v>
       </c>
       <c r="H27" s="130"/>
-      <c r="I27" s="220"/>
-      <c r="J27" s="220"/>
-      <c r="K27" s="220"/>
+      <c r="I27" s="221"/>
+      <c r="J27" s="221"/>
+      <c r="K27" s="221"/>
       <c r="L27" s="82"/>
       <c r="M27" s="60"/>
     </row>
@@ -7966,10 +7976,10 @@
       <c r="C28" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="H28" s="220"/>
-      <c r="I28" s="220"/>
-      <c r="J28" s="220"/>
-      <c r="K28" s="220"/>
+      <c r="H28" s="221"/>
+      <c r="I28" s="221"/>
+      <c r="J28" s="221"/>
+      <c r="K28" s="221"/>
       <c r="L28" s="82"/>
       <c r="M28" s="60"/>
     </row>
@@ -7985,9 +7995,9 @@
       <c r="G30" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I30" s="218"/>
-      <c r="J30" s="218"/>
-      <c r="K30" s="218"/>
+      <c r="I30" s="219"/>
+      <c r="J30" s="219"/>
+      <c r="K30" s="219"/>
       <c r="L30" s="82"/>
       <c r="M30" s="60"/>
     </row>
@@ -7999,10 +8009,10 @@
     </row>
     <row r="32" spans="1:16" ht="22.5" customHeight="1">
       <c r="A32" s="54"/>
-      <c r="B32" s="219"/>
-      <c r="C32" s="218"/>
-      <c r="D32" s="218"/>
-      <c r="E32" s="218"/>
+      <c r="B32" s="220"/>
+      <c r="C32" s="219"/>
+      <c r="D32" s="219"/>
+      <c r="E32" s="219"/>
       <c r="F32" s="37" t="s">
         <v>23</v>
       </c>
@@ -8056,7 +8066,7 @@
       <c r="M36" s="67"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="dBClJkYQQhxj4mVrX2ahU19mGoF/FS9IRvNjSxdQpLL32CPLDsldUGirbw66XSS1HAOI3L35r861XahOkK1X9w==" saltValue="UNhImtmM6PvE7bCtDxAmpg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="yeVXm2DbRINmw30FbDwnXRQlQSTmd0NrlsQsTrmM4+tcQ54XCwouKvu+K+3EkNCWcQ+QyC6AsGrWv7ODkG57nQ==" saltValue="DviMdF7QGtzNyjhQldseGg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="23">
     <mergeCell ref="I30:K30"/>
     <mergeCell ref="B32:E32"/>
@@ -8252,39 +8262,39 @@
     </row>
     <row r="2" spans="1:54" ht="30" customHeight="1"/>
     <row r="3" spans="1:54" ht="50.1" customHeight="1">
-      <c r="A3" s="230" t="s">
+      <c r="A3" s="231" t="s">
         <v>169</v>
       </c>
-      <c r="B3" s="230"/>
-      <c r="C3" s="230"/>
-      <c r="D3" s="230"/>
-      <c r="E3" s="230"/>
-      <c r="F3" s="230"/>
-      <c r="G3" s="230"/>
-      <c r="H3" s="230"/>
-      <c r="I3" s="230"/>
-      <c r="J3" s="230"/>
-      <c r="K3" s="230"/>
-      <c r="L3" s="230"/>
-      <c r="M3" s="230"/>
-      <c r="N3" s="230"/>
-      <c r="O3" s="230"/>
-      <c r="P3" s="230"/>
-      <c r="Q3" s="230"/>
-      <c r="R3" s="230"/>
-      <c r="S3" s="230"/>
-      <c r="T3" s="230"/>
-      <c r="U3" s="230"/>
-      <c r="V3" s="230"/>
-      <c r="W3" s="230"/>
-      <c r="X3" s="230"/>
-      <c r="Y3" s="230"/>
-      <c r="Z3" s="230"/>
-      <c r="AA3" s="230"/>
-      <c r="AB3" s="230"/>
-      <c r="AC3" s="230"/>
-      <c r="AD3" s="230"/>
-      <c r="AE3" s="230"/>
+      <c r="B3" s="231"/>
+      <c r="C3" s="231"/>
+      <c r="D3" s="231"/>
+      <c r="E3" s="231"/>
+      <c r="F3" s="231"/>
+      <c r="G3" s="231"/>
+      <c r="H3" s="231"/>
+      <c r="I3" s="231"/>
+      <c r="J3" s="231"/>
+      <c r="K3" s="231"/>
+      <c r="L3" s="231"/>
+      <c r="M3" s="231"/>
+      <c r="N3" s="231"/>
+      <c r="O3" s="231"/>
+      <c r="P3" s="231"/>
+      <c r="Q3" s="231"/>
+      <c r="R3" s="231"/>
+      <c r="S3" s="231"/>
+      <c r="T3" s="231"/>
+      <c r="U3" s="231"/>
+      <c r="V3" s="231"/>
+      <c r="W3" s="231"/>
+      <c r="X3" s="231"/>
+      <c r="Y3" s="231"/>
+      <c r="Z3" s="231"/>
+      <c r="AA3" s="231"/>
+      <c r="AB3" s="231"/>
+      <c r="AC3" s="231"/>
+      <c r="AD3" s="231"/>
+      <c r="AE3" s="231"/>
       <c r="AF3" s="144"/>
       <c r="AG3" s="144"/>
       <c r="AH3" s="144"/>
@@ -8346,17 +8356,17 @@
     </row>
     <row r="6" spans="1:54" ht="30" customHeight="1" thickBot="1">
       <c r="A6" s="111"/>
-      <c r="B6" s="236" t="str">
+      <c r="B6" s="237" t="str">
         <f>IF(OR(AK7=FALSE,AK11=FALSE,AK13=FALSE),"※項目が未チェックです","")</f>
         <v>※項目が未チェックです</v>
       </c>
-      <c r="C6" s="236"/>
-      <c r="D6" s="236"/>
-      <c r="E6" s="236"/>
-      <c r="F6" s="236"/>
-      <c r="G6" s="236"/>
-      <c r="H6" s="236"/>
-      <c r="I6" s="236"/>
+      <c r="C6" s="237"/>
+      <c r="D6" s="237"/>
+      <c r="E6" s="237"/>
+      <c r="F6" s="237"/>
+      <c r="G6" s="237"/>
+      <c r="H6" s="237"/>
+      <c r="I6" s="237"/>
       <c r="J6" s="136"/>
       <c r="K6" s="136"/>
       <c r="L6" s="136"/>
@@ -8777,18 +8787,18 @@
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
-      <c r="D16" s="233"/>
-      <c r="E16" s="233"/>
+      <c r="D16" s="234"/>
+      <c r="E16" s="234"/>
       <c r="F16" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="233"/>
-      <c r="H16" s="233"/>
+      <c r="G16" s="234"/>
+      <c r="H16" s="234"/>
       <c r="I16" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="J16" s="233"/>
-      <c r="K16" s="233"/>
+      <c r="J16" s="234"/>
+      <c r="K16" s="234"/>
       <c r="L16" s="31" t="s">
         <v>19</v>
       </c>
@@ -8800,18 +8810,18 @@
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
-      <c r="S16" s="234"/>
-      <c r="T16" s="234"/>
-      <c r="U16" s="234"/>
-      <c r="V16" s="234"/>
-      <c r="W16" s="234"/>
-      <c r="X16" s="234"/>
-      <c r="Y16" s="234"/>
-      <c r="Z16" s="234"/>
-      <c r="AA16" s="234"/>
-      <c r="AB16" s="234"/>
-      <c r="AC16" s="234"/>
-      <c r="AD16" s="234"/>
+      <c r="S16" s="235"/>
+      <c r="T16" s="235"/>
+      <c r="U16" s="235"/>
+      <c r="V16" s="235"/>
+      <c r="W16" s="235"/>
+      <c r="X16" s="235"/>
+      <c r="Y16" s="235"/>
+      <c r="Z16" s="235"/>
+      <c r="AA16" s="235"/>
+      <c r="AB16" s="235"/>
+      <c r="AC16" s="235"/>
+      <c r="AD16" s="235"/>
       <c r="AE16" s="2"/>
       <c r="AH16" s="45"/>
       <c r="AR16" s="3"/>
@@ -8903,56 +8913,56 @@
       <c r="A19" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="231" t="s">
+      <c r="B19" s="232" t="s">
         <v>165</v>
       </c>
-      <c r="C19" s="231"/>
-      <c r="D19" s="231"/>
-      <c r="E19" s="231"/>
-      <c r="F19" s="231"/>
-      <c r="G19" s="231"/>
-      <c r="H19" s="235" t="str">
+      <c r="C19" s="232"/>
+      <c r="D19" s="232"/>
+      <c r="E19" s="232"/>
+      <c r="F19" s="232"/>
+      <c r="G19" s="232"/>
+      <c r="H19" s="236" t="str">
         <f>IF(別添2!E6="","",別添2!E6)</f>
         <v/>
       </c>
-      <c r="I19" s="235"/>
-      <c r="J19" s="235"/>
-      <c r="K19" s="235"/>
-      <c r="L19" s="235"/>
-      <c r="M19" s="235"/>
-      <c r="N19" s="235"/>
-      <c r="O19" s="235"/>
-      <c r="P19" s="235"/>
-      <c r="Q19" s="235"/>
-      <c r="R19" s="235"/>
-      <c r="S19" s="235"/>
-      <c r="T19" s="235"/>
+      <c r="I19" s="236"/>
+      <c r="J19" s="236"/>
+      <c r="K19" s="236"/>
+      <c r="L19" s="236"/>
+      <c r="M19" s="236"/>
+      <c r="N19" s="236"/>
+      <c r="O19" s="236"/>
+      <c r="P19" s="236"/>
+      <c r="Q19" s="236"/>
+      <c r="R19" s="236"/>
+      <c r="S19" s="236"/>
+      <c r="T19" s="236"/>
     </row>
     <row r="20" spans="1:64" ht="30" customHeight="1">
-      <c r="B20" s="231" t="s">
+      <c r="B20" s="232" t="s">
         <v>159</v>
       </c>
-      <c r="C20" s="231"/>
-      <c r="D20" s="231"/>
-      <c r="E20" s="231"/>
-      <c r="F20" s="231"/>
-      <c r="G20" s="231"/>
-      <c r="H20" s="232" t="str">
+      <c r="C20" s="232"/>
+      <c r="D20" s="232"/>
+      <c r="E20" s="232"/>
+      <c r="F20" s="232"/>
+      <c r="G20" s="232"/>
+      <c r="H20" s="233" t="str">
         <f>IF(別添2!H28="","",別添2!H28)</f>
         <v/>
       </c>
-      <c r="I20" s="232"/>
-      <c r="J20" s="232"/>
-      <c r="K20" s="232"/>
-      <c r="L20" s="232"/>
-      <c r="M20" s="232"/>
-      <c r="N20" s="232"/>
-      <c r="O20" s="232"/>
-      <c r="P20" s="232"/>
-      <c r="Q20" s="232"/>
-      <c r="R20" s="232"/>
-      <c r="S20" s="232"/>
-      <c r="T20" s="232"/>
+      <c r="I20" s="233"/>
+      <c r="J20" s="233"/>
+      <c r="K20" s="233"/>
+      <c r="L20" s="233"/>
+      <c r="M20" s="233"/>
+      <c r="N20" s="233"/>
+      <c r="O20" s="233"/>
+      <c r="P20" s="233"/>
+      <c r="Q20" s="233"/>
+      <c r="R20" s="233"/>
+      <c r="S20" s="233"/>
+      <c r="T20" s="233"/>
     </row>
     <row r="21" spans="1:64" ht="15" customHeight="1">
       <c r="A21" s="12"/>
@@ -9163,26 +9173,26 @@
       <c r="F29" s="134"/>
       <c r="G29" s="134"/>
       <c r="H29" s="134"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="229"/>
-      <c r="M29" s="229"/>
-      <c r="N29" s="229"/>
-      <c r="O29" s="229"/>
-      <c r="P29" s="229"/>
-      <c r="Q29" s="229"/>
-      <c r="R29" s="229"/>
-      <c r="S29" s="229"/>
-      <c r="T29" s="229"/>
-      <c r="U29" s="229"/>
-      <c r="V29" s="229"/>
-      <c r="W29" s="229"/>
-      <c r="X29" s="229"/>
-      <c r="Y29" s="229"/>
-      <c r="Z29" s="229"/>
-      <c r="AA29" s="229"/>
-      <c r="AB29" s="229"/>
+      <c r="I29" s="230"/>
+      <c r="J29" s="230"/>
+      <c r="K29" s="230"/>
+      <c r="L29" s="230"/>
+      <c r="M29" s="230"/>
+      <c r="N29" s="230"/>
+      <c r="O29" s="230"/>
+      <c r="P29" s="230"/>
+      <c r="Q29" s="230"/>
+      <c r="R29" s="230"/>
+      <c r="S29" s="230"/>
+      <c r="T29" s="230"/>
+      <c r="U29" s="230"/>
+      <c r="V29" s="230"/>
+      <c r="W29" s="230"/>
+      <c r="X29" s="230"/>
+      <c r="Y29" s="230"/>
+      <c r="Z29" s="230"/>
+      <c r="AA29" s="230"/>
+      <c r="AB29" s="230"/>
       <c r="AC29" s="16"/>
       <c r="AD29" s="16"/>
       <c r="AE29" s="16"/>
@@ -9249,7 +9259,7 @@
     <row r="51" s="16" customFormat="1" ht="24.95" customHeight="1"/>
     <row r="52" s="16" customFormat="1" ht="24.95" customHeight="1"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="a72KYiQt8dcM1+bLjuD8cm1bNurCmzStBugadPonjnrZApUfa6hJoNGaU0sysDh0DcbbrDTn5bigAYp6i9hmpQ==" saltValue="eQG+vUvjkvUETpT5rl15Ug==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="yhUJiCc6B2AdXqg2dCRoyXpw8/G05An5x2W1GfpTJ1/TP+K7ldAZFbXYGRfkYMSxR4LeWi1/mNconD/F0esygg==" saltValue="k4F59GgecTN27/OCN2N9Og==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="11">
     <mergeCell ref="I29:AB29"/>
     <mergeCell ref="A3:AE3"/>
@@ -9418,13 +9428,13 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="18.75" customHeight="1">
-      <c r="A3" s="237" t="s">
+      <c r="A3" s="238" t="s">
         <v>170</v>
       </c>
-      <c r="B3" s="237"/>
-      <c r="C3" s="237"/>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
+      <c r="B3" s="238"/>
+      <c r="C3" s="238"/>
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
       <c r="F3" s="23"/>
       <c r="G3" s="23"/>
       <c r="H3" s="23"/>
@@ -9503,7 +9513,7 @@
       <c r="H11" s="38"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="QBshGNUWKKCDZ4Gw46ShUYpqp3njinTBW/lspEddJY5pq5pBczN4sp90Vsxilc7AKOWHJD/mlSA6XiEpphB0jQ==" saltValue="7v5tBe/cf1YlhZHwblpGnA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="wTIwdFrKCE3aTr2+0J+/IkCXto7qg2zyj+hcGYTNXl9ijyK5bKuzDLBWW713/d+RuDvKok3kYFHJJWum8mKGow==" saltValue="muyuenkI/vZco8p0IPhr8w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A3:E3"/>
   </mergeCells>
@@ -9585,34 +9595,34 @@
       </c>
       <c r="K2" s="202"/>
       <c r="L2" s="202"/>
-      <c r="M2" s="238" t="str">
+      <c r="M2" s="239" t="str">
         <f>IF(AH9=TRUE,C9,IF(AH10=TRUE,C10,""))</f>
         <v/>
       </c>
-      <c r="N2" s="238"/>
-      <c r="O2" s="238"/>
-      <c r="P2" s="238"/>
-      <c r="Q2" s="238"/>
-      <c r="R2" s="238"/>
+      <c r="N2" s="239"/>
+      <c r="O2" s="239"/>
+      <c r="P2" s="239"/>
+      <c r="Q2" s="239"/>
+      <c r="R2" s="239"/>
       <c r="S2" s="32" t="s">
         <v>356</v>
       </c>
       <c r="T2" s="202"/>
-      <c r="U2" s="241"/>
-      <c r="V2" s="241"/>
-      <c r="W2" s="242" t="s">
+      <c r="U2" s="242"/>
+      <c r="V2" s="242"/>
+      <c r="W2" s="243" t="s">
         <v>40</v>
       </c>
-      <c r="X2" s="242"/>
-      <c r="Y2" s="242"/>
-      <c r="Z2" s="242"/>
-      <c r="AA2" s="242"/>
-      <c r="AB2" s="242"/>
-      <c r="AC2" s="242"/>
-      <c r="AD2" s="242"/>
-      <c r="AE2" s="242"/>
-      <c r="AF2" s="242"/>
-      <c r="AG2" s="242"/>
+      <c r="X2" s="243"/>
+      <c r="Y2" s="243"/>
+      <c r="Z2" s="243"/>
+      <c r="AA2" s="243"/>
+      <c r="AB2" s="243"/>
+      <c r="AC2" s="243"/>
+      <c r="AD2" s="243"/>
+      <c r="AE2" s="243"/>
+      <c r="AF2" s="243"/>
+      <c r="AG2" s="243"/>
     </row>
     <row r="3" spans="1:43" ht="7.15" customHeight="1">
       <c r="A3" s="2"/>
@@ -9668,26 +9678,26 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
-      <c r="S4" s="243" t="s">
+      <c r="S4" s="244" t="s">
         <v>160</v>
       </c>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="243"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="244" t="str">
+      <c r="T4" s="244"/>
+      <c r="U4" s="244"/>
+      <c r="V4" s="244"/>
+      <c r="W4" s="244"/>
+      <c r="X4" s="245" t="str">
         <f>IF(別添2!E6="","",別添2!E6)</f>
         <v/>
       </c>
-      <c r="Y4" s="245"/>
-      <c r="Z4" s="245"/>
-      <c r="AA4" s="245"/>
-      <c r="AB4" s="245"/>
-      <c r="AC4" s="245"/>
-      <c r="AD4" s="245"/>
-      <c r="AE4" s="245"/>
-      <c r="AF4" s="245"/>
-      <c r="AG4" s="246"/>
+      <c r="Y4" s="246"/>
+      <c r="Z4" s="246"/>
+      <c r="AA4" s="246"/>
+      <c r="AB4" s="246"/>
+      <c r="AC4" s="246"/>
+      <c r="AD4" s="246"/>
+      <c r="AE4" s="246"/>
+      <c r="AF4" s="246"/>
+      <c r="AG4" s="247"/>
     </row>
     <row r="5" spans="1:43" ht="16.149999999999999" customHeight="1">
       <c r="A5" s="2"/>
@@ -9708,26 +9718,26 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
-      <c r="S5" s="247" t="s">
+      <c r="S5" s="248" t="s">
         <v>161</v>
       </c>
-      <c r="T5" s="247"/>
-      <c r="U5" s="247"/>
-      <c r="V5" s="247"/>
-      <c r="W5" s="248"/>
-      <c r="X5" s="249" t="str">
+      <c r="T5" s="248"/>
+      <c r="U5" s="248"/>
+      <c r="V5" s="248"/>
+      <c r="W5" s="249"/>
+      <c r="X5" s="250" t="str">
         <f>IF(別添2!H28="","",別添2!H28)</f>
         <v/>
       </c>
-      <c r="Y5" s="250"/>
-      <c r="Z5" s="250"/>
-      <c r="AA5" s="250"/>
-      <c r="AB5" s="250"/>
-      <c r="AC5" s="250"/>
-      <c r="AD5" s="250"/>
-      <c r="AE5" s="250"/>
-      <c r="AF5" s="250"/>
-      <c r="AG5" s="251"/>
+      <c r="Y5" s="251"/>
+      <c r="Z5" s="251"/>
+      <c r="AA5" s="251"/>
+      <c r="AB5" s="251"/>
+      <c r="AC5" s="251"/>
+      <c r="AD5" s="251"/>
+      <c r="AE5" s="251"/>
+      <c r="AF5" s="251"/>
+      <c r="AG5" s="252"/>
     </row>
     <row r="6" spans="1:43" s="91" customFormat="1" ht="16.149999999999999" customHeight="1">
       <c r="X6" s="92"/>
@@ -9760,7 +9770,10 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="G7" s="203" t="str">
+        <f>IF($AH$9=$AH$10,"※どちらか１つを選択してください。","")</f>
+        <v>※どちらか１つを選択してください。</v>
+      </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -9936,18 +9949,18 @@
       <c r="AG14" s="2"/>
     </row>
     <row r="15" spans="1:43" ht="16.149999999999999" customHeight="1" thickBot="1">
-      <c r="B15" s="254" t="s">
+      <c r="B15" s="255" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="255"/>
-      <c r="D15" s="255"/>
-      <c r="E15" s="239"/>
-      <c r="F15" s="239"/>
+      <c r="C15" s="256"/>
+      <c r="D15" s="256"/>
+      <c r="E15" s="240"/>
+      <c r="F15" s="240"/>
       <c r="G15" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H15" s="239"/>
-      <c r="I15" s="239"/>
+      <c r="H15" s="240"/>
+      <c r="I15" s="240"/>
       <c r="J15" s="5" t="s">
         <v>30</v>
       </c>
@@ -9959,23 +9972,23 @@
         <v>16</v>
       </c>
       <c r="N15" s="5"/>
-      <c r="O15" s="239"/>
-      <c r="P15" s="239"/>
+      <c r="O15" s="240"/>
+      <c r="P15" s="240"/>
       <c r="Q15" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R15" s="239"/>
-      <c r="S15" s="239"/>
+      <c r="R15" s="240"/>
+      <c r="S15" s="240"/>
       <c r="T15" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="V15" s="252" t="str">
-        <f>IF(OR(E15="",H15="",O15="",R15=""),"",((O15-E15)*12)+(R15-H15))</f>
+      <c r="V15" s="253" t="str">
+        <f>IF(OR(E15="",H15="",O15="",R15=""),"",((O15-E15)*12)+(R15-H15)+1)</f>
         <v/>
       </c>
-      <c r="W15" s="252"/>
-      <c r="X15" s="252"/>
-      <c r="Y15" s="253"/>
+      <c r="W15" s="253"/>
+      <c r="X15" s="253"/>
+      <c r="Y15" s="254"/>
       <c r="Z15" s="2" t="s">
         <v>46</v>
       </c>
@@ -10046,18 +10059,18 @@
     </row>
     <row r="18" spans="1:62" ht="16.149999999999999" customHeight="1" thickBot="1">
       <c r="A18" s="2"/>
-      <c r="B18" s="254" t="s">
+      <c r="B18" s="255" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="255"/>
-      <c r="D18" s="255"/>
-      <c r="E18" s="239"/>
-      <c r="F18" s="239"/>
+      <c r="C18" s="256"/>
+      <c r="D18" s="256"/>
+      <c r="E18" s="240"/>
+      <c r="F18" s="240"/>
       <c r="G18" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H18" s="239"/>
-      <c r="I18" s="239"/>
+      <c r="H18" s="240"/>
+      <c r="I18" s="240"/>
       <c r="J18" s="5" t="s">
         <v>30</v>
       </c>
@@ -10069,23 +10082,23 @@
         <v>16</v>
       </c>
       <c r="N18" s="5"/>
-      <c r="O18" s="239"/>
-      <c r="P18" s="239"/>
+      <c r="O18" s="240"/>
+      <c r="P18" s="240"/>
       <c r="Q18" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R18" s="239"/>
-      <c r="S18" s="239"/>
+      <c r="R18" s="240"/>
+      <c r="S18" s="240"/>
       <c r="T18" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="V18" s="252" t="str">
-        <f>IF(OR(E18="",H18="",O18="",R18=""),"",((O18-E18)*12)+(R18-H18))</f>
+      <c r="V18" s="253" t="str">
+        <f>IF(OR(E18="",H18="",O18="",R18=""),"",((O18-E18)*12)+(R18-H18)+1)</f>
         <v/>
       </c>
-      <c r="W18" s="252"/>
-      <c r="X18" s="252"/>
-      <c r="Y18" s="253"/>
+      <c r="W18" s="253"/>
+      <c r="X18" s="253"/>
+      <c r="Y18" s="254"/>
       <c r="Z18" s="2" t="s">
         <v>46</v>
       </c>
@@ -10150,12 +10163,12 @@
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
-      <c r="T20" s="266"/>
-      <c r="U20" s="266"/>
-      <c r="V20" s="266"/>
-      <c r="W20" s="266"/>
-      <c r="X20" s="266"/>
-      <c r="Y20" s="266"/>
+      <c r="T20" s="267"/>
+      <c r="U20" s="267"/>
+      <c r="V20" s="267"/>
+      <c r="W20" s="267"/>
+      <c r="X20" s="267"/>
+      <c r="Y20" s="267"/>
       <c r="Z20" s="2"/>
       <c r="AA20" s="2"/>
       <c r="AB20" s="2"/>
@@ -10195,11 +10208,11 @@
       <c r="Y21" s="5"/>
       <c r="Z21" s="5"/>
       <c r="AA21" s="5"/>
-      <c r="AB21" s="240"/>
-      <c r="AC21" s="240"/>
-      <c r="AD21" s="240"/>
-      <c r="AE21" s="240"/>
-      <c r="AF21" s="240"/>
+      <c r="AB21" s="241"/>
+      <c r="AC21" s="241"/>
+      <c r="AD21" s="241"/>
+      <c r="AE21" s="241"/>
+      <c r="AF21" s="241"/>
       <c r="AG21" s="6" t="s">
         <v>38</v>
       </c>
@@ -10404,34 +10417,34 @@
       <c r="AE26" s="158"/>
       <c r="AF26" s="2"/>
       <c r="AG26" s="3"/>
-      <c r="AI26" s="294"/>
-      <c r="AJ26" s="294"/>
-      <c r="AK26" s="294"/>
-      <c r="AL26" s="294"/>
-      <c r="AM26" s="294"/>
-      <c r="AN26" s="294"/>
-      <c r="AO26" s="294"/>
-      <c r="AP26" s="294"/>
-      <c r="AQ26" s="294"/>
-      <c r="AR26" s="294"/>
-      <c r="AS26" s="294"/>
-      <c r="AT26" s="294"/>
-      <c r="AU26" s="294"/>
-      <c r="AV26" s="294"/>
-      <c r="AW26" s="294"/>
-      <c r="AX26" s="294"/>
-      <c r="AY26" s="294"/>
-      <c r="AZ26" s="294"/>
-      <c r="BA26" s="294"/>
-      <c r="BB26" s="294"/>
-      <c r="BC26" s="294"/>
-      <c r="BD26" s="294"/>
-      <c r="BE26" s="294"/>
-      <c r="BF26" s="294"/>
-      <c r="BG26" s="294"/>
-      <c r="BH26" s="294"/>
-      <c r="BI26" s="294"/>
-      <c r="BJ26" s="294"/>
+      <c r="AI26" s="295"/>
+      <c r="AJ26" s="295"/>
+      <c r="AK26" s="295"/>
+      <c r="AL26" s="295"/>
+      <c r="AM26" s="295"/>
+      <c r="AN26" s="295"/>
+      <c r="AO26" s="295"/>
+      <c r="AP26" s="295"/>
+      <c r="AQ26" s="295"/>
+      <c r="AR26" s="295"/>
+      <c r="AS26" s="295"/>
+      <c r="AT26" s="295"/>
+      <c r="AU26" s="295"/>
+      <c r="AV26" s="295"/>
+      <c r="AW26" s="295"/>
+      <c r="AX26" s="295"/>
+      <c r="AY26" s="295"/>
+      <c r="AZ26" s="295"/>
+      <c r="BA26" s="295"/>
+      <c r="BB26" s="295"/>
+      <c r="BC26" s="295"/>
+      <c r="BD26" s="295"/>
+      <c r="BE26" s="295"/>
+      <c r="BF26" s="295"/>
+      <c r="BG26" s="295"/>
+      <c r="BH26" s="295"/>
+      <c r="BI26" s="295"/>
+      <c r="BJ26" s="295"/>
     </row>
     <row r="27" spans="1:62" s="36" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="108" t="s">
@@ -10471,34 +10484,34 @@
       <c r="AE27" s="158"/>
       <c r="AF27" s="2"/>
       <c r="AG27" s="3"/>
-      <c r="AI27" s="295"/>
-      <c r="AJ27" s="295"/>
-      <c r="AK27" s="295"/>
-      <c r="AL27" s="295"/>
-      <c r="AM27" s="295"/>
-      <c r="AN27" s="295"/>
-      <c r="AO27" s="295"/>
-      <c r="AP27" s="295"/>
-      <c r="AQ27" s="295"/>
-      <c r="AR27" s="295"/>
-      <c r="AS27" s="295"/>
-      <c r="AT27" s="295"/>
-      <c r="AU27" s="295"/>
-      <c r="AV27" s="295"/>
-      <c r="AW27" s="295"/>
-      <c r="AX27" s="295"/>
-      <c r="AY27" s="295"/>
-      <c r="AZ27" s="295"/>
-      <c r="BA27" s="295"/>
-      <c r="BB27" s="295"/>
-      <c r="BC27" s="295"/>
-      <c r="BD27" s="295"/>
-      <c r="BE27" s="295"/>
-      <c r="BF27" s="295"/>
-      <c r="BG27" s="295"/>
-      <c r="BH27" s="295"/>
-      <c r="BI27" s="295"/>
-      <c r="BJ27" s="295"/>
+      <c r="AI27" s="296"/>
+      <c r="AJ27" s="296"/>
+      <c r="AK27" s="296"/>
+      <c r="AL27" s="296"/>
+      <c r="AM27" s="296"/>
+      <c r="AN27" s="296"/>
+      <c r="AO27" s="296"/>
+      <c r="AP27" s="296"/>
+      <c r="AQ27" s="296"/>
+      <c r="AR27" s="296"/>
+      <c r="AS27" s="296"/>
+      <c r="AT27" s="296"/>
+      <c r="AU27" s="296"/>
+      <c r="AV27" s="296"/>
+      <c r="AW27" s="296"/>
+      <c r="AX27" s="296"/>
+      <c r="AY27" s="296"/>
+      <c r="AZ27" s="296"/>
+      <c r="BA27" s="296"/>
+      <c r="BB27" s="296"/>
+      <c r="BC27" s="296"/>
+      <c r="BD27" s="296"/>
+      <c r="BE27" s="296"/>
+      <c r="BF27" s="296"/>
+      <c r="BG27" s="296"/>
+      <c r="BH27" s="296"/>
+      <c r="BI27" s="296"/>
+      <c r="BJ27" s="296"/>
     </row>
     <row r="28" spans="1:62" s="36" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="31"/>
@@ -10663,34 +10676,34 @@
       <c r="AE30" s="32"/>
       <c r="AF30" s="32"/>
       <c r="AG30" s="32"/>
-      <c r="AI30" s="290"/>
-      <c r="AJ30" s="290"/>
-      <c r="AK30" s="290"/>
-      <c r="AL30" s="290"/>
-      <c r="AM30" s="290"/>
-      <c r="AN30" s="290"/>
-      <c r="AO30" s="290"/>
-      <c r="AP30" s="290"/>
-      <c r="AQ30" s="290"/>
-      <c r="AR30" s="290"/>
-      <c r="AS30" s="290"/>
-      <c r="AT30" s="290"/>
-      <c r="AU30" s="290"/>
-      <c r="AV30" s="290"/>
-      <c r="AW30" s="290"/>
-      <c r="AX30" s="290"/>
-      <c r="AY30" s="290"/>
-      <c r="AZ30" s="290"/>
-      <c r="BA30" s="290"/>
-      <c r="BB30" s="290"/>
-      <c r="BC30" s="290"/>
-      <c r="BD30" s="290"/>
-      <c r="BE30" s="290"/>
-      <c r="BF30" s="290"/>
-      <c r="BG30" s="290"/>
-      <c r="BH30" s="290"/>
-      <c r="BI30" s="290"/>
-      <c r="BJ30" s="290"/>
+      <c r="AI30" s="291"/>
+      <c r="AJ30" s="291"/>
+      <c r="AK30" s="291"/>
+      <c r="AL30" s="291"/>
+      <c r="AM30" s="291"/>
+      <c r="AN30" s="291"/>
+      <c r="AO30" s="291"/>
+      <c r="AP30" s="291"/>
+      <c r="AQ30" s="291"/>
+      <c r="AR30" s="291"/>
+      <c r="AS30" s="291"/>
+      <c r="AT30" s="291"/>
+      <c r="AU30" s="291"/>
+      <c r="AV30" s="291"/>
+      <c r="AW30" s="291"/>
+      <c r="AX30" s="291"/>
+      <c r="AY30" s="291"/>
+      <c r="AZ30" s="291"/>
+      <c r="BA30" s="291"/>
+      <c r="BB30" s="291"/>
+      <c r="BC30" s="291"/>
+      <c r="BD30" s="291"/>
+      <c r="BE30" s="291"/>
+      <c r="BF30" s="291"/>
+      <c r="BG30" s="291"/>
+      <c r="BH30" s="291"/>
+      <c r="BI30" s="291"/>
+      <c r="BJ30" s="291"/>
     </row>
     <row r="31" spans="1:62" s="36" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="26" t="s">
@@ -10723,13 +10736,13 @@
       <c r="Z31" s="13"/>
       <c r="AA31" s="21"/>
       <c r="AB31" s="105"/>
-      <c r="AC31" s="261" t="str">
+      <c r="AC31" s="262" t="str">
         <f>IF(AC39+AC48=0,"",AC39+AC48)</f>
         <v/>
       </c>
-      <c r="AD31" s="261"/>
-      <c r="AE31" s="261"/>
-      <c r="AF31" s="261"/>
+      <c r="AD31" s="262"/>
+      <c r="AE31" s="262"/>
+      <c r="AF31" s="262"/>
       <c r="AG31" s="22" t="s">
         <v>37</v>
       </c>
@@ -10766,56 +10779,56 @@
       <c r="Z32" s="194"/>
       <c r="AA32" s="195"/>
       <c r="AB32" s="195"/>
-      <c r="AC32" s="262" t="str">
+      <c r="AC32" s="263" t="str">
         <f>IF(AC40+AC49=0,"",AC40+AC49)</f>
         <v/>
       </c>
-      <c r="AD32" s="262"/>
-      <c r="AE32" s="262"/>
-      <c r="AF32" s="262"/>
+      <c r="AD32" s="263"/>
+      <c r="AE32" s="263"/>
+      <c r="AF32" s="263"/>
       <c r="AG32" s="196" t="s">
         <v>38</v>
       </c>
       <c r="AR32" s="100"/>
     </row>
     <row r="33" spans="1:44" s="36" customFormat="1" ht="15" customHeight="1">
-      <c r="A33" s="263" t="s">
+      <c r="A33" s="264" t="s">
         <v>217</v>
       </c>
-      <c r="B33" s="264"/>
-      <c r="C33" s="264"/>
-      <c r="D33" s="264"/>
-      <c r="E33" s="264"/>
-      <c r="F33" s="264"/>
-      <c r="G33" s="264"/>
-      <c r="H33" s="264"/>
-      <c r="I33" s="264"/>
-      <c r="J33" s="264"/>
-      <c r="K33" s="264"/>
-      <c r="L33" s="264"/>
-      <c r="M33" s="264"/>
-      <c r="N33" s="264"/>
-      <c r="O33" s="264"/>
-      <c r="P33" s="264"/>
-      <c r="Q33" s="264"/>
-      <c r="R33" s="264"/>
-      <c r="S33" s="264"/>
-      <c r="T33" s="264"/>
-      <c r="U33" s="264"/>
-      <c r="V33" s="264"/>
-      <c r="W33" s="264"/>
-      <c r="X33" s="264"/>
-      <c r="Y33" s="264"/>
-      <c r="Z33" s="264"/>
-      <c r="AA33" s="264"/>
-      <c r="AB33" s="264"/>
-      <c r="AC33" s="265" t="str">
+      <c r="B33" s="265"/>
+      <c r="C33" s="265"/>
+      <c r="D33" s="265"/>
+      <c r="E33" s="265"/>
+      <c r="F33" s="265"/>
+      <c r="G33" s="265"/>
+      <c r="H33" s="265"/>
+      <c r="I33" s="265"/>
+      <c r="J33" s="265"/>
+      <c r="K33" s="265"/>
+      <c r="L33" s="265"/>
+      <c r="M33" s="265"/>
+      <c r="N33" s="265"/>
+      <c r="O33" s="265"/>
+      <c r="P33" s="265"/>
+      <c r="Q33" s="265"/>
+      <c r="R33" s="265"/>
+      <c r="S33" s="265"/>
+      <c r="T33" s="265"/>
+      <c r="U33" s="265"/>
+      <c r="V33" s="265"/>
+      <c r="W33" s="265"/>
+      <c r="X33" s="265"/>
+      <c r="Y33" s="265"/>
+      <c r="Z33" s="265"/>
+      <c r="AA33" s="265"/>
+      <c r="AB33" s="265"/>
+      <c r="AC33" s="266" t="str">
         <f>IF(AC41+AC50=0,"",AC41+AC50)</f>
         <v/>
       </c>
-      <c r="AD33" s="265"/>
-      <c r="AE33" s="265"/>
-      <c r="AF33" s="265"/>
+      <c r="AD33" s="266"/>
+      <c r="AE33" s="266"/>
+      <c r="AF33" s="266"/>
       <c r="AG33" s="33" t="s">
         <v>38</v>
       </c>
@@ -10852,13 +10865,13 @@
       <c r="Z34" s="8"/>
       <c r="AA34" s="8"/>
       <c r="AB34" s="120"/>
-      <c r="AC34" s="256" t="str">
+      <c r="AC34" s="257" t="str">
         <f>IFERROR(AC32-AC33,"")</f>
         <v/>
       </c>
-      <c r="AD34" s="256"/>
-      <c r="AE34" s="256"/>
-      <c r="AF34" s="256"/>
+      <c r="AD34" s="257"/>
+      <c r="AE34" s="257"/>
+      <c r="AF34" s="257"/>
       <c r="AG34" s="121" t="s">
         <v>38</v>
       </c>
@@ -10895,53 +10908,53 @@
       <c r="Z35" s="198"/>
       <c r="AA35" s="198"/>
       <c r="AB35" s="199"/>
-      <c r="AC35" s="257" t="str">
+      <c r="AC35" s="258" t="str">
         <f>IFERROR((AC34/AC33)*100,"")</f>
         <v/>
       </c>
-      <c r="AD35" s="257"/>
-      <c r="AE35" s="257"/>
-      <c r="AF35" s="257"/>
+      <c r="AD35" s="258"/>
+      <c r="AE35" s="258"/>
+      <c r="AF35" s="258"/>
       <c r="AG35" s="200" t="s">
         <v>49</v>
       </c>
       <c r="AR35" s="3"/>
     </row>
     <row r="36" spans="1:44" s="36" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A36" s="258" t="s">
+      <c r="A36" s="259" t="s">
         <v>174</v>
       </c>
-      <c r="B36" s="259"/>
-      <c r="C36" s="259"/>
-      <c r="D36" s="259"/>
-      <c r="E36" s="259"/>
-      <c r="F36" s="259"/>
-      <c r="G36" s="259"/>
-      <c r="H36" s="259"/>
-      <c r="I36" s="259"/>
-      <c r="J36" s="259"/>
-      <c r="K36" s="259"/>
-      <c r="L36" s="259"/>
-      <c r="M36" s="259"/>
-      <c r="N36" s="259"/>
-      <c r="O36" s="259"/>
-      <c r="P36" s="259"/>
-      <c r="Q36" s="259"/>
-      <c r="R36" s="259"/>
-      <c r="S36" s="259"/>
-      <c r="T36" s="259"/>
-      <c r="U36" s="259"/>
-      <c r="V36" s="259"/>
-      <c r="W36" s="259"/>
-      <c r="X36" s="259"/>
-      <c r="Y36" s="259"/>
-      <c r="Z36" s="259"/>
-      <c r="AA36" s="259"/>
-      <c r="AB36" s="259"/>
-      <c r="AC36" s="260"/>
-      <c r="AD36" s="260"/>
-      <c r="AE36" s="260"/>
-      <c r="AF36" s="260"/>
+      <c r="B36" s="260"/>
+      <c r="C36" s="260"/>
+      <c r="D36" s="260"/>
+      <c r="E36" s="260"/>
+      <c r="F36" s="260"/>
+      <c r="G36" s="260"/>
+      <c r="H36" s="260"/>
+      <c r="I36" s="260"/>
+      <c r="J36" s="260"/>
+      <c r="K36" s="260"/>
+      <c r="L36" s="260"/>
+      <c r="M36" s="260"/>
+      <c r="N36" s="260"/>
+      <c r="O36" s="260"/>
+      <c r="P36" s="260"/>
+      <c r="Q36" s="260"/>
+      <c r="R36" s="260"/>
+      <c r="S36" s="260"/>
+      <c r="T36" s="260"/>
+      <c r="U36" s="260"/>
+      <c r="V36" s="260"/>
+      <c r="W36" s="260"/>
+      <c r="X36" s="260"/>
+      <c r="Y36" s="260"/>
+      <c r="Z36" s="260"/>
+      <c r="AA36" s="260"/>
+      <c r="AB36" s="260"/>
+      <c r="AC36" s="261"/>
+      <c r="AD36" s="261"/>
+      <c r="AE36" s="261"/>
+      <c r="AF36" s="261"/>
       <c r="AG36" s="123" t="s">
         <v>38</v>
       </c>
@@ -10984,41 +10997,41 @@
       <c r="AR37" s="3"/>
     </row>
     <row r="38" spans="1:44" s="36" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A38" s="267" t="s">
+      <c r="A38" s="268" t="s">
         <v>316</v>
       </c>
-      <c r="B38" s="267"/>
-      <c r="C38" s="267"/>
-      <c r="D38" s="267"/>
-      <c r="E38" s="267"/>
-      <c r="F38" s="267"/>
-      <c r="G38" s="267"/>
-      <c r="H38" s="267"/>
-      <c r="I38" s="267"/>
-      <c r="J38" s="267"/>
-      <c r="K38" s="267"/>
-      <c r="L38" s="267"/>
-      <c r="M38" s="267"/>
-      <c r="N38" s="267"/>
-      <c r="O38" s="267"/>
-      <c r="P38" s="267"/>
-      <c r="Q38" s="267"/>
-      <c r="R38" s="267"/>
-      <c r="S38" s="267"/>
-      <c r="T38" s="267"/>
-      <c r="U38" s="267"/>
-      <c r="V38" s="267"/>
-      <c r="W38" s="267"/>
-      <c r="X38" s="267"/>
-      <c r="Y38" s="267"/>
-      <c r="Z38" s="267"/>
-      <c r="AA38" s="267"/>
-      <c r="AB38" s="267"/>
-      <c r="AC38" s="267"/>
-      <c r="AD38" s="267"/>
-      <c r="AE38" s="267"/>
-      <c r="AF38" s="267"/>
-      <c r="AG38" s="267"/>
+      <c r="B38" s="268"/>
+      <c r="C38" s="268"/>
+      <c r="D38" s="268"/>
+      <c r="E38" s="268"/>
+      <c r="F38" s="268"/>
+      <c r="G38" s="268"/>
+      <c r="H38" s="268"/>
+      <c r="I38" s="268"/>
+      <c r="J38" s="268"/>
+      <c r="K38" s="268"/>
+      <c r="L38" s="268"/>
+      <c r="M38" s="268"/>
+      <c r="N38" s="268"/>
+      <c r="O38" s="268"/>
+      <c r="P38" s="268"/>
+      <c r="Q38" s="268"/>
+      <c r="R38" s="268"/>
+      <c r="S38" s="268"/>
+      <c r="T38" s="268"/>
+      <c r="U38" s="268"/>
+      <c r="V38" s="268"/>
+      <c r="W38" s="268"/>
+      <c r="X38" s="268"/>
+      <c r="Y38" s="268"/>
+      <c r="Z38" s="268"/>
+      <c r="AA38" s="268"/>
+      <c r="AB38" s="268"/>
+      <c r="AC38" s="268"/>
+      <c r="AD38" s="268"/>
+      <c r="AE38" s="268"/>
+      <c r="AF38" s="268"/>
+      <c r="AG38" s="268"/>
       <c r="AR38" s="3"/>
     </row>
     <row r="39" spans="1:44" s="36" customFormat="1" ht="15" customHeight="1">
@@ -11052,90 +11065,90 @@
       <c r="Z39" s="13"/>
       <c r="AA39" s="21"/>
       <c r="AB39" s="105"/>
-      <c r="AC39" s="268"/>
-      <c r="AD39" s="268"/>
-      <c r="AE39" s="268"/>
-      <c r="AF39" s="268"/>
+      <c r="AC39" s="269"/>
+      <c r="AD39" s="269"/>
+      <c r="AE39" s="269"/>
+      <c r="AF39" s="269"/>
       <c r="AG39" s="22" t="s">
         <v>37</v>
       </c>
       <c r="AR39" s="3"/>
     </row>
     <row r="40" spans="1:44" s="36" customFormat="1" ht="15" customHeight="1">
-      <c r="A40" s="269" t="s">
+      <c r="A40" s="270" t="s">
         <v>218</v>
       </c>
-      <c r="B40" s="270"/>
-      <c r="C40" s="270"/>
-      <c r="D40" s="270"/>
-      <c r="E40" s="270"/>
-      <c r="F40" s="270"/>
-      <c r="G40" s="270"/>
-      <c r="H40" s="270"/>
-      <c r="I40" s="270"/>
-      <c r="J40" s="270"/>
-      <c r="K40" s="270"/>
-      <c r="L40" s="270"/>
-      <c r="M40" s="270"/>
-      <c r="N40" s="270"/>
-      <c r="O40" s="270"/>
-      <c r="P40" s="270"/>
-      <c r="Q40" s="270"/>
-      <c r="R40" s="270"/>
-      <c r="S40" s="270"/>
-      <c r="T40" s="270"/>
-      <c r="U40" s="270"/>
-      <c r="V40" s="270"/>
-      <c r="W40" s="270"/>
-      <c r="X40" s="270"/>
-      <c r="Y40" s="270"/>
-      <c r="Z40" s="270"/>
-      <c r="AA40" s="270"/>
-      <c r="AB40" s="270"/>
-      <c r="AC40" s="271"/>
-      <c r="AD40" s="271"/>
-      <c r="AE40" s="271"/>
-      <c r="AF40" s="271"/>
+      <c r="B40" s="271"/>
+      <c r="C40" s="271"/>
+      <c r="D40" s="271"/>
+      <c r="E40" s="271"/>
+      <c r="F40" s="271"/>
+      <c r="G40" s="271"/>
+      <c r="H40" s="271"/>
+      <c r="I40" s="271"/>
+      <c r="J40" s="271"/>
+      <c r="K40" s="271"/>
+      <c r="L40" s="271"/>
+      <c r="M40" s="271"/>
+      <c r="N40" s="271"/>
+      <c r="O40" s="271"/>
+      <c r="P40" s="271"/>
+      <c r="Q40" s="271"/>
+      <c r="R40" s="271"/>
+      <c r="S40" s="271"/>
+      <c r="T40" s="271"/>
+      <c r="U40" s="271"/>
+      <c r="V40" s="271"/>
+      <c r="W40" s="271"/>
+      <c r="X40" s="271"/>
+      <c r="Y40" s="271"/>
+      <c r="Z40" s="271"/>
+      <c r="AA40" s="271"/>
+      <c r="AB40" s="271"/>
+      <c r="AC40" s="272"/>
+      <c r="AD40" s="272"/>
+      <c r="AE40" s="272"/>
+      <c r="AF40" s="272"/>
       <c r="AG40" s="28" t="s">
         <v>38</v>
       </c>
       <c r="AR40" s="3"/>
     </row>
     <row r="41" spans="1:44" s="36" customFormat="1" ht="15" customHeight="1">
-      <c r="A41" s="263" t="s">
+      <c r="A41" s="264" t="s">
         <v>219</v>
       </c>
-      <c r="B41" s="264"/>
-      <c r="C41" s="264"/>
-      <c r="D41" s="264"/>
-      <c r="E41" s="264"/>
-      <c r="F41" s="264"/>
-      <c r="G41" s="264"/>
-      <c r="H41" s="264"/>
-      <c r="I41" s="264"/>
-      <c r="J41" s="264"/>
-      <c r="K41" s="264"/>
-      <c r="L41" s="264"/>
-      <c r="M41" s="264"/>
-      <c r="N41" s="264"/>
-      <c r="O41" s="264"/>
-      <c r="P41" s="264"/>
-      <c r="Q41" s="264"/>
-      <c r="R41" s="264"/>
-      <c r="S41" s="264"/>
-      <c r="T41" s="264"/>
-      <c r="U41" s="264"/>
-      <c r="V41" s="264"/>
-      <c r="W41" s="264"/>
-      <c r="X41" s="264"/>
-      <c r="Y41" s="264"/>
-      <c r="Z41" s="264"/>
-      <c r="AA41" s="264"/>
-      <c r="AB41" s="264"/>
-      <c r="AC41" s="271"/>
-      <c r="AD41" s="271"/>
-      <c r="AE41" s="271"/>
-      <c r="AF41" s="271"/>
+      <c r="B41" s="265"/>
+      <c r="C41" s="265"/>
+      <c r="D41" s="265"/>
+      <c r="E41" s="265"/>
+      <c r="F41" s="265"/>
+      <c r="G41" s="265"/>
+      <c r="H41" s="265"/>
+      <c r="I41" s="265"/>
+      <c r="J41" s="265"/>
+      <c r="K41" s="265"/>
+      <c r="L41" s="265"/>
+      <c r="M41" s="265"/>
+      <c r="N41" s="265"/>
+      <c r="O41" s="265"/>
+      <c r="P41" s="265"/>
+      <c r="Q41" s="265"/>
+      <c r="R41" s="265"/>
+      <c r="S41" s="265"/>
+      <c r="T41" s="265"/>
+      <c r="U41" s="265"/>
+      <c r="V41" s="265"/>
+      <c r="W41" s="265"/>
+      <c r="X41" s="265"/>
+      <c r="Y41" s="265"/>
+      <c r="Z41" s="265"/>
+      <c r="AA41" s="265"/>
+      <c r="AB41" s="265"/>
+      <c r="AC41" s="272"/>
+      <c r="AD41" s="272"/>
+      <c r="AE41" s="272"/>
+      <c r="AF41" s="272"/>
       <c r="AG41" s="33" t="s">
         <v>38</v>
       </c>
@@ -11172,13 +11185,13 @@
       <c r="Z42" s="4"/>
       <c r="AA42" s="4"/>
       <c r="AB42" s="106"/>
-      <c r="AC42" s="272" t="str">
+      <c r="AC42" s="273" t="str">
         <f>IF(AC40-AC41=0,"",AC40-AC41)</f>
         <v/>
       </c>
-      <c r="AD42" s="272"/>
-      <c r="AE42" s="272"/>
-      <c r="AF42" s="272"/>
+      <c r="AD42" s="273"/>
+      <c r="AE42" s="273"/>
+      <c r="AF42" s="273"/>
       <c r="AG42" s="33" t="s">
         <v>38</v>
       </c>
@@ -11215,93 +11228,93 @@
       <c r="Z43" s="125"/>
       <c r="AA43" s="125"/>
       <c r="AB43" s="126"/>
-      <c r="AC43" s="273" t="str">
+      <c r="AC43" s="274" t="str">
         <f>IFERROR((AC42/AC41)*100,"")</f>
         <v/>
       </c>
-      <c r="AD43" s="273"/>
-      <c r="AE43" s="273"/>
-      <c r="AF43" s="273"/>
+      <c r="AD43" s="274"/>
+      <c r="AE43" s="274"/>
+      <c r="AF43" s="274"/>
       <c r="AG43" s="127" t="s">
         <v>49</v>
       </c>
       <c r="AR43" s="3"/>
     </row>
     <row r="44" spans="1:44" s="36" customFormat="1" ht="15" customHeight="1">
-      <c r="A44" s="274" t="s">
+      <c r="A44" s="275" t="s">
         <v>220</v>
       </c>
-      <c r="B44" s="275"/>
-      <c r="C44" s="275"/>
-      <c r="D44" s="275"/>
-      <c r="E44" s="275"/>
-      <c r="F44" s="275"/>
-      <c r="G44" s="275"/>
-      <c r="H44" s="275"/>
-      <c r="I44" s="275"/>
-      <c r="J44" s="275"/>
-      <c r="K44" s="275"/>
-      <c r="L44" s="275"/>
-      <c r="M44" s="275"/>
-      <c r="N44" s="275"/>
-      <c r="O44" s="275"/>
-      <c r="P44" s="275"/>
-      <c r="Q44" s="275"/>
-      <c r="R44" s="275"/>
-      <c r="S44" s="275"/>
-      <c r="T44" s="275"/>
-      <c r="U44" s="275"/>
-      <c r="V44" s="275"/>
-      <c r="W44" s="275"/>
-      <c r="X44" s="275"/>
-      <c r="Y44" s="275"/>
-      <c r="Z44" s="275"/>
-      <c r="AA44" s="275"/>
-      <c r="AB44" s="275"/>
-      <c r="AC44" s="278"/>
-      <c r="AD44" s="278"/>
-      <c r="AE44" s="278"/>
-      <c r="AF44" s="278"/>
+      <c r="B44" s="276"/>
+      <c r="C44" s="276"/>
+      <c r="D44" s="276"/>
+      <c r="E44" s="276"/>
+      <c r="F44" s="276"/>
+      <c r="G44" s="276"/>
+      <c r="H44" s="276"/>
+      <c r="I44" s="276"/>
+      <c r="J44" s="276"/>
+      <c r="K44" s="276"/>
+      <c r="L44" s="276"/>
+      <c r="M44" s="276"/>
+      <c r="N44" s="276"/>
+      <c r="O44" s="276"/>
+      <c r="P44" s="276"/>
+      <c r="Q44" s="276"/>
+      <c r="R44" s="276"/>
+      <c r="S44" s="276"/>
+      <c r="T44" s="276"/>
+      <c r="U44" s="276"/>
+      <c r="V44" s="276"/>
+      <c r="W44" s="276"/>
+      <c r="X44" s="276"/>
+      <c r="Y44" s="276"/>
+      <c r="Z44" s="276"/>
+      <c r="AA44" s="276"/>
+      <c r="AB44" s="276"/>
+      <c r="AC44" s="279"/>
+      <c r="AD44" s="279"/>
+      <c r="AE44" s="279"/>
+      <c r="AF44" s="279"/>
       <c r="AG44" s="128" t="s">
         <v>50</v>
       </c>
       <c r="AR44" s="3"/>
     </row>
     <row r="45" spans="1:44" s="36" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A45" s="276" t="s">
+      <c r="A45" s="277" t="s">
         <v>221</v>
       </c>
-      <c r="B45" s="277"/>
-      <c r="C45" s="277"/>
-      <c r="D45" s="277"/>
-      <c r="E45" s="277"/>
-      <c r="F45" s="277"/>
-      <c r="G45" s="277"/>
-      <c r="H45" s="277"/>
-      <c r="I45" s="277"/>
-      <c r="J45" s="277"/>
-      <c r="K45" s="277"/>
-      <c r="L45" s="277"/>
-      <c r="M45" s="277"/>
-      <c r="N45" s="277"/>
-      <c r="O45" s="277"/>
-      <c r="P45" s="277"/>
-      <c r="Q45" s="277"/>
-      <c r="R45" s="277"/>
-      <c r="S45" s="277"/>
-      <c r="T45" s="277"/>
-      <c r="U45" s="277"/>
-      <c r="V45" s="277"/>
-      <c r="W45" s="277"/>
-      <c r="X45" s="277"/>
-      <c r="Y45" s="277"/>
-      <c r="Z45" s="277"/>
-      <c r="AA45" s="277"/>
-      <c r="AB45" s="277"/>
-      <c r="AC45" s="279"/>
-      <c r="AD45" s="279"/>
-      <c r="AE45" s="279"/>
-      <c r="AF45" s="279"/>
+      <c r="B45" s="278"/>
+      <c r="C45" s="278"/>
+      <c r="D45" s="278"/>
+      <c r="E45" s="278"/>
+      <c r="F45" s="278"/>
+      <c r="G45" s="278"/>
+      <c r="H45" s="278"/>
+      <c r="I45" s="278"/>
+      <c r="J45" s="278"/>
+      <c r="K45" s="278"/>
+      <c r="L45" s="278"/>
+      <c r="M45" s="278"/>
+      <c r="N45" s="278"/>
+      <c r="O45" s="278"/>
+      <c r="P45" s="278"/>
+      <c r="Q45" s="278"/>
+      <c r="R45" s="278"/>
+      <c r="S45" s="278"/>
+      <c r="T45" s="278"/>
+      <c r="U45" s="278"/>
+      <c r="V45" s="278"/>
+      <c r="W45" s="278"/>
+      <c r="X45" s="278"/>
+      <c r="Y45" s="278"/>
+      <c r="Z45" s="278"/>
+      <c r="AA45" s="278"/>
+      <c r="AB45" s="278"/>
+      <c r="AC45" s="280"/>
+      <c r="AD45" s="280"/>
+      <c r="AE45" s="280"/>
+      <c r="AF45" s="280"/>
       <c r="AG45" s="129" t="s">
         <v>50</v>
       </c>
@@ -11344,41 +11357,41 @@
       <c r="AR46" s="3"/>
     </row>
     <row r="47" spans="1:44" s="36" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A47" s="267" t="s">
+      <c r="A47" s="268" t="s">
         <v>164</v>
       </c>
-      <c r="B47" s="267"/>
-      <c r="C47" s="267"/>
-      <c r="D47" s="267"/>
-      <c r="E47" s="267"/>
-      <c r="F47" s="267"/>
-      <c r="G47" s="267"/>
-      <c r="H47" s="267"/>
-      <c r="I47" s="267"/>
-      <c r="J47" s="267"/>
-      <c r="K47" s="267"/>
-      <c r="L47" s="267"/>
-      <c r="M47" s="267"/>
-      <c r="N47" s="267"/>
-      <c r="O47" s="267"/>
-      <c r="P47" s="267"/>
-      <c r="Q47" s="267"/>
-      <c r="R47" s="267"/>
-      <c r="S47" s="267"/>
-      <c r="T47" s="267"/>
-      <c r="U47" s="267"/>
-      <c r="V47" s="267"/>
-      <c r="W47" s="267"/>
-      <c r="X47" s="267"/>
-      <c r="Y47" s="267"/>
-      <c r="Z47" s="267"/>
-      <c r="AA47" s="267"/>
-      <c r="AB47" s="267"/>
-      <c r="AC47" s="267"/>
-      <c r="AD47" s="267"/>
-      <c r="AE47" s="267"/>
-      <c r="AF47" s="267"/>
-      <c r="AG47" s="267"/>
+      <c r="B47" s="268"/>
+      <c r="C47" s="268"/>
+      <c r="D47" s="268"/>
+      <c r="E47" s="268"/>
+      <c r="F47" s="268"/>
+      <c r="G47" s="268"/>
+      <c r="H47" s="268"/>
+      <c r="I47" s="268"/>
+      <c r="J47" s="268"/>
+      <c r="K47" s="268"/>
+      <c r="L47" s="268"/>
+      <c r="M47" s="268"/>
+      <c r="N47" s="268"/>
+      <c r="O47" s="268"/>
+      <c r="P47" s="268"/>
+      <c r="Q47" s="268"/>
+      <c r="R47" s="268"/>
+      <c r="S47" s="268"/>
+      <c r="T47" s="268"/>
+      <c r="U47" s="268"/>
+      <c r="V47" s="268"/>
+      <c r="W47" s="268"/>
+      <c r="X47" s="268"/>
+      <c r="Y47" s="268"/>
+      <c r="Z47" s="268"/>
+      <c r="AA47" s="268"/>
+      <c r="AB47" s="268"/>
+      <c r="AC47" s="268"/>
+      <c r="AD47" s="268"/>
+      <c r="AE47" s="268"/>
+      <c r="AF47" s="268"/>
+      <c r="AG47" s="268"/>
       <c r="AR47" s="3"/>
     </row>
     <row r="48" spans="1:44" s="36" customFormat="1" ht="15" customHeight="1">
@@ -11412,90 +11425,90 @@
       <c r="Z48" s="13"/>
       <c r="AA48" s="21"/>
       <c r="AB48" s="105"/>
-      <c r="AC48" s="268"/>
-      <c r="AD48" s="268"/>
-      <c r="AE48" s="268"/>
-      <c r="AF48" s="268"/>
+      <c r="AC48" s="269"/>
+      <c r="AD48" s="269"/>
+      <c r="AE48" s="269"/>
+      <c r="AF48" s="269"/>
       <c r="AG48" s="22" t="s">
         <v>37</v>
       </c>
       <c r="AR48" s="3"/>
     </row>
     <row r="49" spans="1:67" s="36" customFormat="1" ht="15" customHeight="1">
-      <c r="A49" s="269" t="s">
+      <c r="A49" s="270" t="s">
         <v>222</v>
       </c>
-      <c r="B49" s="270"/>
-      <c r="C49" s="270"/>
-      <c r="D49" s="270"/>
-      <c r="E49" s="270"/>
-      <c r="F49" s="270"/>
-      <c r="G49" s="270"/>
-      <c r="H49" s="270"/>
-      <c r="I49" s="270"/>
-      <c r="J49" s="270"/>
-      <c r="K49" s="270"/>
-      <c r="L49" s="270"/>
-      <c r="M49" s="270"/>
-      <c r="N49" s="270"/>
-      <c r="O49" s="270"/>
-      <c r="P49" s="270"/>
-      <c r="Q49" s="270"/>
-      <c r="R49" s="270"/>
-      <c r="S49" s="270"/>
-      <c r="T49" s="270"/>
-      <c r="U49" s="270"/>
-      <c r="V49" s="270"/>
-      <c r="W49" s="270"/>
-      <c r="X49" s="270"/>
-      <c r="Y49" s="270"/>
-      <c r="Z49" s="270"/>
-      <c r="AA49" s="270"/>
-      <c r="AB49" s="270"/>
-      <c r="AC49" s="271"/>
-      <c r="AD49" s="271"/>
-      <c r="AE49" s="271"/>
-      <c r="AF49" s="271"/>
+      <c r="B49" s="271"/>
+      <c r="C49" s="271"/>
+      <c r="D49" s="271"/>
+      <c r="E49" s="271"/>
+      <c r="F49" s="271"/>
+      <c r="G49" s="271"/>
+      <c r="H49" s="271"/>
+      <c r="I49" s="271"/>
+      <c r="J49" s="271"/>
+      <c r="K49" s="271"/>
+      <c r="L49" s="271"/>
+      <c r="M49" s="271"/>
+      <c r="N49" s="271"/>
+      <c r="O49" s="271"/>
+      <c r="P49" s="271"/>
+      <c r="Q49" s="271"/>
+      <c r="R49" s="271"/>
+      <c r="S49" s="271"/>
+      <c r="T49" s="271"/>
+      <c r="U49" s="271"/>
+      <c r="V49" s="271"/>
+      <c r="W49" s="271"/>
+      <c r="X49" s="271"/>
+      <c r="Y49" s="271"/>
+      <c r="Z49" s="271"/>
+      <c r="AA49" s="271"/>
+      <c r="AB49" s="271"/>
+      <c r="AC49" s="272"/>
+      <c r="AD49" s="272"/>
+      <c r="AE49" s="272"/>
+      <c r="AF49" s="272"/>
       <c r="AG49" s="28" t="s">
         <v>38</v>
       </c>
       <c r="AR49" s="3"/>
     </row>
     <row r="50" spans="1:67" s="36" customFormat="1" ht="15" customHeight="1">
-      <c r="A50" s="263" t="s">
+      <c r="A50" s="264" t="s">
         <v>223</v>
       </c>
-      <c r="B50" s="264"/>
-      <c r="C50" s="264"/>
-      <c r="D50" s="264"/>
-      <c r="E50" s="264"/>
-      <c r="F50" s="264"/>
-      <c r="G50" s="264"/>
-      <c r="H50" s="264"/>
-      <c r="I50" s="264"/>
-      <c r="J50" s="264"/>
-      <c r="K50" s="264"/>
-      <c r="L50" s="264"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="264"/>
-      <c r="P50" s="264"/>
-      <c r="Q50" s="264"/>
-      <c r="R50" s="264"/>
-      <c r="S50" s="264"/>
-      <c r="T50" s="264"/>
-      <c r="U50" s="264"/>
-      <c r="V50" s="264"/>
-      <c r="W50" s="264"/>
-      <c r="X50" s="264"/>
-      <c r="Y50" s="264"/>
-      <c r="Z50" s="264"/>
-      <c r="AA50" s="264"/>
-      <c r="AB50" s="264"/>
-      <c r="AC50" s="271"/>
-      <c r="AD50" s="271"/>
-      <c r="AE50" s="271"/>
-      <c r="AF50" s="271"/>
+      <c r="B50" s="265"/>
+      <c r="C50" s="265"/>
+      <c r="D50" s="265"/>
+      <c r="E50" s="265"/>
+      <c r="F50" s="265"/>
+      <c r="G50" s="265"/>
+      <c r="H50" s="265"/>
+      <c r="I50" s="265"/>
+      <c r="J50" s="265"/>
+      <c r="K50" s="265"/>
+      <c r="L50" s="265"/>
+      <c r="M50" s="265"/>
+      <c r="N50" s="265"/>
+      <c r="O50" s="265"/>
+      <c r="P50" s="265"/>
+      <c r="Q50" s="265"/>
+      <c r="R50" s="265"/>
+      <c r="S50" s="265"/>
+      <c r="T50" s="265"/>
+      <c r="U50" s="265"/>
+      <c r="V50" s="265"/>
+      <c r="W50" s="265"/>
+      <c r="X50" s="265"/>
+      <c r="Y50" s="265"/>
+      <c r="Z50" s="265"/>
+      <c r="AA50" s="265"/>
+      <c r="AB50" s="265"/>
+      <c r="AC50" s="272"/>
+      <c r="AD50" s="272"/>
+      <c r="AE50" s="272"/>
+      <c r="AF50" s="272"/>
       <c r="AG50" s="33" t="s">
         <v>38</v>
       </c>
@@ -11532,13 +11545,13 @@
       <c r="Z51" s="4"/>
       <c r="AA51" s="4"/>
       <c r="AB51" s="106"/>
-      <c r="AC51" s="272" t="str">
+      <c r="AC51" s="273" t="str">
         <f>IF(AC49-AC50=0,"",AC49-AC50)</f>
         <v/>
       </c>
-      <c r="AD51" s="272"/>
-      <c r="AE51" s="272"/>
-      <c r="AF51" s="272"/>
+      <c r="AD51" s="273"/>
+      <c r="AE51" s="273"/>
+      <c r="AF51" s="273"/>
       <c r="AG51" s="33" t="s">
         <v>38</v>
       </c>
@@ -11575,93 +11588,93 @@
       <c r="Z52" s="125"/>
       <c r="AA52" s="125"/>
       <c r="AB52" s="126"/>
-      <c r="AC52" s="273" t="str">
+      <c r="AC52" s="274" t="str">
         <f>IFERROR((AC51/AC50)*100,"")</f>
         <v/>
       </c>
-      <c r="AD52" s="273"/>
-      <c r="AE52" s="273"/>
-      <c r="AF52" s="273"/>
+      <c r="AD52" s="274"/>
+      <c r="AE52" s="274"/>
+      <c r="AF52" s="274"/>
       <c r="AG52" s="127" t="s">
         <v>49</v>
       </c>
       <c r="AR52" s="3"/>
     </row>
     <row r="53" spans="1:67" s="36" customFormat="1" ht="15" customHeight="1">
-      <c r="A53" s="274" t="s">
+      <c r="A53" s="275" t="s">
         <v>224</v>
       </c>
-      <c r="B53" s="275"/>
-      <c r="C53" s="275"/>
-      <c r="D53" s="275"/>
-      <c r="E53" s="275"/>
-      <c r="F53" s="275"/>
-      <c r="G53" s="275"/>
-      <c r="H53" s="275"/>
-      <c r="I53" s="275"/>
-      <c r="J53" s="275"/>
-      <c r="K53" s="275"/>
-      <c r="L53" s="275"/>
-      <c r="M53" s="275"/>
-      <c r="N53" s="275"/>
-      <c r="O53" s="275"/>
-      <c r="P53" s="275"/>
-      <c r="Q53" s="275"/>
-      <c r="R53" s="275"/>
-      <c r="S53" s="275"/>
-      <c r="T53" s="275"/>
-      <c r="U53" s="275"/>
-      <c r="V53" s="275"/>
-      <c r="W53" s="275"/>
-      <c r="X53" s="275"/>
-      <c r="Y53" s="275"/>
-      <c r="Z53" s="275"/>
-      <c r="AA53" s="275"/>
-      <c r="AB53" s="275"/>
-      <c r="AC53" s="278"/>
-      <c r="AD53" s="278"/>
-      <c r="AE53" s="278"/>
-      <c r="AF53" s="278"/>
+      <c r="B53" s="276"/>
+      <c r="C53" s="276"/>
+      <c r="D53" s="276"/>
+      <c r="E53" s="276"/>
+      <c r="F53" s="276"/>
+      <c r="G53" s="276"/>
+      <c r="H53" s="276"/>
+      <c r="I53" s="276"/>
+      <c r="J53" s="276"/>
+      <c r="K53" s="276"/>
+      <c r="L53" s="276"/>
+      <c r="M53" s="276"/>
+      <c r="N53" s="276"/>
+      <c r="O53" s="276"/>
+      <c r="P53" s="276"/>
+      <c r="Q53" s="276"/>
+      <c r="R53" s="276"/>
+      <c r="S53" s="276"/>
+      <c r="T53" s="276"/>
+      <c r="U53" s="276"/>
+      <c r="V53" s="276"/>
+      <c r="W53" s="276"/>
+      <c r="X53" s="276"/>
+      <c r="Y53" s="276"/>
+      <c r="Z53" s="276"/>
+      <c r="AA53" s="276"/>
+      <c r="AB53" s="276"/>
+      <c r="AC53" s="279"/>
+      <c r="AD53" s="279"/>
+      <c r="AE53" s="279"/>
+      <c r="AF53" s="279"/>
       <c r="AG53" s="128" t="s">
         <v>50</v>
       </c>
       <c r="AR53" s="3"/>
     </row>
     <row r="54" spans="1:67" s="36" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A54" s="276" t="s">
+      <c r="A54" s="277" t="s">
         <v>225</v>
       </c>
-      <c r="B54" s="277"/>
-      <c r="C54" s="277"/>
-      <c r="D54" s="277"/>
-      <c r="E54" s="277"/>
-      <c r="F54" s="277"/>
-      <c r="G54" s="277"/>
-      <c r="H54" s="277"/>
-      <c r="I54" s="277"/>
-      <c r="J54" s="277"/>
-      <c r="K54" s="277"/>
-      <c r="L54" s="277"/>
-      <c r="M54" s="277"/>
-      <c r="N54" s="277"/>
-      <c r="O54" s="277"/>
-      <c r="P54" s="277"/>
-      <c r="Q54" s="277"/>
-      <c r="R54" s="277"/>
-      <c r="S54" s="277"/>
-      <c r="T54" s="277"/>
-      <c r="U54" s="277"/>
-      <c r="V54" s="277"/>
-      <c r="W54" s="277"/>
-      <c r="X54" s="277"/>
-      <c r="Y54" s="277"/>
-      <c r="Z54" s="277"/>
-      <c r="AA54" s="277"/>
-      <c r="AB54" s="277"/>
-      <c r="AC54" s="279"/>
-      <c r="AD54" s="279"/>
-      <c r="AE54" s="279"/>
-      <c r="AF54" s="279"/>
+      <c r="B54" s="278"/>
+      <c r="C54" s="278"/>
+      <c r="D54" s="278"/>
+      <c r="E54" s="278"/>
+      <c r="F54" s="278"/>
+      <c r="G54" s="278"/>
+      <c r="H54" s="278"/>
+      <c r="I54" s="278"/>
+      <c r="J54" s="278"/>
+      <c r="K54" s="278"/>
+      <c r="L54" s="278"/>
+      <c r="M54" s="278"/>
+      <c r="N54" s="278"/>
+      <c r="O54" s="278"/>
+      <c r="P54" s="278"/>
+      <c r="Q54" s="278"/>
+      <c r="R54" s="278"/>
+      <c r="S54" s="278"/>
+      <c r="T54" s="278"/>
+      <c r="U54" s="278"/>
+      <c r="V54" s="278"/>
+      <c r="W54" s="278"/>
+      <c r="X54" s="278"/>
+      <c r="Y54" s="278"/>
+      <c r="Z54" s="278"/>
+      <c r="AA54" s="278"/>
+      <c r="AB54" s="278"/>
+      <c r="AC54" s="280"/>
+      <c r="AD54" s="280"/>
+      <c r="AE54" s="280"/>
+      <c r="AF54" s="280"/>
       <c r="AG54" s="129" t="s">
         <v>50</v>
       </c>
@@ -11704,17 +11717,17 @@
       <c r="AR55" s="3"/>
     </row>
     <row r="56" spans="1:67" s="36" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A56" s="297" t="s">
+      <c r="A56" s="298" t="s">
         <v>317</v>
       </c>
-      <c r="B56" s="297"/>
-      <c r="C56" s="297"/>
-      <c r="D56" s="297"/>
-      <c r="E56" s="297"/>
-      <c r="F56" s="297"/>
-      <c r="G56" s="297"/>
-      <c r="H56" s="297"/>
-      <c r="I56" s="297"/>
+      <c r="B56" s="298"/>
+      <c r="C56" s="298"/>
+      <c r="D56" s="298"/>
+      <c r="E56" s="298"/>
+      <c r="F56" s="298"/>
+      <c r="G56" s="298"/>
+      <c r="H56" s="298"/>
+      <c r="I56" s="298"/>
       <c r="J56" s="148"/>
       <c r="K56" s="148"/>
       <c r="L56" s="148"/>
@@ -11772,93 +11785,93 @@
       <c r="Z57" s="13"/>
       <c r="AA57" s="21"/>
       <c r="AB57" s="105"/>
-      <c r="AC57" s="268"/>
-      <c r="AD57" s="268"/>
-      <c r="AE57" s="268"/>
-      <c r="AF57" s="268"/>
+      <c r="AC57" s="269"/>
+      <c r="AD57" s="269"/>
+      <c r="AE57" s="269"/>
+      <c r="AF57" s="269"/>
       <c r="AG57" s="22" t="s">
         <v>38</v>
       </c>
       <c r="AR57" s="3"/>
     </row>
     <row r="58" spans="1:67" s="36" customFormat="1" ht="15" customHeight="1">
-      <c r="A58" s="269" t="s">
+      <c r="A58" s="270" t="s">
         <v>212</v>
       </c>
-      <c r="B58" s="270"/>
-      <c r="C58" s="270"/>
-      <c r="D58" s="270"/>
-      <c r="E58" s="270"/>
-      <c r="F58" s="270"/>
-      <c r="G58" s="270"/>
-      <c r="H58" s="270"/>
-      <c r="I58" s="270"/>
-      <c r="J58" s="270"/>
-      <c r="K58" s="270"/>
-      <c r="L58" s="270"/>
-      <c r="M58" s="270"/>
-      <c r="N58" s="270"/>
-      <c r="O58" s="270"/>
-      <c r="P58" s="270"/>
-      <c r="Q58" s="270"/>
-      <c r="R58" s="270"/>
-      <c r="S58" s="270"/>
-      <c r="T58" s="270"/>
-      <c r="U58" s="270"/>
-      <c r="V58" s="270"/>
-      <c r="W58" s="270"/>
-      <c r="X58" s="270"/>
-      <c r="Y58" s="270"/>
-      <c r="Z58" s="270"/>
-      <c r="AA58" s="270"/>
-      <c r="AB58" s="270"/>
-      <c r="AC58" s="271"/>
-      <c r="AD58" s="271"/>
-      <c r="AE58" s="271"/>
-      <c r="AF58" s="271"/>
+      <c r="B58" s="271"/>
+      <c r="C58" s="271"/>
+      <c r="D58" s="271"/>
+      <c r="E58" s="271"/>
+      <c r="F58" s="271"/>
+      <c r="G58" s="271"/>
+      <c r="H58" s="271"/>
+      <c r="I58" s="271"/>
+      <c r="J58" s="271"/>
+      <c r="K58" s="271"/>
+      <c r="L58" s="271"/>
+      <c r="M58" s="271"/>
+      <c r="N58" s="271"/>
+      <c r="O58" s="271"/>
+      <c r="P58" s="271"/>
+      <c r="Q58" s="271"/>
+      <c r="R58" s="271"/>
+      <c r="S58" s="271"/>
+      <c r="T58" s="271"/>
+      <c r="U58" s="271"/>
+      <c r="V58" s="271"/>
+      <c r="W58" s="271"/>
+      <c r="X58" s="271"/>
+      <c r="Y58" s="271"/>
+      <c r="Z58" s="271"/>
+      <c r="AA58" s="271"/>
+      <c r="AB58" s="271"/>
+      <c r="AC58" s="272"/>
+      <c r="AD58" s="272"/>
+      <c r="AE58" s="272"/>
+      <c r="AF58" s="272"/>
       <c r="AG58" s="28" t="s">
         <v>38</v>
       </c>
       <c r="AR58" s="3"/>
     </row>
     <row r="59" spans="1:67" s="36" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A59" s="281" t="s">
+      <c r="A59" s="282" t="s">
         <v>315</v>
       </c>
-      <c r="B59" s="282"/>
-      <c r="C59" s="282"/>
-      <c r="D59" s="282"/>
-      <c r="E59" s="282"/>
-      <c r="F59" s="282"/>
-      <c r="G59" s="282"/>
-      <c r="H59" s="282"/>
-      <c r="I59" s="282"/>
-      <c r="J59" s="282"/>
-      <c r="K59" s="282"/>
-      <c r="L59" s="282"/>
-      <c r="M59" s="282"/>
-      <c r="N59" s="282"/>
-      <c r="O59" s="282"/>
-      <c r="P59" s="282"/>
-      <c r="Q59" s="282"/>
-      <c r="R59" s="282"/>
-      <c r="S59" s="282"/>
-      <c r="T59" s="282"/>
-      <c r="U59" s="282"/>
-      <c r="V59" s="282"/>
-      <c r="W59" s="282"/>
-      <c r="X59" s="282"/>
-      <c r="Y59" s="282"/>
-      <c r="Z59" s="282"/>
-      <c r="AA59" s="282"/>
-      <c r="AB59" s="282"/>
-      <c r="AC59" s="280" t="str">
+      <c r="B59" s="283"/>
+      <c r="C59" s="283"/>
+      <c r="D59" s="283"/>
+      <c r="E59" s="283"/>
+      <c r="F59" s="283"/>
+      <c r="G59" s="283"/>
+      <c r="H59" s="283"/>
+      <c r="I59" s="283"/>
+      <c r="J59" s="283"/>
+      <c r="K59" s="283"/>
+      <c r="L59" s="283"/>
+      <c r="M59" s="283"/>
+      <c r="N59" s="283"/>
+      <c r="O59" s="283"/>
+      <c r="P59" s="283"/>
+      <c r="Q59" s="283"/>
+      <c r="R59" s="283"/>
+      <c r="S59" s="283"/>
+      <c r="T59" s="283"/>
+      <c r="U59" s="283"/>
+      <c r="V59" s="283"/>
+      <c r="W59" s="283"/>
+      <c r="X59" s="283"/>
+      <c r="Y59" s="283"/>
+      <c r="Z59" s="283"/>
+      <c r="AA59" s="283"/>
+      <c r="AB59" s="283"/>
+      <c r="AC59" s="281" t="str">
         <f>IFERROR((AC57/AC58)*100,"")</f>
         <v/>
       </c>
-      <c r="AD59" s="280"/>
-      <c r="AE59" s="280"/>
-      <c r="AF59" s="280"/>
+      <c r="AD59" s="281"/>
+      <c r="AE59" s="281"/>
+      <c r="AF59" s="281"/>
       <c r="AG59" s="33" t="s">
         <v>49</v>
       </c>
@@ -11898,41 +11911,41 @@
       <c r="BO59" s="16"/>
     </row>
     <row r="60" spans="1:67" s="36" customFormat="1" ht="15" customHeight="1">
-      <c r="A60" s="288" t="s">
+      <c r="A60" s="289" t="s">
         <v>352</v>
       </c>
-      <c r="B60" s="288"/>
-      <c r="C60" s="288"/>
-      <c r="D60" s="288"/>
-      <c r="E60" s="288"/>
-      <c r="F60" s="288"/>
-      <c r="G60" s="288"/>
-      <c r="H60" s="288"/>
-      <c r="I60" s="288"/>
-      <c r="J60" s="288"/>
-      <c r="K60" s="288"/>
-      <c r="L60" s="288"/>
-      <c r="M60" s="288"/>
-      <c r="N60" s="288"/>
-      <c r="O60" s="288"/>
-      <c r="P60" s="288"/>
-      <c r="Q60" s="288"/>
-      <c r="R60" s="288"/>
-      <c r="S60" s="288"/>
-      <c r="T60" s="288"/>
-      <c r="U60" s="288"/>
-      <c r="V60" s="288"/>
-      <c r="W60" s="288"/>
-      <c r="X60" s="288"/>
-      <c r="Y60" s="288"/>
-      <c r="Z60" s="288"/>
-      <c r="AA60" s="288"/>
-      <c r="AB60" s="288"/>
-      <c r="AC60" s="288"/>
-      <c r="AD60" s="288"/>
-      <c r="AE60" s="288"/>
-      <c r="AF60" s="288"/>
-      <c r="AG60" s="288"/>
+      <c r="B60" s="289"/>
+      <c r="C60" s="289"/>
+      <c r="D60" s="289"/>
+      <c r="E60" s="289"/>
+      <c r="F60" s="289"/>
+      <c r="G60" s="289"/>
+      <c r="H60" s="289"/>
+      <c r="I60" s="289"/>
+      <c r="J60" s="289"/>
+      <c r="K60" s="289"/>
+      <c r="L60" s="289"/>
+      <c r="M60" s="289"/>
+      <c r="N60" s="289"/>
+      <c r="O60" s="289"/>
+      <c r="P60" s="289"/>
+      <c r="Q60" s="289"/>
+      <c r="R60" s="289"/>
+      <c r="S60" s="289"/>
+      <c r="T60" s="289"/>
+      <c r="U60" s="289"/>
+      <c r="V60" s="289"/>
+      <c r="W60" s="289"/>
+      <c r="X60" s="289"/>
+      <c r="Y60" s="289"/>
+      <c r="Z60" s="289"/>
+      <c r="AA60" s="289"/>
+      <c r="AB60" s="289"/>
+      <c r="AC60" s="289"/>
+      <c r="AD60" s="289"/>
+      <c r="AE60" s="289"/>
+      <c r="AF60" s="289"/>
+      <c r="AG60" s="289"/>
       <c r="AH60" s="16"/>
       <c r="AI60" s="140"/>
       <c r="AJ60" s="141"/>
@@ -11944,13 +11957,13 @@
       <c r="AP60" s="141"/>
       <c r="AQ60" s="141"/>
       <c r="AR60" s="141"/>
-      <c r="AS60" s="289"/>
-      <c r="AT60" s="289"/>
-      <c r="AU60" s="289"/>
-      <c r="AV60" s="289"/>
-      <c r="AW60" s="289"/>
-      <c r="AX60" s="289"/>
-      <c r="AY60" s="289"/>
+      <c r="AS60" s="290"/>
+      <c r="AT60" s="290"/>
+      <c r="AU60" s="290"/>
+      <c r="AV60" s="290"/>
+      <c r="AW60" s="290"/>
+      <c r="AX60" s="290"/>
+      <c r="AY60" s="290"/>
       <c r="AZ60" s="141"/>
       <c r="BA60" s="16"/>
       <c r="BB60" s="16"/>
@@ -11970,40 +11983,40 @@
     </row>
     <row r="61" spans="1:67" s="36" customFormat="1" ht="15" customHeight="1">
       <c r="A61" s="151"/>
-      <c r="B61" s="290" t="s">
+      <c r="B61" s="291" t="s">
         <v>176</v>
       </c>
-      <c r="C61" s="290"/>
-      <c r="D61" s="290"/>
-      <c r="E61" s="290"/>
-      <c r="F61" s="290"/>
-      <c r="G61" s="290"/>
-      <c r="H61" s="290"/>
-      <c r="I61" s="290"/>
-      <c r="J61" s="290"/>
-      <c r="K61" s="290"/>
-      <c r="L61" s="290"/>
-      <c r="M61" s="290"/>
-      <c r="N61" s="290"/>
-      <c r="O61" s="290"/>
-      <c r="P61" s="290"/>
-      <c r="Q61" s="290"/>
-      <c r="R61" s="290"/>
-      <c r="S61" s="290"/>
-      <c r="T61" s="290"/>
-      <c r="U61" s="290"/>
-      <c r="V61" s="290"/>
-      <c r="W61" s="290"/>
-      <c r="X61" s="290"/>
-      <c r="Y61" s="290"/>
-      <c r="Z61" s="290"/>
-      <c r="AA61" s="290"/>
-      <c r="AB61" s="290"/>
-      <c r="AC61" s="290"/>
-      <c r="AD61" s="290"/>
-      <c r="AE61" s="290"/>
-      <c r="AF61" s="290"/>
-      <c r="AG61" s="290"/>
+      <c r="C61" s="291"/>
+      <c r="D61" s="291"/>
+      <c r="E61" s="291"/>
+      <c r="F61" s="291"/>
+      <c r="G61" s="291"/>
+      <c r="H61" s="291"/>
+      <c r="I61" s="291"/>
+      <c r="J61" s="291"/>
+      <c r="K61" s="291"/>
+      <c r="L61" s="291"/>
+      <c r="M61" s="291"/>
+      <c r="N61" s="291"/>
+      <c r="O61" s="291"/>
+      <c r="P61" s="291"/>
+      <c r="Q61" s="291"/>
+      <c r="R61" s="291"/>
+      <c r="S61" s="291"/>
+      <c r="T61" s="291"/>
+      <c r="U61" s="291"/>
+      <c r="V61" s="291"/>
+      <c r="W61" s="291"/>
+      <c r="X61" s="291"/>
+      <c r="Y61" s="291"/>
+      <c r="Z61" s="291"/>
+      <c r="AA61" s="291"/>
+      <c r="AB61" s="291"/>
+      <c r="AC61" s="291"/>
+      <c r="AD61" s="291"/>
+      <c r="AE61" s="291"/>
+      <c r="AF61" s="291"/>
+      <c r="AG61" s="291"/>
       <c r="AH61" s="16"/>
       <c r="AI61" s="140"/>
       <c r="AJ61" s="141"/>
@@ -12155,13 +12168,13 @@
       <c r="AP63" s="141"/>
       <c r="AQ63" s="141"/>
       <c r="AR63" s="141"/>
-      <c r="AS63" s="289"/>
-      <c r="AT63" s="289"/>
-      <c r="AU63" s="289"/>
-      <c r="AV63" s="289"/>
-      <c r="AW63" s="289"/>
-      <c r="AX63" s="289"/>
-      <c r="AY63" s="289"/>
+      <c r="AS63" s="290"/>
+      <c r="AT63" s="290"/>
+      <c r="AU63" s="290"/>
+      <c r="AV63" s="290"/>
+      <c r="AW63" s="290"/>
+      <c r="AX63" s="290"/>
+      <c r="AY63" s="290"/>
       <c r="AZ63" s="141"/>
       <c r="BA63" s="16"/>
       <c r="BB63" s="16"/>
@@ -12209,14 +12222,14 @@
       <c r="Y64" s="13"/>
       <c r="Z64" s="13"/>
       <c r="AA64" s="13"/>
-      <c r="AB64" s="296" t="str">
+      <c r="AB64" s="297" t="str">
         <f>IF(AB21=0,"",AB21)</f>
         <v/>
       </c>
-      <c r="AC64" s="296"/>
-      <c r="AD64" s="296"/>
-      <c r="AE64" s="296"/>
-      <c r="AF64" s="296"/>
+      <c r="AC64" s="297"/>
+      <c r="AD64" s="297"/>
+      <c r="AE64" s="297"/>
+      <c r="AF64" s="297"/>
       <c r="AG64" s="14" t="s">
         <v>38</v>
       </c>
@@ -12285,14 +12298,14 @@
       <c r="Y65" s="8"/>
       <c r="Z65" s="8"/>
       <c r="AA65" s="8"/>
-      <c r="AB65" s="286" t="str">
-        <f>IFERROR(AC34*AC59*V18,"")</f>
+      <c r="AB65" s="287" t="str">
+        <f>IFERROR(AC34*(AC59/100)*V18,"")</f>
         <v/>
       </c>
-      <c r="AC65" s="286"/>
-      <c r="AD65" s="286"/>
-      <c r="AE65" s="286"/>
-      <c r="AF65" s="286"/>
+      <c r="AC65" s="287"/>
+      <c r="AD65" s="287"/>
+      <c r="AE65" s="287"/>
+      <c r="AF65" s="287"/>
       <c r="AG65" s="9" t="s">
         <v>38</v>
       </c>
@@ -12307,13 +12320,13 @@
       <c r="AP65" s="141"/>
       <c r="AQ65" s="141"/>
       <c r="AR65" s="141"/>
-      <c r="AS65" s="289"/>
-      <c r="AT65" s="289"/>
-      <c r="AU65" s="289"/>
-      <c r="AV65" s="289"/>
-      <c r="AW65" s="289"/>
-      <c r="AX65" s="289"/>
-      <c r="AY65" s="289"/>
+      <c r="AS65" s="290"/>
+      <c r="AT65" s="290"/>
+      <c r="AU65" s="290"/>
+      <c r="AV65" s="290"/>
+      <c r="AW65" s="290"/>
+      <c r="AX65" s="290"/>
+      <c r="AY65" s="290"/>
       <c r="AZ65" s="141"/>
       <c r="BA65" s="16"/>
       <c r="BB65" s="16"/>
@@ -12361,15 +12374,15 @@
       <c r="Y66" s="184"/>
       <c r="Z66" s="184"/>
       <c r="AA66" s="184"/>
-      <c r="AB66" s="286" t="str">
-        <f>IFERROR(AC36*V18,"")</f>
+      <c r="AB66" s="287" t="str">
+        <f>IF(AC36=0,"",AC36)</f>
         <v/>
       </c>
-      <c r="AC66" s="286"/>
-      <c r="AD66" s="286"/>
-      <c r="AE66" s="286"/>
-      <c r="AF66" s="286"/>
-      <c r="AG66" s="292" t="s">
+      <c r="AC66" s="287"/>
+      <c r="AD66" s="287"/>
+      <c r="AE66" s="287"/>
+      <c r="AF66" s="287"/>
+      <c r="AG66" s="293" t="s">
         <v>38</v>
       </c>
       <c r="AH66" s="185"/>
@@ -12437,12 +12450,12 @@
       <c r="Y67" s="191"/>
       <c r="Z67" s="191"/>
       <c r="AA67" s="191"/>
-      <c r="AB67" s="291"/>
-      <c r="AC67" s="291"/>
-      <c r="AD67" s="291"/>
-      <c r="AE67" s="291"/>
-      <c r="AF67" s="291"/>
-      <c r="AG67" s="293"/>
+      <c r="AB67" s="292"/>
+      <c r="AC67" s="292"/>
+      <c r="AD67" s="292"/>
+      <c r="AE67" s="292"/>
+      <c r="AF67" s="292"/>
+      <c r="AG67" s="294"/>
       <c r="AH67" s="16"/>
       <c r="AI67" s="16"/>
       <c r="AJ67" s="146"/>
@@ -12508,14 +12521,14 @@
       <c r="Y68" s="8"/>
       <c r="Z68" s="8"/>
       <c r="AA68" s="8"/>
-      <c r="AB68" s="286" t="str">
+      <c r="AB68" s="287" t="str">
         <f>IFERROR((AB65+AB66)-AB64,"")</f>
         <v/>
       </c>
-      <c r="AC68" s="286"/>
-      <c r="AD68" s="286"/>
-      <c r="AE68" s="286"/>
-      <c r="AF68" s="286"/>
+      <c r="AC68" s="287"/>
+      <c r="AD68" s="287"/>
+      <c r="AE68" s="287"/>
+      <c r="AF68" s="287"/>
       <c r="AG68" s="9" t="s">
         <v>38</v>
       </c>
@@ -12530,24 +12543,24 @@
       <c r="AP68" s="16"/>
       <c r="AQ68" s="16"/>
       <c r="AR68" s="16"/>
-      <c r="AS68" s="287"/>
-      <c r="AT68" s="287"/>
-      <c r="AU68" s="287"/>
-      <c r="AV68" s="287"/>
-      <c r="AW68" s="287"/>
-      <c r="AX68" s="287"/>
-      <c r="AY68" s="287"/>
+      <c r="AS68" s="288"/>
+      <c r="AT68" s="288"/>
+      <c r="AU68" s="288"/>
+      <c r="AV68" s="288"/>
+      <c r="AW68" s="288"/>
+      <c r="AX68" s="288"/>
+      <c r="AY68" s="288"/>
       <c r="AZ68" s="141"/>
       <c r="BA68" s="16"/>
       <c r="BB68" s="141"/>
       <c r="BC68" s="16"/>
-      <c r="BD68" s="283"/>
-      <c r="BE68" s="283"/>
-      <c r="BF68" s="283"/>
-      <c r="BG68" s="283"/>
-      <c r="BH68" s="283"/>
-      <c r="BI68" s="283"/>
-      <c r="BJ68" s="283"/>
+      <c r="BD68" s="284"/>
+      <c r="BE68" s="284"/>
+      <c r="BF68" s="284"/>
+      <c r="BG68" s="284"/>
+      <c r="BH68" s="284"/>
+      <c r="BI68" s="284"/>
+      <c r="BJ68" s="284"/>
       <c r="BK68" s="145"/>
       <c r="BL68" s="16"/>
       <c r="BM68" s="16"/>
@@ -12584,14 +12597,14 @@
       <c r="Y69" s="25"/>
       <c r="Z69" s="25"/>
       <c r="AA69" s="25"/>
-      <c r="AB69" s="284" t="str">
+      <c r="AB69" s="285" t="str">
         <f>IF(AB68&gt;=0,"賃金改善額充当済み","賃金改善額充当不足")</f>
         <v>賃金改善額充当済み</v>
       </c>
-      <c r="AC69" s="284"/>
-      <c r="AD69" s="284"/>
-      <c r="AE69" s="284"/>
-      <c r="AF69" s="284"/>
+      <c r="AC69" s="285"/>
+      <c r="AD69" s="285"/>
+      <c r="AE69" s="285"/>
+      <c r="AF69" s="285"/>
       <c r="AG69" s="29"/>
       <c r="AH69" s="16"/>
       <c r="AI69" s="16"/>
@@ -12813,24 +12826,24 @@
       <c r="AP72" s="16"/>
       <c r="AQ72" s="16"/>
       <c r="AR72" s="16"/>
-      <c r="AS72" s="287"/>
-      <c r="AT72" s="287"/>
-      <c r="AU72" s="287"/>
-      <c r="AV72" s="287"/>
-      <c r="AW72" s="287"/>
-      <c r="AX72" s="287"/>
-      <c r="AY72" s="287"/>
+      <c r="AS72" s="288"/>
+      <c r="AT72" s="288"/>
+      <c r="AU72" s="288"/>
+      <c r="AV72" s="288"/>
+      <c r="AW72" s="288"/>
+      <c r="AX72" s="288"/>
+      <c r="AY72" s="288"/>
       <c r="AZ72" s="141"/>
       <c r="BA72" s="16"/>
       <c r="BB72" s="141"/>
       <c r="BC72" s="16"/>
-      <c r="BD72" s="283"/>
-      <c r="BE72" s="283"/>
-      <c r="BF72" s="283"/>
-      <c r="BG72" s="283"/>
-      <c r="BH72" s="283"/>
-      <c r="BI72" s="283"/>
-      <c r="BJ72" s="283"/>
+      <c r="BD72" s="284"/>
+      <c r="BE72" s="284"/>
+      <c r="BF72" s="284"/>
+      <c r="BG72" s="284"/>
+      <c r="BH72" s="284"/>
+      <c r="BI72" s="284"/>
+      <c r="BJ72" s="284"/>
       <c r="BK72" s="145"/>
       <c r="BL72" s="16"/>
       <c r="BM72" s="16"/>
@@ -12845,18 +12858,18 @@
         <v>16</v>
       </c>
       <c r="E73" s="2"/>
-      <c r="F73" s="233"/>
-      <c r="G73" s="233"/>
+      <c r="F73" s="234"/>
+      <c r="G73" s="234"/>
       <c r="H73" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I73" s="233"/>
-      <c r="J73" s="233"/>
+      <c r="I73" s="234"/>
+      <c r="J73" s="234"/>
       <c r="K73" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="L73" s="233"/>
-      <c r="M73" s="233"/>
+      <c r="L73" s="234"/>
+      <c r="M73" s="234"/>
       <c r="N73" s="2" t="s">
         <v>19</v>
       </c>
@@ -12868,18 +12881,18 @@
       <c r="R73" s="2"/>
       <c r="S73" s="2"/>
       <c r="T73" s="2"/>
-      <c r="U73" s="285"/>
-      <c r="V73" s="285"/>
-      <c r="W73" s="285"/>
-      <c r="X73" s="285"/>
-      <c r="Y73" s="285"/>
-      <c r="Z73" s="285"/>
-      <c r="AA73" s="285"/>
-      <c r="AB73" s="285"/>
-      <c r="AC73" s="285"/>
-      <c r="AD73" s="285"/>
-      <c r="AE73" s="285"/>
-      <c r="AF73" s="285"/>
+      <c r="U73" s="286"/>
+      <c r="V73" s="286"/>
+      <c r="W73" s="286"/>
+      <c r="X73" s="286"/>
+      <c r="Y73" s="286"/>
+      <c r="Z73" s="286"/>
+      <c r="AA73" s="286"/>
+      <c r="AB73" s="286"/>
+      <c r="AC73" s="286"/>
+      <c r="AD73" s="286"/>
+      <c r="AE73" s="286"/>
+      <c r="AF73" s="286"/>
       <c r="AG73" s="2"/>
       <c r="AH73" s="140"/>
       <c r="AI73" s="16"/>
@@ -14237,7 +14250,7 @@
       <c r="AG108" s="23"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="icN5TEJJObrClDH4ooTbmneMj8umWVcso9fqzWyv6sQ3Jksf7zbRKyq1w5NcL3RTQ+6izM5URMzBqhlCU5a8QA==" saltValue="KAUW7e0jUHSWj8pORd8kLg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="z55u6KWEWY8uRUoAXRwYOyzYoVneMAZ0uppNnjOMTM7eOfeQc9K1+kcCuUNvZKkbNY1MBGQKUvLlmBJ0mFj9QA==" saltValue="F6ZYdMMf6xPabIqvR2zL+A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="81">
     <mergeCell ref="AB66:AF67"/>
     <mergeCell ref="AG66:AG67"/>
@@ -14470,34 +14483,34 @@
       </c>
       <c r="K2" s="202"/>
       <c r="L2" s="202"/>
-      <c r="M2" s="238" t="str">
+      <c r="M2" s="239" t="str">
         <f>IF(AH11=TRUE,C11,IF(AH12=TRUE,C12,""))</f>
         <v/>
       </c>
-      <c r="N2" s="238"/>
-      <c r="O2" s="238"/>
-      <c r="P2" s="238"/>
-      <c r="Q2" s="238"/>
-      <c r="R2" s="238"/>
+      <c r="N2" s="239"/>
+      <c r="O2" s="239"/>
+      <c r="P2" s="239"/>
+      <c r="Q2" s="239"/>
+      <c r="R2" s="239"/>
       <c r="S2" s="32" t="s">
         <v>356</v>
       </c>
       <c r="T2" s="202"/>
-      <c r="U2" s="241"/>
-      <c r="V2" s="241"/>
-      <c r="W2" s="242" t="s">
+      <c r="U2" s="242"/>
+      <c r="V2" s="242"/>
+      <c r="W2" s="243" t="s">
         <v>40</v>
       </c>
-      <c r="X2" s="242"/>
-      <c r="Y2" s="242"/>
-      <c r="Z2" s="242"/>
-      <c r="AA2" s="242"/>
-      <c r="AB2" s="242"/>
-      <c r="AC2" s="242"/>
-      <c r="AD2" s="242"/>
-      <c r="AE2" s="242"/>
-      <c r="AF2" s="242"/>
-      <c r="AG2" s="242"/>
+      <c r="X2" s="243"/>
+      <c r="Y2" s="243"/>
+      <c r="Z2" s="243"/>
+      <c r="AA2" s="243"/>
+      <c r="AB2" s="243"/>
+      <c r="AC2" s="243"/>
+      <c r="AD2" s="243"/>
+      <c r="AE2" s="243"/>
+      <c r="AF2" s="243"/>
+      <c r="AG2" s="243"/>
     </row>
     <row r="3" spans="1:67" ht="7.15" customHeight="1">
       <c r="A3" s="2"/>
@@ -14553,26 +14566,26 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
-      <c r="S4" s="243" t="s">
+      <c r="S4" s="244" t="s">
         <v>160</v>
       </c>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="243"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="244" t="str">
+      <c r="T4" s="244"/>
+      <c r="U4" s="244"/>
+      <c r="V4" s="244"/>
+      <c r="W4" s="244"/>
+      <c r="X4" s="245" t="str">
         <f>IF(別添2!E6="","",別添2!E6)</f>
         <v/>
       </c>
-      <c r="Y4" s="245"/>
-      <c r="Z4" s="245"/>
-      <c r="AA4" s="245"/>
-      <c r="AB4" s="245"/>
-      <c r="AC4" s="245"/>
-      <c r="AD4" s="245"/>
-      <c r="AE4" s="245"/>
-      <c r="AF4" s="245"/>
-      <c r="AG4" s="246"/>
+      <c r="Y4" s="246"/>
+      <c r="Z4" s="246"/>
+      <c r="AA4" s="246"/>
+      <c r="AB4" s="246"/>
+      <c r="AC4" s="246"/>
+      <c r="AD4" s="246"/>
+      <c r="AE4" s="246"/>
+      <c r="AF4" s="246"/>
+      <c r="AG4" s="247"/>
     </row>
     <row r="5" spans="1:67" ht="16.149999999999999" customHeight="1">
       <c r="A5" s="2"/>
@@ -14593,26 +14606,26 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
-      <c r="S5" s="247" t="s">
+      <c r="S5" s="248" t="s">
         <v>161</v>
       </c>
-      <c r="T5" s="247"/>
-      <c r="U5" s="247"/>
-      <c r="V5" s="247"/>
-      <c r="W5" s="248"/>
-      <c r="X5" s="249" t="str">
+      <c r="T5" s="248"/>
+      <c r="U5" s="248"/>
+      <c r="V5" s="248"/>
+      <c r="W5" s="249"/>
+      <c r="X5" s="250" t="str">
         <f>IF(別添2!H28="","",別添2!H28)</f>
         <v/>
       </c>
-      <c r="Y5" s="250"/>
-      <c r="Z5" s="250"/>
-      <c r="AA5" s="250"/>
-      <c r="AB5" s="250"/>
-      <c r="AC5" s="250"/>
-      <c r="AD5" s="250"/>
-      <c r="AE5" s="250"/>
-      <c r="AF5" s="250"/>
-      <c r="AG5" s="251"/>
+      <c r="Y5" s="251"/>
+      <c r="Z5" s="251"/>
+      <c r="AA5" s="251"/>
+      <c r="AB5" s="251"/>
+      <c r="AC5" s="251"/>
+      <c r="AD5" s="251"/>
+      <c r="AE5" s="251"/>
+      <c r="AF5" s="251"/>
+      <c r="AG5" s="252"/>
     </row>
     <row r="6" spans="1:67" ht="16.149999999999999" customHeight="1">
       <c r="A6" s="17"/>
@@ -14632,24 +14645,24 @@
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
       <c r="Q6" s="17"/>
-      <c r="R6" s="298" t="s">
+      <c r="R6" s="299" t="s">
         <v>187</v>
       </c>
-      <c r="S6" s="298"/>
-      <c r="T6" s="298"/>
-      <c r="U6" s="298"/>
-      <c r="V6" s="298"/>
-      <c r="W6" s="299"/>
-      <c r="X6" s="300"/>
-      <c r="Y6" s="301"/>
-      <c r="Z6" s="301"/>
-      <c r="AA6" s="301"/>
-      <c r="AB6" s="301"/>
-      <c r="AC6" s="301"/>
-      <c r="AD6" s="301"/>
-      <c r="AE6" s="301"/>
-      <c r="AF6" s="301"/>
-      <c r="AG6" s="302"/>
+      <c r="S6" s="299"/>
+      <c r="T6" s="299"/>
+      <c r="U6" s="299"/>
+      <c r="V6" s="299"/>
+      <c r="W6" s="300"/>
+      <c r="X6" s="301"/>
+      <c r="Y6" s="302"/>
+      <c r="Z6" s="302"/>
+      <c r="AA6" s="302"/>
+      <c r="AB6" s="302"/>
+      <c r="AC6" s="302"/>
+      <c r="AD6" s="302"/>
+      <c r="AE6" s="302"/>
+      <c r="AF6" s="302"/>
+      <c r="AG6" s="303"/>
       <c r="AH6" s="157"/>
       <c r="AI6" s="157"/>
       <c r="AJ6" s="157"/>
@@ -14703,24 +14716,24 @@
       <c r="O7" s="17"/>
       <c r="P7" s="17"/>
       <c r="Q7" s="17"/>
-      <c r="R7" s="298" t="s">
+      <c r="R7" s="299" t="s">
         <v>180</v>
       </c>
-      <c r="S7" s="298"/>
-      <c r="T7" s="298"/>
-      <c r="U7" s="298"/>
-      <c r="V7" s="298"/>
-      <c r="W7" s="299"/>
-      <c r="X7" s="300"/>
-      <c r="Y7" s="301"/>
-      <c r="Z7" s="301"/>
-      <c r="AA7" s="301"/>
-      <c r="AB7" s="301"/>
-      <c r="AC7" s="301"/>
-      <c r="AD7" s="301"/>
-      <c r="AE7" s="301"/>
-      <c r="AF7" s="301"/>
-      <c r="AG7" s="302"/>
+      <c r="S7" s="299"/>
+      <c r="T7" s="299"/>
+      <c r="U7" s="299"/>
+      <c r="V7" s="299"/>
+      <c r="W7" s="300"/>
+      <c r="X7" s="301"/>
+      <c r="Y7" s="302"/>
+      <c r="Z7" s="302"/>
+      <c r="AA7" s="302"/>
+      <c r="AB7" s="302"/>
+      <c r="AC7" s="302"/>
+      <c r="AD7" s="302"/>
+      <c r="AE7" s="302"/>
+      <c r="AF7" s="302"/>
+      <c r="AG7" s="303"/>
       <c r="AH7" s="157"/>
       <c r="AI7" s="157"/>
       <c r="AJ7" s="157"/>
@@ -14787,7 +14800,10 @@
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+      <c r="G9" s="203" t="str">
+        <f>IF($AH$11=$AH$12,"※どちらか１つを選択してください。","")</f>
+        <v>※どちらか１つを選択してください。</v>
+      </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -14963,18 +14979,18 @@
       <c r="AG16" s="2"/>
     </row>
     <row r="17" spans="1:62" ht="16.149999999999999" customHeight="1" thickBot="1">
-      <c r="B17" s="254" t="s">
+      <c r="B17" s="255" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="255"/>
-      <c r="D17" s="255"/>
-      <c r="E17" s="239"/>
-      <c r="F17" s="239"/>
+      <c r="C17" s="256"/>
+      <c r="D17" s="256"/>
+      <c r="E17" s="240"/>
+      <c r="F17" s="240"/>
       <c r="G17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="239"/>
-      <c r="I17" s="239"/>
+      <c r="H17" s="240"/>
+      <c r="I17" s="240"/>
       <c r="J17" s="5" t="s">
         <v>30</v>
       </c>
@@ -14986,23 +15002,23 @@
         <v>16</v>
       </c>
       <c r="N17" s="5"/>
-      <c r="O17" s="239"/>
-      <c r="P17" s="239"/>
+      <c r="O17" s="240"/>
+      <c r="P17" s="240"/>
       <c r="Q17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R17" s="239"/>
-      <c r="S17" s="239"/>
+      <c r="R17" s="240"/>
+      <c r="S17" s="240"/>
       <c r="T17" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="V17" s="252" t="str">
-        <f>IF(OR(E17="",H17="",O17="",R17=""),"",((O17-E17)*12)+(R17-H17))</f>
+      <c r="V17" s="253" t="str">
+        <f>IF(OR(E17="",H17="",O17="",R17=""),"",((O17-E17)*12)+(R17-H17)+1)</f>
         <v/>
       </c>
-      <c r="W17" s="252"/>
-      <c r="X17" s="252"/>
-      <c r="Y17" s="253"/>
+      <c r="W17" s="253"/>
+      <c r="X17" s="253"/>
+      <c r="Y17" s="254"/>
       <c r="Z17" s="2" t="s">
         <v>46</v>
       </c>
@@ -15076,18 +15092,18 @@
     </row>
     <row r="20" spans="1:62" ht="16.149999999999999" customHeight="1" thickBot="1">
       <c r="A20" s="2"/>
-      <c r="B20" s="254" t="s">
+      <c r="B20" s="255" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="255"/>
-      <c r="D20" s="255"/>
-      <c r="E20" s="239"/>
-      <c r="F20" s="239"/>
+      <c r="C20" s="256"/>
+      <c r="D20" s="256"/>
+      <c r="E20" s="240"/>
+      <c r="F20" s="240"/>
       <c r="G20" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H20" s="239"/>
-      <c r="I20" s="239"/>
+      <c r="H20" s="240"/>
+      <c r="I20" s="240"/>
       <c r="J20" s="5" t="s">
         <v>30</v>
       </c>
@@ -15099,23 +15115,23 @@
         <v>16</v>
       </c>
       <c r="N20" s="5"/>
-      <c r="O20" s="239"/>
-      <c r="P20" s="239"/>
+      <c r="O20" s="240"/>
+      <c r="P20" s="240"/>
       <c r="Q20" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R20" s="239"/>
-      <c r="S20" s="239"/>
+      <c r="R20" s="240"/>
+      <c r="S20" s="240"/>
       <c r="T20" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="V20" s="252" t="str">
-        <f>IF(OR(E20="",H20="",O20="",R20=""),"",((O20-E20)*12)+(R20-H20))</f>
+      <c r="V20" s="253" t="str">
+        <f>IF(OR(E20="",H20="",O20="",R20=""),"",((O20-E20)*12)+(R20-H20)+1)</f>
         <v/>
       </c>
-      <c r="W20" s="252"/>
-      <c r="X20" s="252"/>
-      <c r="Y20" s="253"/>
+      <c r="W20" s="253"/>
+      <c r="X20" s="253"/>
+      <c r="Y20" s="254"/>
       <c r="Z20" s="2" t="s">
         <v>46</v>
       </c>
@@ -15180,12 +15196,12 @@
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
-      <c r="T22" s="266"/>
-      <c r="U22" s="266"/>
-      <c r="V22" s="266"/>
-      <c r="W22" s="266"/>
-      <c r="X22" s="266"/>
-      <c r="Y22" s="266"/>
+      <c r="T22" s="267"/>
+      <c r="U22" s="267"/>
+      <c r="V22" s="267"/>
+      <c r="W22" s="267"/>
+      <c r="X22" s="267"/>
+      <c r="Y22" s="267"/>
       <c r="Z22" s="2"/>
       <c r="AA22" s="2"/>
       <c r="AB22" s="2"/>
@@ -15225,11 +15241,11 @@
       <c r="Y23" s="13"/>
       <c r="Z23" s="13"/>
       <c r="AA23" s="13"/>
-      <c r="AB23" s="303"/>
-      <c r="AC23" s="303"/>
-      <c r="AD23" s="303"/>
-      <c r="AE23" s="303"/>
-      <c r="AF23" s="303"/>
+      <c r="AB23" s="304"/>
+      <c r="AC23" s="304"/>
+      <c r="AD23" s="304"/>
+      <c r="AE23" s="304"/>
+      <c r="AF23" s="304"/>
       <c r="AG23" s="14" t="s">
         <v>38</v>
       </c>
@@ -15434,34 +15450,34 @@
       <c r="AE28" s="165"/>
       <c r="AF28" s="2"/>
       <c r="AG28" s="3"/>
-      <c r="AI28" s="294"/>
-      <c r="AJ28" s="294"/>
-      <c r="AK28" s="294"/>
-      <c r="AL28" s="294"/>
-      <c r="AM28" s="294"/>
-      <c r="AN28" s="294"/>
-      <c r="AO28" s="294"/>
-      <c r="AP28" s="294"/>
-      <c r="AQ28" s="294"/>
-      <c r="AR28" s="294"/>
-      <c r="AS28" s="294"/>
-      <c r="AT28" s="294"/>
-      <c r="AU28" s="294"/>
-      <c r="AV28" s="294"/>
-      <c r="AW28" s="294"/>
-      <c r="AX28" s="294"/>
-      <c r="AY28" s="294"/>
-      <c r="AZ28" s="294"/>
-      <c r="BA28" s="294"/>
-      <c r="BB28" s="294"/>
-      <c r="BC28" s="294"/>
-      <c r="BD28" s="294"/>
-      <c r="BE28" s="294"/>
-      <c r="BF28" s="294"/>
-      <c r="BG28" s="294"/>
-      <c r="BH28" s="294"/>
-      <c r="BI28" s="294"/>
-      <c r="BJ28" s="294"/>
+      <c r="AI28" s="295"/>
+      <c r="AJ28" s="295"/>
+      <c r="AK28" s="295"/>
+      <c r="AL28" s="295"/>
+      <c r="AM28" s="295"/>
+      <c r="AN28" s="295"/>
+      <c r="AO28" s="295"/>
+      <c r="AP28" s="295"/>
+      <c r="AQ28" s="295"/>
+      <c r="AR28" s="295"/>
+      <c r="AS28" s="295"/>
+      <c r="AT28" s="295"/>
+      <c r="AU28" s="295"/>
+      <c r="AV28" s="295"/>
+      <c r="AW28" s="295"/>
+      <c r="AX28" s="295"/>
+      <c r="AY28" s="295"/>
+      <c r="AZ28" s="295"/>
+      <c r="BA28" s="295"/>
+      <c r="BB28" s="295"/>
+      <c r="BC28" s="295"/>
+      <c r="BD28" s="295"/>
+      <c r="BE28" s="295"/>
+      <c r="BF28" s="295"/>
+      <c r="BG28" s="295"/>
+      <c r="BH28" s="295"/>
+      <c r="BI28" s="295"/>
+      <c r="BJ28" s="295"/>
     </row>
     <row r="29" spans="1:62" s="36" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="108" t="s">
@@ -15501,34 +15517,34 @@
       <c r="AE29" s="165"/>
       <c r="AF29" s="2"/>
       <c r="AG29" s="3"/>
-      <c r="AI29" s="295"/>
-      <c r="AJ29" s="295"/>
-      <c r="AK29" s="295"/>
-      <c r="AL29" s="295"/>
-      <c r="AM29" s="295"/>
-      <c r="AN29" s="295"/>
-      <c r="AO29" s="295"/>
-      <c r="AP29" s="295"/>
-      <c r="AQ29" s="295"/>
-      <c r="AR29" s="295"/>
-      <c r="AS29" s="295"/>
-      <c r="AT29" s="295"/>
-      <c r="AU29" s="295"/>
-      <c r="AV29" s="295"/>
-      <c r="AW29" s="295"/>
-      <c r="AX29" s="295"/>
-      <c r="AY29" s="295"/>
-      <c r="AZ29" s="295"/>
-      <c r="BA29" s="295"/>
-      <c r="BB29" s="295"/>
-      <c r="BC29" s="295"/>
-      <c r="BD29" s="295"/>
-      <c r="BE29" s="295"/>
-      <c r="BF29" s="295"/>
-      <c r="BG29" s="295"/>
-      <c r="BH29" s="295"/>
-      <c r="BI29" s="295"/>
-      <c r="BJ29" s="295"/>
+      <c r="AI29" s="296"/>
+      <c r="AJ29" s="296"/>
+      <c r="AK29" s="296"/>
+      <c r="AL29" s="296"/>
+      <c r="AM29" s="296"/>
+      <c r="AN29" s="296"/>
+      <c r="AO29" s="296"/>
+      <c r="AP29" s="296"/>
+      <c r="AQ29" s="296"/>
+      <c r="AR29" s="296"/>
+      <c r="AS29" s="296"/>
+      <c r="AT29" s="296"/>
+      <c r="AU29" s="296"/>
+      <c r="AV29" s="296"/>
+      <c r="AW29" s="296"/>
+      <c r="AX29" s="296"/>
+      <c r="AY29" s="296"/>
+      <c r="AZ29" s="296"/>
+      <c r="BA29" s="296"/>
+      <c r="BB29" s="296"/>
+      <c r="BC29" s="296"/>
+      <c r="BD29" s="296"/>
+      <c r="BE29" s="296"/>
+      <c r="BF29" s="296"/>
+      <c r="BG29" s="296"/>
+      <c r="BH29" s="296"/>
+      <c r="BI29" s="296"/>
+      <c r="BJ29" s="296"/>
     </row>
     <row r="30" spans="1:62" s="36" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="31"/>
@@ -15693,34 +15709,34 @@
       <c r="AE32" s="32"/>
       <c r="AF32" s="32"/>
       <c r="AG32" s="32"/>
-      <c r="AI32" s="290"/>
-      <c r="AJ32" s="290"/>
-      <c r="AK32" s="290"/>
-      <c r="AL32" s="290"/>
-      <c r="AM32" s="290"/>
-      <c r="AN32" s="290"/>
-      <c r="AO32" s="290"/>
-      <c r="AP32" s="290"/>
-      <c r="AQ32" s="290"/>
-      <c r="AR32" s="290"/>
-      <c r="AS32" s="290"/>
-      <c r="AT32" s="290"/>
-      <c r="AU32" s="290"/>
-      <c r="AV32" s="290"/>
-      <c r="AW32" s="290"/>
-      <c r="AX32" s="290"/>
-      <c r="AY32" s="290"/>
-      <c r="AZ32" s="290"/>
-      <c r="BA32" s="290"/>
-      <c r="BB32" s="290"/>
-      <c r="BC32" s="290"/>
-      <c r="BD32" s="290"/>
-      <c r="BE32" s="290"/>
-      <c r="BF32" s="290"/>
-      <c r="BG32" s="290"/>
-      <c r="BH32" s="290"/>
-      <c r="BI32" s="290"/>
-      <c r="BJ32" s="290"/>
+      <c r="AI32" s="291"/>
+      <c r="AJ32" s="291"/>
+      <c r="AK32" s="291"/>
+      <c r="AL32" s="291"/>
+      <c r="AM32" s="291"/>
+      <c r="AN32" s="291"/>
+      <c r="AO32" s="291"/>
+      <c r="AP32" s="291"/>
+      <c r="AQ32" s="291"/>
+      <c r="AR32" s="291"/>
+      <c r="AS32" s="291"/>
+      <c r="AT32" s="291"/>
+      <c r="AU32" s="291"/>
+      <c r="AV32" s="291"/>
+      <c r="AW32" s="291"/>
+      <c r="AX32" s="291"/>
+      <c r="AY32" s="291"/>
+      <c r="AZ32" s="291"/>
+      <c r="BA32" s="291"/>
+      <c r="BB32" s="291"/>
+      <c r="BC32" s="291"/>
+      <c r="BD32" s="291"/>
+      <c r="BE32" s="291"/>
+      <c r="BF32" s="291"/>
+      <c r="BG32" s="291"/>
+      <c r="BH32" s="291"/>
+      <c r="BI32" s="291"/>
+      <c r="BJ32" s="291"/>
     </row>
     <row r="33" spans="1:44" s="36" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="26" t="s">
@@ -15753,13 +15769,13 @@
       <c r="Z33" s="13"/>
       <c r="AA33" s="21"/>
       <c r="AB33" s="105"/>
-      <c r="AC33" s="261" t="str">
+      <c r="AC33" s="262" t="str">
         <f>IF(AC41+AC50=0,"",AC41+AC50)</f>
         <v/>
       </c>
-      <c r="AD33" s="261"/>
-      <c r="AE33" s="261"/>
-      <c r="AF33" s="261"/>
+      <c r="AD33" s="262"/>
+      <c r="AE33" s="262"/>
+      <c r="AF33" s="262"/>
       <c r="AG33" s="22" t="s">
         <v>37</v>
       </c>
@@ -15796,56 +15812,56 @@
       <c r="Z34" s="194"/>
       <c r="AA34" s="195"/>
       <c r="AB34" s="195"/>
-      <c r="AC34" s="262" t="str">
+      <c r="AC34" s="263" t="str">
         <f>IF(AC42+AC51=0,"",AC42+AC51)</f>
         <v/>
       </c>
-      <c r="AD34" s="262"/>
-      <c r="AE34" s="262"/>
-      <c r="AF34" s="262"/>
+      <c r="AD34" s="263"/>
+      <c r="AE34" s="263"/>
+      <c r="AF34" s="263"/>
       <c r="AG34" s="196" t="s">
         <v>38</v>
       </c>
       <c r="AR34" s="100"/>
     </row>
     <row r="35" spans="1:44" s="36" customFormat="1" ht="15" customHeight="1">
-      <c r="A35" s="263" t="s">
+      <c r="A35" s="264" t="s">
         <v>217</v>
       </c>
-      <c r="B35" s="264"/>
-      <c r="C35" s="264"/>
-      <c r="D35" s="264"/>
-      <c r="E35" s="264"/>
-      <c r="F35" s="264"/>
-      <c r="G35" s="264"/>
-      <c r="H35" s="264"/>
-      <c r="I35" s="264"/>
-      <c r="J35" s="264"/>
-      <c r="K35" s="264"/>
-      <c r="L35" s="264"/>
-      <c r="M35" s="264"/>
-      <c r="N35" s="264"/>
-      <c r="O35" s="264"/>
-      <c r="P35" s="264"/>
-      <c r="Q35" s="264"/>
-      <c r="R35" s="264"/>
-      <c r="S35" s="264"/>
-      <c r="T35" s="264"/>
-      <c r="U35" s="264"/>
-      <c r="V35" s="264"/>
-      <c r="W35" s="264"/>
-      <c r="X35" s="264"/>
-      <c r="Y35" s="264"/>
-      <c r="Z35" s="264"/>
-      <c r="AA35" s="264"/>
-      <c r="AB35" s="264"/>
-      <c r="AC35" s="265" t="str">
+      <c r="B35" s="265"/>
+      <c r="C35" s="265"/>
+      <c r="D35" s="265"/>
+      <c r="E35" s="265"/>
+      <c r="F35" s="265"/>
+      <c r="G35" s="265"/>
+      <c r="H35" s="265"/>
+      <c r="I35" s="265"/>
+      <c r="J35" s="265"/>
+      <c r="K35" s="265"/>
+      <c r="L35" s="265"/>
+      <c r="M35" s="265"/>
+      <c r="N35" s="265"/>
+      <c r="O35" s="265"/>
+      <c r="P35" s="265"/>
+      <c r="Q35" s="265"/>
+      <c r="R35" s="265"/>
+      <c r="S35" s="265"/>
+      <c r="T35" s="265"/>
+      <c r="U35" s="265"/>
+      <c r="V35" s="265"/>
+      <c r="W35" s="265"/>
+      <c r="X35" s="265"/>
+      <c r="Y35" s="265"/>
+      <c r="Z35" s="265"/>
+      <c r="AA35" s="265"/>
+      <c r="AB35" s="265"/>
+      <c r="AC35" s="266" t="str">
         <f>IF(AC43+AC52=0,"",AC43+AC52)</f>
         <v/>
       </c>
-      <c r="AD35" s="265"/>
-      <c r="AE35" s="265"/>
-      <c r="AF35" s="265"/>
+      <c r="AD35" s="266"/>
+      <c r="AE35" s="266"/>
+      <c r="AF35" s="266"/>
       <c r="AG35" s="33" t="s">
         <v>38</v>
       </c>
@@ -15882,13 +15898,13 @@
       <c r="Z36" s="8"/>
       <c r="AA36" s="8"/>
       <c r="AB36" s="120"/>
-      <c r="AC36" s="256" t="str">
+      <c r="AC36" s="257" t="str">
         <f>IFERROR(AC34-AC35,"")</f>
         <v/>
       </c>
-      <c r="AD36" s="256"/>
-      <c r="AE36" s="256"/>
-      <c r="AF36" s="256"/>
+      <c r="AD36" s="257"/>
+      <c r="AE36" s="257"/>
+      <c r="AF36" s="257"/>
       <c r="AG36" s="121" t="s">
         <v>38</v>
       </c>
@@ -15925,53 +15941,53 @@
       <c r="Z37" s="198"/>
       <c r="AA37" s="198"/>
       <c r="AB37" s="199"/>
-      <c r="AC37" s="304" t="str">
+      <c r="AC37" s="305" t="str">
         <f>IFERROR((AC36/AC35)*100,"")</f>
         <v/>
       </c>
-      <c r="AD37" s="304"/>
-      <c r="AE37" s="304"/>
-      <c r="AF37" s="304"/>
+      <c r="AD37" s="305"/>
+      <c r="AE37" s="305"/>
+      <c r="AF37" s="305"/>
       <c r="AG37" s="200" t="s">
         <v>49</v>
       </c>
       <c r="AR37" s="3"/>
     </row>
     <row r="38" spans="1:44" s="36" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A38" s="258" t="s">
+      <c r="A38" s="259" t="s">
         <v>174</v>
       </c>
-      <c r="B38" s="259"/>
-      <c r="C38" s="259"/>
-      <c r="D38" s="259"/>
-      <c r="E38" s="259"/>
-      <c r="F38" s="259"/>
-      <c r="G38" s="259"/>
-      <c r="H38" s="259"/>
-      <c r="I38" s="259"/>
-      <c r="J38" s="259"/>
-      <c r="K38" s="259"/>
-      <c r="L38" s="259"/>
-      <c r="M38" s="259"/>
-      <c r="N38" s="259"/>
-      <c r="O38" s="259"/>
-      <c r="P38" s="259"/>
-      <c r="Q38" s="259"/>
-      <c r="R38" s="259"/>
-      <c r="S38" s="259"/>
-      <c r="T38" s="259"/>
-      <c r="U38" s="259"/>
-      <c r="V38" s="259"/>
-      <c r="W38" s="259"/>
-      <c r="X38" s="259"/>
-      <c r="Y38" s="259"/>
-      <c r="Z38" s="259"/>
-      <c r="AA38" s="259"/>
-      <c r="AB38" s="259"/>
-      <c r="AC38" s="260"/>
-      <c r="AD38" s="260"/>
-      <c r="AE38" s="260"/>
-      <c r="AF38" s="260"/>
+      <c r="B38" s="260"/>
+      <c r="C38" s="260"/>
+      <c r="D38" s="260"/>
+      <c r="E38" s="260"/>
+      <c r="F38" s="260"/>
+      <c r="G38" s="260"/>
+      <c r="H38" s="260"/>
+      <c r="I38" s="260"/>
+      <c r="J38" s="260"/>
+      <c r="K38" s="260"/>
+      <c r="L38" s="260"/>
+      <c r="M38" s="260"/>
+      <c r="N38" s="260"/>
+      <c r="O38" s="260"/>
+      <c r="P38" s="260"/>
+      <c r="Q38" s="260"/>
+      <c r="R38" s="260"/>
+      <c r="S38" s="260"/>
+      <c r="T38" s="260"/>
+      <c r="U38" s="260"/>
+      <c r="V38" s="260"/>
+      <c r="W38" s="260"/>
+      <c r="X38" s="260"/>
+      <c r="Y38" s="260"/>
+      <c r="Z38" s="260"/>
+      <c r="AA38" s="260"/>
+      <c r="AB38" s="260"/>
+      <c r="AC38" s="261"/>
+      <c r="AD38" s="261"/>
+      <c r="AE38" s="261"/>
+      <c r="AF38" s="261"/>
       <c r="AG38" s="123" t="s">
         <v>38</v>
       </c>
@@ -16014,41 +16030,41 @@
       <c r="AR39" s="3"/>
     </row>
     <row r="40" spans="1:44" s="36" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A40" s="267" t="s">
+      <c r="A40" s="268" t="s">
         <v>316</v>
       </c>
-      <c r="B40" s="267"/>
-      <c r="C40" s="267"/>
-      <c r="D40" s="267"/>
-      <c r="E40" s="267"/>
-      <c r="F40" s="267"/>
-      <c r="G40" s="267"/>
-      <c r="H40" s="267"/>
-      <c r="I40" s="267"/>
-      <c r="J40" s="267"/>
-      <c r="K40" s="267"/>
-      <c r="L40" s="267"/>
-      <c r="M40" s="267"/>
-      <c r="N40" s="267"/>
-      <c r="O40" s="267"/>
-      <c r="P40" s="267"/>
-      <c r="Q40" s="267"/>
-      <c r="R40" s="267"/>
-      <c r="S40" s="267"/>
-      <c r="T40" s="267"/>
-      <c r="U40" s="267"/>
-      <c r="V40" s="267"/>
-      <c r="W40" s="267"/>
-      <c r="X40" s="267"/>
-      <c r="Y40" s="267"/>
-      <c r="Z40" s="267"/>
-      <c r="AA40" s="267"/>
-      <c r="AB40" s="267"/>
-      <c r="AC40" s="267"/>
-      <c r="AD40" s="267"/>
-      <c r="AE40" s="267"/>
-      <c r="AF40" s="267"/>
-      <c r="AG40" s="267"/>
+      <c r="B40" s="268"/>
+      <c r="C40" s="268"/>
+      <c r="D40" s="268"/>
+      <c r="E40" s="268"/>
+      <c r="F40" s="268"/>
+      <c r="G40" s="268"/>
+      <c r="H40" s="268"/>
+      <c r="I40" s="268"/>
+      <c r="J40" s="268"/>
+      <c r="K40" s="268"/>
+      <c r="L40" s="268"/>
+      <c r="M40" s="268"/>
+      <c r="N40" s="268"/>
+      <c r="O40" s="268"/>
+      <c r="P40" s="268"/>
+      <c r="Q40" s="268"/>
+      <c r="R40" s="268"/>
+      <c r="S40" s="268"/>
+      <c r="T40" s="268"/>
+      <c r="U40" s="268"/>
+      <c r="V40" s="268"/>
+      <c r="W40" s="268"/>
+      <c r="X40" s="268"/>
+      <c r="Y40" s="268"/>
+      <c r="Z40" s="268"/>
+      <c r="AA40" s="268"/>
+      <c r="AB40" s="268"/>
+      <c r="AC40" s="268"/>
+      <c r="AD40" s="268"/>
+      <c r="AE40" s="268"/>
+      <c r="AF40" s="268"/>
+      <c r="AG40" s="268"/>
       <c r="AR40" s="3"/>
     </row>
     <row r="41" spans="1:44" s="36" customFormat="1" ht="15" customHeight="1">
@@ -16082,90 +16098,90 @@
       <c r="Z41" s="13"/>
       <c r="AA41" s="21"/>
       <c r="AB41" s="105"/>
-      <c r="AC41" s="268"/>
-      <c r="AD41" s="268"/>
-      <c r="AE41" s="268"/>
-      <c r="AF41" s="268"/>
+      <c r="AC41" s="269"/>
+      <c r="AD41" s="269"/>
+      <c r="AE41" s="269"/>
+      <c r="AF41" s="269"/>
       <c r="AG41" s="22" t="s">
         <v>37</v>
       </c>
       <c r="AR41" s="3"/>
     </row>
     <row r="42" spans="1:44" s="36" customFormat="1" ht="15" customHeight="1">
-      <c r="A42" s="269" t="s">
+      <c r="A42" s="270" t="s">
         <v>218</v>
       </c>
-      <c r="B42" s="270"/>
-      <c r="C42" s="270"/>
-      <c r="D42" s="270"/>
-      <c r="E42" s="270"/>
-      <c r="F42" s="270"/>
-      <c r="G42" s="270"/>
-      <c r="H42" s="270"/>
-      <c r="I42" s="270"/>
-      <c r="J42" s="270"/>
-      <c r="K42" s="270"/>
-      <c r="L42" s="270"/>
-      <c r="M42" s="270"/>
-      <c r="N42" s="270"/>
-      <c r="O42" s="270"/>
-      <c r="P42" s="270"/>
-      <c r="Q42" s="270"/>
-      <c r="R42" s="270"/>
-      <c r="S42" s="270"/>
-      <c r="T42" s="270"/>
-      <c r="U42" s="270"/>
-      <c r="V42" s="270"/>
-      <c r="W42" s="270"/>
-      <c r="X42" s="270"/>
-      <c r="Y42" s="270"/>
-      <c r="Z42" s="270"/>
-      <c r="AA42" s="270"/>
-      <c r="AB42" s="270"/>
-      <c r="AC42" s="271"/>
-      <c r="AD42" s="271"/>
-      <c r="AE42" s="271"/>
-      <c r="AF42" s="271"/>
+      <c r="B42" s="271"/>
+      <c r="C42" s="271"/>
+      <c r="D42" s="271"/>
+      <c r="E42" s="271"/>
+      <c r="F42" s="271"/>
+      <c r="G42" s="271"/>
+      <c r="H42" s="271"/>
+      <c r="I42" s="271"/>
+      <c r="J42" s="271"/>
+      <c r="K42" s="271"/>
+      <c r="L42" s="271"/>
+      <c r="M42" s="271"/>
+      <c r="N42" s="271"/>
+      <c r="O42" s="271"/>
+      <c r="P42" s="271"/>
+      <c r="Q42" s="271"/>
+      <c r="R42" s="271"/>
+      <c r="S42" s="271"/>
+      <c r="T42" s="271"/>
+      <c r="U42" s="271"/>
+      <c r="V42" s="271"/>
+      <c r="W42" s="271"/>
+      <c r="X42" s="271"/>
+      <c r="Y42" s="271"/>
+      <c r="Z42" s="271"/>
+      <c r="AA42" s="271"/>
+      <c r="AB42" s="271"/>
+      <c r="AC42" s="272"/>
+      <c r="AD42" s="272"/>
+      <c r="AE42" s="272"/>
+      <c r="AF42" s="272"/>
       <c r="AG42" s="28" t="s">
         <v>38</v>
       </c>
       <c r="AR42" s="3"/>
     </row>
     <row r="43" spans="1:44" s="36" customFormat="1" ht="15" customHeight="1">
-      <c r="A43" s="263" t="s">
+      <c r="A43" s="264" t="s">
         <v>219</v>
       </c>
-      <c r="B43" s="264"/>
-      <c r="C43" s="264"/>
-      <c r="D43" s="264"/>
-      <c r="E43" s="264"/>
-      <c r="F43" s="264"/>
-      <c r="G43" s="264"/>
-      <c r="H43" s="264"/>
-      <c r="I43" s="264"/>
-      <c r="J43" s="264"/>
-      <c r="K43" s="264"/>
-      <c r="L43" s="264"/>
-      <c r="M43" s="264"/>
-      <c r="N43" s="264"/>
-      <c r="O43" s="264"/>
-      <c r="P43" s="264"/>
-      <c r="Q43" s="264"/>
-      <c r="R43" s="264"/>
-      <c r="S43" s="264"/>
-      <c r="T43" s="264"/>
-      <c r="U43" s="264"/>
-      <c r="V43" s="264"/>
-      <c r="W43" s="264"/>
-      <c r="X43" s="264"/>
-      <c r="Y43" s="264"/>
-      <c r="Z43" s="264"/>
-      <c r="AA43" s="264"/>
-      <c r="AB43" s="264"/>
-      <c r="AC43" s="271"/>
-      <c r="AD43" s="271"/>
-      <c r="AE43" s="271"/>
-      <c r="AF43" s="271"/>
+      <c r="B43" s="265"/>
+      <c r="C43" s="265"/>
+      <c r="D43" s="265"/>
+      <c r="E43" s="265"/>
+      <c r="F43" s="265"/>
+      <c r="G43" s="265"/>
+      <c r="H43" s="265"/>
+      <c r="I43" s="265"/>
+      <c r="J43" s="265"/>
+      <c r="K43" s="265"/>
+      <c r="L43" s="265"/>
+      <c r="M43" s="265"/>
+      <c r="N43" s="265"/>
+      <c r="O43" s="265"/>
+      <c r="P43" s="265"/>
+      <c r="Q43" s="265"/>
+      <c r="R43" s="265"/>
+      <c r="S43" s="265"/>
+      <c r="T43" s="265"/>
+      <c r="U43" s="265"/>
+      <c r="V43" s="265"/>
+      <c r="W43" s="265"/>
+      <c r="X43" s="265"/>
+      <c r="Y43" s="265"/>
+      <c r="Z43" s="265"/>
+      <c r="AA43" s="265"/>
+      <c r="AB43" s="265"/>
+      <c r="AC43" s="272"/>
+      <c r="AD43" s="272"/>
+      <c r="AE43" s="272"/>
+      <c r="AF43" s="272"/>
       <c r="AG43" s="33" t="s">
         <v>38</v>
       </c>
@@ -16202,13 +16218,13 @@
       <c r="Z44" s="4"/>
       <c r="AA44" s="4"/>
       <c r="AB44" s="106"/>
-      <c r="AC44" s="272" t="str">
+      <c r="AC44" s="273" t="str">
         <f>IF(AC42-AC43=0,"",AC42-AC43)</f>
         <v/>
       </c>
-      <c r="AD44" s="272"/>
-      <c r="AE44" s="272"/>
-      <c r="AF44" s="272"/>
+      <c r="AD44" s="273"/>
+      <c r="AE44" s="273"/>
+      <c r="AF44" s="273"/>
       <c r="AG44" s="33" t="s">
         <v>38</v>
       </c>
@@ -16245,93 +16261,93 @@
       <c r="Z45" s="125"/>
       <c r="AA45" s="125"/>
       <c r="AB45" s="126"/>
-      <c r="AC45" s="305" t="str">
+      <c r="AC45" s="306" t="str">
         <f>IFERROR((AC44/AC43)*100,"")</f>
         <v/>
       </c>
-      <c r="AD45" s="305"/>
-      <c r="AE45" s="305"/>
-      <c r="AF45" s="305"/>
+      <c r="AD45" s="306"/>
+      <c r="AE45" s="306"/>
+      <c r="AF45" s="306"/>
       <c r="AG45" s="127" t="s">
         <v>49</v>
       </c>
       <c r="AR45" s="3"/>
     </row>
     <row r="46" spans="1:44" s="36" customFormat="1" ht="15" customHeight="1">
-      <c r="A46" s="274" t="s">
+      <c r="A46" s="275" t="s">
         <v>220</v>
       </c>
-      <c r="B46" s="275"/>
-      <c r="C46" s="275"/>
-      <c r="D46" s="275"/>
-      <c r="E46" s="275"/>
-      <c r="F46" s="275"/>
-      <c r="G46" s="275"/>
-      <c r="H46" s="275"/>
-      <c r="I46" s="275"/>
-      <c r="J46" s="275"/>
-      <c r="K46" s="275"/>
-      <c r="L46" s="275"/>
-      <c r="M46" s="275"/>
-      <c r="N46" s="275"/>
-      <c r="O46" s="275"/>
-      <c r="P46" s="275"/>
-      <c r="Q46" s="275"/>
-      <c r="R46" s="275"/>
-      <c r="S46" s="275"/>
-      <c r="T46" s="275"/>
-      <c r="U46" s="275"/>
-      <c r="V46" s="275"/>
-      <c r="W46" s="275"/>
-      <c r="X46" s="275"/>
-      <c r="Y46" s="275"/>
-      <c r="Z46" s="275"/>
-      <c r="AA46" s="275"/>
-      <c r="AB46" s="275"/>
-      <c r="AC46" s="278"/>
-      <c r="AD46" s="278"/>
-      <c r="AE46" s="278"/>
-      <c r="AF46" s="278"/>
+      <c r="B46" s="276"/>
+      <c r="C46" s="276"/>
+      <c r="D46" s="276"/>
+      <c r="E46" s="276"/>
+      <c r="F46" s="276"/>
+      <c r="G46" s="276"/>
+      <c r="H46" s="276"/>
+      <c r="I46" s="276"/>
+      <c r="J46" s="276"/>
+      <c r="K46" s="276"/>
+      <c r="L46" s="276"/>
+      <c r="M46" s="276"/>
+      <c r="N46" s="276"/>
+      <c r="O46" s="276"/>
+      <c r="P46" s="276"/>
+      <c r="Q46" s="276"/>
+      <c r="R46" s="276"/>
+      <c r="S46" s="276"/>
+      <c r="T46" s="276"/>
+      <c r="U46" s="276"/>
+      <c r="V46" s="276"/>
+      <c r="W46" s="276"/>
+      <c r="X46" s="276"/>
+      <c r="Y46" s="276"/>
+      <c r="Z46" s="276"/>
+      <c r="AA46" s="276"/>
+      <c r="AB46" s="276"/>
+      <c r="AC46" s="279"/>
+      <c r="AD46" s="279"/>
+      <c r="AE46" s="279"/>
+      <c r="AF46" s="279"/>
       <c r="AG46" s="128" t="s">
         <v>50</v>
       </c>
       <c r="AR46" s="3"/>
     </row>
     <row r="47" spans="1:44" s="36" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A47" s="276" t="s">
+      <c r="A47" s="277" t="s">
         <v>221</v>
       </c>
-      <c r="B47" s="277"/>
-      <c r="C47" s="277"/>
-      <c r="D47" s="277"/>
-      <c r="E47" s="277"/>
-      <c r="F47" s="277"/>
-      <c r="G47" s="277"/>
-      <c r="H47" s="277"/>
-      <c r="I47" s="277"/>
-      <c r="J47" s="277"/>
-      <c r="K47" s="277"/>
-      <c r="L47" s="277"/>
-      <c r="M47" s="277"/>
-      <c r="N47" s="277"/>
-      <c r="O47" s="277"/>
-      <c r="P47" s="277"/>
-      <c r="Q47" s="277"/>
-      <c r="R47" s="277"/>
-      <c r="S47" s="277"/>
-      <c r="T47" s="277"/>
-      <c r="U47" s="277"/>
-      <c r="V47" s="277"/>
-      <c r="W47" s="277"/>
-      <c r="X47" s="277"/>
-      <c r="Y47" s="277"/>
-      <c r="Z47" s="277"/>
-      <c r="AA47" s="277"/>
-      <c r="AB47" s="277"/>
-      <c r="AC47" s="279"/>
-      <c r="AD47" s="279"/>
-      <c r="AE47" s="279"/>
-      <c r="AF47" s="279"/>
+      <c r="B47" s="278"/>
+      <c r="C47" s="278"/>
+      <c r="D47" s="278"/>
+      <c r="E47" s="278"/>
+      <c r="F47" s="278"/>
+      <c r="G47" s="278"/>
+      <c r="H47" s="278"/>
+      <c r="I47" s="278"/>
+      <c r="J47" s="278"/>
+      <c r="K47" s="278"/>
+      <c r="L47" s="278"/>
+      <c r="M47" s="278"/>
+      <c r="N47" s="278"/>
+      <c r="O47" s="278"/>
+      <c r="P47" s="278"/>
+      <c r="Q47" s="278"/>
+      <c r="R47" s="278"/>
+      <c r="S47" s="278"/>
+      <c r="T47" s="278"/>
+      <c r="U47" s="278"/>
+      <c r="V47" s="278"/>
+      <c r="W47" s="278"/>
+      <c r="X47" s="278"/>
+      <c r="Y47" s="278"/>
+      <c r="Z47" s="278"/>
+      <c r="AA47" s="278"/>
+      <c r="AB47" s="278"/>
+      <c r="AC47" s="280"/>
+      <c r="AD47" s="280"/>
+      <c r="AE47" s="280"/>
+      <c r="AF47" s="280"/>
       <c r="AG47" s="129" t="s">
         <v>50</v>
       </c>
@@ -16374,41 +16390,41 @@
       <c r="AR48" s="3"/>
     </row>
     <row r="49" spans="1:67" s="36" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A49" s="267" t="s">
+      <c r="A49" s="268" t="s">
         <v>164</v>
       </c>
-      <c r="B49" s="267"/>
-      <c r="C49" s="267"/>
-      <c r="D49" s="267"/>
-      <c r="E49" s="267"/>
-      <c r="F49" s="267"/>
-      <c r="G49" s="267"/>
-      <c r="H49" s="267"/>
-      <c r="I49" s="267"/>
-      <c r="J49" s="267"/>
-      <c r="K49" s="267"/>
-      <c r="L49" s="267"/>
-      <c r="M49" s="267"/>
-      <c r="N49" s="267"/>
-      <c r="O49" s="267"/>
-      <c r="P49" s="267"/>
-      <c r="Q49" s="267"/>
-      <c r="R49" s="267"/>
-      <c r="S49" s="267"/>
-      <c r="T49" s="267"/>
-      <c r="U49" s="267"/>
-      <c r="V49" s="267"/>
-      <c r="W49" s="267"/>
-      <c r="X49" s="267"/>
-      <c r="Y49" s="267"/>
-      <c r="Z49" s="267"/>
-      <c r="AA49" s="267"/>
-      <c r="AB49" s="267"/>
-      <c r="AC49" s="267"/>
-      <c r="AD49" s="267"/>
-      <c r="AE49" s="267"/>
-      <c r="AF49" s="267"/>
-      <c r="AG49" s="267"/>
+      <c r="B49" s="268"/>
+      <c r="C49" s="268"/>
+      <c r="D49" s="268"/>
+      <c r="E49" s="268"/>
+      <c r="F49" s="268"/>
+      <c r="G49" s="268"/>
+      <c r="H49" s="268"/>
+      <c r="I49" s="268"/>
+      <c r="J49" s="268"/>
+      <c r="K49" s="268"/>
+      <c r="L49" s="268"/>
+      <c r="M49" s="268"/>
+      <c r="N49" s="268"/>
+      <c r="O49" s="268"/>
+      <c r="P49" s="268"/>
+      <c r="Q49" s="268"/>
+      <c r="R49" s="268"/>
+      <c r="S49" s="268"/>
+      <c r="T49" s="268"/>
+      <c r="U49" s="268"/>
+      <c r="V49" s="268"/>
+      <c r="W49" s="268"/>
+      <c r="X49" s="268"/>
+      <c r="Y49" s="268"/>
+      <c r="Z49" s="268"/>
+      <c r="AA49" s="268"/>
+      <c r="AB49" s="268"/>
+      <c r="AC49" s="268"/>
+      <c r="AD49" s="268"/>
+      <c r="AE49" s="268"/>
+      <c r="AF49" s="268"/>
+      <c r="AG49" s="268"/>
       <c r="AR49" s="3"/>
     </row>
     <row r="50" spans="1:67" s="36" customFormat="1" ht="15" customHeight="1">
@@ -16442,90 +16458,90 @@
       <c r="Z50" s="13"/>
       <c r="AA50" s="21"/>
       <c r="AB50" s="105"/>
-      <c r="AC50" s="268"/>
-      <c r="AD50" s="268"/>
-      <c r="AE50" s="268"/>
-      <c r="AF50" s="268"/>
+      <c r="AC50" s="269"/>
+      <c r="AD50" s="269"/>
+      <c r="AE50" s="269"/>
+      <c r="AF50" s="269"/>
       <c r="AG50" s="22" t="s">
         <v>37</v>
       </c>
       <c r="AR50" s="3"/>
     </row>
     <row r="51" spans="1:67" s="36" customFormat="1" ht="15" customHeight="1">
-      <c r="A51" s="269" t="s">
+      <c r="A51" s="270" t="s">
         <v>222</v>
       </c>
-      <c r="B51" s="270"/>
-      <c r="C51" s="270"/>
-      <c r="D51" s="270"/>
-      <c r="E51" s="270"/>
-      <c r="F51" s="270"/>
-      <c r="G51" s="270"/>
-      <c r="H51" s="270"/>
-      <c r="I51" s="270"/>
-      <c r="J51" s="270"/>
-      <c r="K51" s="270"/>
-      <c r="L51" s="270"/>
-      <c r="M51" s="270"/>
-      <c r="N51" s="270"/>
-      <c r="O51" s="270"/>
-      <c r="P51" s="270"/>
-      <c r="Q51" s="270"/>
-      <c r="R51" s="270"/>
-      <c r="S51" s="270"/>
-      <c r="T51" s="270"/>
-      <c r="U51" s="270"/>
-      <c r="V51" s="270"/>
-      <c r="W51" s="270"/>
-      <c r="X51" s="270"/>
-      <c r="Y51" s="270"/>
-      <c r="Z51" s="270"/>
-      <c r="AA51" s="270"/>
-      <c r="AB51" s="270"/>
-      <c r="AC51" s="271"/>
-      <c r="AD51" s="271"/>
-      <c r="AE51" s="271"/>
-      <c r="AF51" s="271"/>
+      <c r="B51" s="271"/>
+      <c r="C51" s="271"/>
+      <c r="D51" s="271"/>
+      <c r="E51" s="271"/>
+      <c r="F51" s="271"/>
+      <c r="G51" s="271"/>
+      <c r="H51" s="271"/>
+      <c r="I51" s="271"/>
+      <c r="J51" s="271"/>
+      <c r="K51" s="271"/>
+      <c r="L51" s="271"/>
+      <c r="M51" s="271"/>
+      <c r="N51" s="271"/>
+      <c r="O51" s="271"/>
+      <c r="P51" s="271"/>
+      <c r="Q51" s="271"/>
+      <c r="R51" s="271"/>
+      <c r="S51" s="271"/>
+      <c r="T51" s="271"/>
+      <c r="U51" s="271"/>
+      <c r="V51" s="271"/>
+      <c r="W51" s="271"/>
+      <c r="X51" s="271"/>
+      <c r="Y51" s="271"/>
+      <c r="Z51" s="271"/>
+      <c r="AA51" s="271"/>
+      <c r="AB51" s="271"/>
+      <c r="AC51" s="272"/>
+      <c r="AD51" s="272"/>
+      <c r="AE51" s="272"/>
+      <c r="AF51" s="272"/>
       <c r="AG51" s="28" t="s">
         <v>38</v>
       </c>
       <c r="AR51" s="3"/>
     </row>
     <row r="52" spans="1:67" s="36" customFormat="1" ht="15" customHeight="1">
-      <c r="A52" s="263" t="s">
+      <c r="A52" s="264" t="s">
         <v>223</v>
       </c>
-      <c r="B52" s="264"/>
-      <c r="C52" s="264"/>
-      <c r="D52" s="264"/>
-      <c r="E52" s="264"/>
-      <c r="F52" s="264"/>
-      <c r="G52" s="264"/>
-      <c r="H52" s="264"/>
-      <c r="I52" s="264"/>
-      <c r="J52" s="264"/>
-      <c r="K52" s="264"/>
-      <c r="L52" s="264"/>
-      <c r="M52" s="264"/>
-      <c r="N52" s="264"/>
-      <c r="O52" s="264"/>
-      <c r="P52" s="264"/>
-      <c r="Q52" s="264"/>
-      <c r="R52" s="264"/>
-      <c r="S52" s="264"/>
-      <c r="T52" s="264"/>
-      <c r="U52" s="264"/>
-      <c r="V52" s="264"/>
-      <c r="W52" s="264"/>
-      <c r="X52" s="264"/>
-      <c r="Y52" s="264"/>
-      <c r="Z52" s="264"/>
-      <c r="AA52" s="264"/>
-      <c r="AB52" s="264"/>
-      <c r="AC52" s="271"/>
-      <c r="AD52" s="271"/>
-      <c r="AE52" s="271"/>
-      <c r="AF52" s="271"/>
+      <c r="B52" s="265"/>
+      <c r="C52" s="265"/>
+      <c r="D52" s="265"/>
+      <c r="E52" s="265"/>
+      <c r="F52" s="265"/>
+      <c r="G52" s="265"/>
+      <c r="H52" s="265"/>
+      <c r="I52" s="265"/>
+      <c r="J52" s="265"/>
+      <c r="K52" s="265"/>
+      <c r="L52" s="265"/>
+      <c r="M52" s="265"/>
+      <c r="N52" s="265"/>
+      <c r="O52" s="265"/>
+      <c r="P52" s="265"/>
+      <c r="Q52" s="265"/>
+      <c r="R52" s="265"/>
+      <c r="S52" s="265"/>
+      <c r="T52" s="265"/>
+      <c r="U52" s="265"/>
+      <c r="V52" s="265"/>
+      <c r="W52" s="265"/>
+      <c r="X52" s="265"/>
+      <c r="Y52" s="265"/>
+      <c r="Z52" s="265"/>
+      <c r="AA52" s="265"/>
+      <c r="AB52" s="265"/>
+      <c r="AC52" s="272"/>
+      <c r="AD52" s="272"/>
+      <c r="AE52" s="272"/>
+      <c r="AF52" s="272"/>
       <c r="AG52" s="33" t="s">
         <v>38</v>
       </c>
@@ -16562,13 +16578,13 @@
       <c r="Z53" s="4"/>
       <c r="AA53" s="4"/>
       <c r="AB53" s="106"/>
-      <c r="AC53" s="272" t="str">
+      <c r="AC53" s="273" t="str">
         <f>IF(AC51-AC52=0,"",AC51-AC52)</f>
         <v/>
       </c>
-      <c r="AD53" s="272"/>
-      <c r="AE53" s="272"/>
-      <c r="AF53" s="272"/>
+      <c r="AD53" s="273"/>
+      <c r="AE53" s="273"/>
+      <c r="AF53" s="273"/>
       <c r="AG53" s="33" t="s">
         <v>38</v>
       </c>
@@ -16605,93 +16621,93 @@
       <c r="Z54" s="125"/>
       <c r="AA54" s="125"/>
       <c r="AB54" s="126"/>
-      <c r="AC54" s="305" t="str">
+      <c r="AC54" s="306" t="str">
         <f>IFERROR((AC53/AC52)*100,"")</f>
         <v/>
       </c>
-      <c r="AD54" s="305"/>
-      <c r="AE54" s="305"/>
-      <c r="AF54" s="305"/>
+      <c r="AD54" s="306"/>
+      <c r="AE54" s="306"/>
+      <c r="AF54" s="306"/>
       <c r="AG54" s="127" t="s">
         <v>49</v>
       </c>
       <c r="AR54" s="3"/>
     </row>
     <row r="55" spans="1:67" s="36" customFormat="1" ht="15" customHeight="1">
-      <c r="A55" s="274" t="s">
+      <c r="A55" s="275" t="s">
         <v>224</v>
       </c>
-      <c r="B55" s="275"/>
-      <c r="C55" s="275"/>
-      <c r="D55" s="275"/>
-      <c r="E55" s="275"/>
-      <c r="F55" s="275"/>
-      <c r="G55" s="275"/>
-      <c r="H55" s="275"/>
-      <c r="I55" s="275"/>
-      <c r="J55" s="275"/>
-      <c r="K55" s="275"/>
-      <c r="L55" s="275"/>
-      <c r="M55" s="275"/>
-      <c r="N55" s="275"/>
-      <c r="O55" s="275"/>
-      <c r="P55" s="275"/>
-      <c r="Q55" s="275"/>
-      <c r="R55" s="275"/>
-      <c r="S55" s="275"/>
-      <c r="T55" s="275"/>
-      <c r="U55" s="275"/>
-      <c r="V55" s="275"/>
-      <c r="W55" s="275"/>
-      <c r="X55" s="275"/>
-      <c r="Y55" s="275"/>
-      <c r="Z55" s="275"/>
-      <c r="AA55" s="275"/>
-      <c r="AB55" s="275"/>
-      <c r="AC55" s="278"/>
-      <c r="AD55" s="278"/>
-      <c r="AE55" s="278"/>
-      <c r="AF55" s="278"/>
+      <c r="B55" s="276"/>
+      <c r="C55" s="276"/>
+      <c r="D55" s="276"/>
+      <c r="E55" s="276"/>
+      <c r="F55" s="276"/>
+      <c r="G55" s="276"/>
+      <c r="H55" s="276"/>
+      <c r="I55" s="276"/>
+      <c r="J55" s="276"/>
+      <c r="K55" s="276"/>
+      <c r="L55" s="276"/>
+      <c r="M55" s="276"/>
+      <c r="N55" s="276"/>
+      <c r="O55" s="276"/>
+      <c r="P55" s="276"/>
+      <c r="Q55" s="276"/>
+      <c r="R55" s="276"/>
+      <c r="S55" s="276"/>
+      <c r="T55" s="276"/>
+      <c r="U55" s="276"/>
+      <c r="V55" s="276"/>
+      <c r="W55" s="276"/>
+      <c r="X55" s="276"/>
+      <c r="Y55" s="276"/>
+      <c r="Z55" s="276"/>
+      <c r="AA55" s="276"/>
+      <c r="AB55" s="276"/>
+      <c r="AC55" s="279"/>
+      <c r="AD55" s="279"/>
+      <c r="AE55" s="279"/>
+      <c r="AF55" s="279"/>
       <c r="AG55" s="128" t="s">
         <v>50</v>
       </c>
       <c r="AR55" s="3"/>
     </row>
     <row r="56" spans="1:67" s="36" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A56" s="276" t="s">
+      <c r="A56" s="277" t="s">
         <v>225</v>
       </c>
-      <c r="B56" s="277"/>
-      <c r="C56" s="277"/>
-      <c r="D56" s="277"/>
-      <c r="E56" s="277"/>
-      <c r="F56" s="277"/>
-      <c r="G56" s="277"/>
-      <c r="H56" s="277"/>
-      <c r="I56" s="277"/>
-      <c r="J56" s="277"/>
-      <c r="K56" s="277"/>
-      <c r="L56" s="277"/>
-      <c r="M56" s="277"/>
-      <c r="N56" s="277"/>
-      <c r="O56" s="277"/>
-      <c r="P56" s="277"/>
-      <c r="Q56" s="277"/>
-      <c r="R56" s="277"/>
-      <c r="S56" s="277"/>
-      <c r="T56" s="277"/>
-      <c r="U56" s="277"/>
-      <c r="V56" s="277"/>
-      <c r="W56" s="277"/>
-      <c r="X56" s="277"/>
-      <c r="Y56" s="277"/>
-      <c r="Z56" s="277"/>
-      <c r="AA56" s="277"/>
-      <c r="AB56" s="277"/>
-      <c r="AC56" s="279"/>
-      <c r="AD56" s="279"/>
-      <c r="AE56" s="279"/>
-      <c r="AF56" s="279"/>
+      <c r="B56" s="278"/>
+      <c r="C56" s="278"/>
+      <c r="D56" s="278"/>
+      <c r="E56" s="278"/>
+      <c r="F56" s="278"/>
+      <c r="G56" s="278"/>
+      <c r="H56" s="278"/>
+      <c r="I56" s="278"/>
+      <c r="J56" s="278"/>
+      <c r="K56" s="278"/>
+      <c r="L56" s="278"/>
+      <c r="M56" s="278"/>
+      <c r="N56" s="278"/>
+      <c r="O56" s="278"/>
+      <c r="P56" s="278"/>
+      <c r="Q56" s="278"/>
+      <c r="R56" s="278"/>
+      <c r="S56" s="278"/>
+      <c r="T56" s="278"/>
+      <c r="U56" s="278"/>
+      <c r="V56" s="278"/>
+      <c r="W56" s="278"/>
+      <c r="X56" s="278"/>
+      <c r="Y56" s="278"/>
+      <c r="Z56" s="278"/>
+      <c r="AA56" s="278"/>
+      <c r="AB56" s="278"/>
+      <c r="AC56" s="280"/>
+      <c r="AD56" s="280"/>
+      <c r="AE56" s="280"/>
+      <c r="AF56" s="280"/>
       <c r="AG56" s="129" t="s">
         <v>50</v>
       </c>
@@ -16734,17 +16750,17 @@
       <c r="AR57" s="3"/>
     </row>
     <row r="58" spans="1:67" s="36" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A58" s="297" t="s">
+      <c r="A58" s="298" t="s">
         <v>317</v>
       </c>
-      <c r="B58" s="297"/>
-      <c r="C58" s="297"/>
-      <c r="D58" s="297"/>
-      <c r="E58" s="297"/>
-      <c r="F58" s="297"/>
-      <c r="G58" s="297"/>
-      <c r="H58" s="297"/>
-      <c r="I58" s="297"/>
+      <c r="B58" s="298"/>
+      <c r="C58" s="298"/>
+      <c r="D58" s="298"/>
+      <c r="E58" s="298"/>
+      <c r="F58" s="298"/>
+      <c r="G58" s="298"/>
+      <c r="H58" s="298"/>
+      <c r="I58" s="298"/>
       <c r="J58" s="164"/>
       <c r="K58" s="164"/>
       <c r="L58" s="164"/>
@@ -16802,93 +16818,93 @@
       <c r="Z59" s="13"/>
       <c r="AA59" s="21"/>
       <c r="AB59" s="105"/>
-      <c r="AC59" s="268"/>
-      <c r="AD59" s="268"/>
-      <c r="AE59" s="268"/>
-      <c r="AF59" s="268"/>
+      <c r="AC59" s="269"/>
+      <c r="AD59" s="269"/>
+      <c r="AE59" s="269"/>
+      <c r="AF59" s="269"/>
       <c r="AG59" s="22" t="s">
         <v>38</v>
       </c>
       <c r="AR59" s="3"/>
     </row>
     <row r="60" spans="1:67" s="36" customFormat="1" ht="15" customHeight="1">
-      <c r="A60" s="269" t="s">
+      <c r="A60" s="270" t="s">
         <v>212</v>
       </c>
-      <c r="B60" s="270"/>
-      <c r="C60" s="270"/>
-      <c r="D60" s="270"/>
-      <c r="E60" s="270"/>
-      <c r="F60" s="270"/>
-      <c r="G60" s="270"/>
-      <c r="H60" s="270"/>
-      <c r="I60" s="270"/>
-      <c r="J60" s="270"/>
-      <c r="K60" s="270"/>
-      <c r="L60" s="270"/>
-      <c r="M60" s="270"/>
-      <c r="N60" s="270"/>
-      <c r="O60" s="270"/>
-      <c r="P60" s="270"/>
-      <c r="Q60" s="270"/>
-      <c r="R60" s="270"/>
-      <c r="S60" s="270"/>
-      <c r="T60" s="270"/>
-      <c r="U60" s="270"/>
-      <c r="V60" s="270"/>
-      <c r="W60" s="270"/>
-      <c r="X60" s="270"/>
-      <c r="Y60" s="270"/>
-      <c r="Z60" s="270"/>
-      <c r="AA60" s="270"/>
-      <c r="AB60" s="270"/>
-      <c r="AC60" s="271"/>
-      <c r="AD60" s="271"/>
-      <c r="AE60" s="271"/>
-      <c r="AF60" s="271"/>
+      <c r="B60" s="271"/>
+      <c r="C60" s="271"/>
+      <c r="D60" s="271"/>
+      <c r="E60" s="271"/>
+      <c r="F60" s="271"/>
+      <c r="G60" s="271"/>
+      <c r="H60" s="271"/>
+      <c r="I60" s="271"/>
+      <c r="J60" s="271"/>
+      <c r="K60" s="271"/>
+      <c r="L60" s="271"/>
+      <c r="M60" s="271"/>
+      <c r="N60" s="271"/>
+      <c r="O60" s="271"/>
+      <c r="P60" s="271"/>
+      <c r="Q60" s="271"/>
+      <c r="R60" s="271"/>
+      <c r="S60" s="271"/>
+      <c r="T60" s="271"/>
+      <c r="U60" s="271"/>
+      <c r="V60" s="271"/>
+      <c r="W60" s="271"/>
+      <c r="X60" s="271"/>
+      <c r="Y60" s="271"/>
+      <c r="Z60" s="271"/>
+      <c r="AA60" s="271"/>
+      <c r="AB60" s="271"/>
+      <c r="AC60" s="272"/>
+      <c r="AD60" s="272"/>
+      <c r="AE60" s="272"/>
+      <c r="AF60" s="272"/>
       <c r="AG60" s="28" t="s">
         <v>38</v>
       </c>
       <c r="AR60" s="3"/>
     </row>
     <row r="61" spans="1:67" s="36" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A61" s="281" t="s">
+      <c r="A61" s="282" t="s">
         <v>315</v>
       </c>
-      <c r="B61" s="282"/>
-      <c r="C61" s="282"/>
-      <c r="D61" s="282"/>
-      <c r="E61" s="282"/>
-      <c r="F61" s="282"/>
-      <c r="G61" s="282"/>
-      <c r="H61" s="282"/>
-      <c r="I61" s="282"/>
-      <c r="J61" s="282"/>
-      <c r="K61" s="282"/>
-      <c r="L61" s="282"/>
-      <c r="M61" s="282"/>
-      <c r="N61" s="282"/>
-      <c r="O61" s="282"/>
-      <c r="P61" s="282"/>
-      <c r="Q61" s="282"/>
-      <c r="R61" s="282"/>
-      <c r="S61" s="282"/>
-      <c r="T61" s="282"/>
-      <c r="U61" s="282"/>
-      <c r="V61" s="282"/>
-      <c r="W61" s="282"/>
-      <c r="X61" s="282"/>
-      <c r="Y61" s="282"/>
-      <c r="Z61" s="282"/>
-      <c r="AA61" s="282"/>
-      <c r="AB61" s="282"/>
-      <c r="AC61" s="280" t="str">
+      <c r="B61" s="283"/>
+      <c r="C61" s="283"/>
+      <c r="D61" s="283"/>
+      <c r="E61" s="283"/>
+      <c r="F61" s="283"/>
+      <c r="G61" s="283"/>
+      <c r="H61" s="283"/>
+      <c r="I61" s="283"/>
+      <c r="J61" s="283"/>
+      <c r="K61" s="283"/>
+      <c r="L61" s="283"/>
+      <c r="M61" s="283"/>
+      <c r="N61" s="283"/>
+      <c r="O61" s="283"/>
+      <c r="P61" s="283"/>
+      <c r="Q61" s="283"/>
+      <c r="R61" s="283"/>
+      <c r="S61" s="283"/>
+      <c r="T61" s="283"/>
+      <c r="U61" s="283"/>
+      <c r="V61" s="283"/>
+      <c r="W61" s="283"/>
+      <c r="X61" s="283"/>
+      <c r="Y61" s="283"/>
+      <c r="Z61" s="283"/>
+      <c r="AA61" s="283"/>
+      <c r="AB61" s="283"/>
+      <c r="AC61" s="281" t="str">
         <f>IFERROR((AC59/AC60)*100,"")</f>
         <v/>
       </c>
-      <c r="AD61" s="280"/>
-      <c r="AE61" s="280"/>
-      <c r="AF61" s="280"/>
+      <c r="AD61" s="281"/>
+      <c r="AE61" s="281"/>
+      <c r="AF61" s="281"/>
       <c r="AG61" s="33" t="s">
         <v>49</v>
       </c>
@@ -16928,41 +16944,41 @@
       <c r="BO61" s="16"/>
     </row>
     <row r="62" spans="1:67" s="36" customFormat="1" ht="15" customHeight="1">
-      <c r="A62" s="288" t="s">
+      <c r="A62" s="289" t="s">
         <v>352</v>
       </c>
-      <c r="B62" s="288"/>
-      <c r="C62" s="288"/>
-      <c r="D62" s="288"/>
-      <c r="E62" s="288"/>
-      <c r="F62" s="288"/>
-      <c r="G62" s="288"/>
-      <c r="H62" s="288"/>
-      <c r="I62" s="288"/>
-      <c r="J62" s="288"/>
-      <c r="K62" s="288"/>
-      <c r="L62" s="288"/>
-      <c r="M62" s="288"/>
-      <c r="N62" s="288"/>
-      <c r="O62" s="288"/>
-      <c r="P62" s="288"/>
-      <c r="Q62" s="288"/>
-      <c r="R62" s="288"/>
-      <c r="S62" s="288"/>
-      <c r="T62" s="288"/>
-      <c r="U62" s="288"/>
-      <c r="V62" s="288"/>
-      <c r="W62" s="288"/>
-      <c r="X62" s="288"/>
-      <c r="Y62" s="288"/>
-      <c r="Z62" s="288"/>
-      <c r="AA62" s="288"/>
-      <c r="AB62" s="288"/>
-      <c r="AC62" s="288"/>
-      <c r="AD62" s="288"/>
-      <c r="AE62" s="288"/>
-      <c r="AF62" s="288"/>
-      <c r="AG62" s="288"/>
+      <c r="B62" s="289"/>
+      <c r="C62" s="289"/>
+      <c r="D62" s="289"/>
+      <c r="E62" s="289"/>
+      <c r="F62" s="289"/>
+      <c r="G62" s="289"/>
+      <c r="H62" s="289"/>
+      <c r="I62" s="289"/>
+      <c r="J62" s="289"/>
+      <c r="K62" s="289"/>
+      <c r="L62" s="289"/>
+      <c r="M62" s="289"/>
+      <c r="N62" s="289"/>
+      <c r="O62" s="289"/>
+      <c r="P62" s="289"/>
+      <c r="Q62" s="289"/>
+      <c r="R62" s="289"/>
+      <c r="S62" s="289"/>
+      <c r="T62" s="289"/>
+      <c r="U62" s="289"/>
+      <c r="V62" s="289"/>
+      <c r="W62" s="289"/>
+      <c r="X62" s="289"/>
+      <c r="Y62" s="289"/>
+      <c r="Z62" s="289"/>
+      <c r="AA62" s="289"/>
+      <c r="AB62" s="289"/>
+      <c r="AC62" s="289"/>
+      <c r="AD62" s="289"/>
+      <c r="AE62" s="289"/>
+      <c r="AF62" s="289"/>
+      <c r="AG62" s="289"/>
       <c r="AH62" s="16"/>
       <c r="AI62" s="162"/>
       <c r="AJ62" s="146"/>
@@ -16974,13 +16990,13 @@
       <c r="AP62" s="146"/>
       <c r="AQ62" s="146"/>
       <c r="AR62" s="146"/>
-      <c r="AS62" s="289"/>
-      <c r="AT62" s="289"/>
-      <c r="AU62" s="289"/>
-      <c r="AV62" s="289"/>
-      <c r="AW62" s="289"/>
-      <c r="AX62" s="289"/>
-      <c r="AY62" s="289"/>
+      <c r="AS62" s="290"/>
+      <c r="AT62" s="290"/>
+      <c r="AU62" s="290"/>
+      <c r="AV62" s="290"/>
+      <c r="AW62" s="290"/>
+      <c r="AX62" s="290"/>
+      <c r="AY62" s="290"/>
       <c r="AZ62" s="146"/>
       <c r="BA62" s="16"/>
       <c r="BB62" s="16"/>
@@ -17000,40 +17016,40 @@
     </row>
     <row r="63" spans="1:67" s="36" customFormat="1" ht="15" customHeight="1">
       <c r="A63" s="151"/>
-      <c r="B63" s="290" t="s">
+      <c r="B63" s="291" t="s">
         <v>176</v>
       </c>
-      <c r="C63" s="290"/>
-      <c r="D63" s="290"/>
-      <c r="E63" s="290"/>
-      <c r="F63" s="290"/>
-      <c r="G63" s="290"/>
-      <c r="H63" s="290"/>
-      <c r="I63" s="290"/>
-      <c r="J63" s="290"/>
-      <c r="K63" s="290"/>
-      <c r="L63" s="290"/>
-      <c r="M63" s="290"/>
-      <c r="N63" s="290"/>
-      <c r="O63" s="290"/>
-      <c r="P63" s="290"/>
-      <c r="Q63" s="290"/>
-      <c r="R63" s="290"/>
-      <c r="S63" s="290"/>
-      <c r="T63" s="290"/>
-      <c r="U63" s="290"/>
-      <c r="V63" s="290"/>
-      <c r="W63" s="290"/>
-      <c r="X63" s="290"/>
-      <c r="Y63" s="290"/>
-      <c r="Z63" s="290"/>
-      <c r="AA63" s="290"/>
-      <c r="AB63" s="290"/>
-      <c r="AC63" s="290"/>
-      <c r="AD63" s="290"/>
-      <c r="AE63" s="290"/>
-      <c r="AF63" s="290"/>
-      <c r="AG63" s="290"/>
+      <c r="C63" s="291"/>
+      <c r="D63" s="291"/>
+      <c r="E63" s="291"/>
+      <c r="F63" s="291"/>
+      <c r="G63" s="291"/>
+      <c r="H63" s="291"/>
+      <c r="I63" s="291"/>
+      <c r="J63" s="291"/>
+      <c r="K63" s="291"/>
+      <c r="L63" s="291"/>
+      <c r="M63" s="291"/>
+      <c r="N63" s="291"/>
+      <c r="O63" s="291"/>
+      <c r="P63" s="291"/>
+      <c r="Q63" s="291"/>
+      <c r="R63" s="291"/>
+      <c r="S63" s="291"/>
+      <c r="T63" s="291"/>
+      <c r="U63" s="291"/>
+      <c r="V63" s="291"/>
+      <c r="W63" s="291"/>
+      <c r="X63" s="291"/>
+      <c r="Y63" s="291"/>
+      <c r="Z63" s="291"/>
+      <c r="AA63" s="291"/>
+      <c r="AB63" s="291"/>
+      <c r="AC63" s="291"/>
+      <c r="AD63" s="291"/>
+      <c r="AE63" s="291"/>
+      <c r="AF63" s="291"/>
+      <c r="AG63" s="291"/>
       <c r="AH63" s="16"/>
       <c r="AI63" s="162"/>
       <c r="AJ63" s="146"/>
@@ -17185,13 +17201,13 @@
       <c r="AP65" s="146"/>
       <c r="AQ65" s="146"/>
       <c r="AR65" s="146"/>
-      <c r="AS65" s="289"/>
-      <c r="AT65" s="289"/>
-      <c r="AU65" s="289"/>
-      <c r="AV65" s="289"/>
-      <c r="AW65" s="289"/>
-      <c r="AX65" s="289"/>
-      <c r="AY65" s="289"/>
+      <c r="AS65" s="290"/>
+      <c r="AT65" s="290"/>
+      <c r="AU65" s="290"/>
+      <c r="AV65" s="290"/>
+      <c r="AW65" s="290"/>
+      <c r="AX65" s="290"/>
+      <c r="AY65" s="290"/>
       <c r="AZ65" s="146"/>
       <c r="BA65" s="16"/>
       <c r="BB65" s="16"/>
@@ -17239,14 +17255,14 @@
       <c r="Y66" s="13"/>
       <c r="Z66" s="13"/>
       <c r="AA66" s="13"/>
-      <c r="AB66" s="296" t="str">
+      <c r="AB66" s="297" t="str">
         <f>IF(AB23=0,"",AB23)</f>
         <v/>
       </c>
-      <c r="AC66" s="296"/>
-      <c r="AD66" s="296"/>
-      <c r="AE66" s="296"/>
-      <c r="AF66" s="296"/>
+      <c r="AC66" s="297"/>
+      <c r="AD66" s="297"/>
+      <c r="AE66" s="297"/>
+      <c r="AF66" s="297"/>
       <c r="AG66" s="14" t="s">
         <v>38</v>
       </c>
@@ -17315,14 +17331,14 @@
       <c r="Y67" s="8"/>
       <c r="Z67" s="8"/>
       <c r="AA67" s="8"/>
-      <c r="AB67" s="286" t="str">
-        <f>IFERROR(AC36*AC61*V20,"")</f>
+      <c r="AB67" s="287" t="str">
+        <f>IFERROR(AC36*(AC61/100)*V20,"")</f>
         <v/>
       </c>
-      <c r="AC67" s="286"/>
-      <c r="AD67" s="286"/>
-      <c r="AE67" s="286"/>
-      <c r="AF67" s="286"/>
+      <c r="AC67" s="287"/>
+      <c r="AD67" s="287"/>
+      <c r="AE67" s="287"/>
+      <c r="AF67" s="287"/>
       <c r="AG67" s="9" t="s">
         <v>38</v>
       </c>
@@ -17337,13 +17353,13 @@
       <c r="AP67" s="146"/>
       <c r="AQ67" s="146"/>
       <c r="AR67" s="146"/>
-      <c r="AS67" s="289"/>
-      <c r="AT67" s="289"/>
-      <c r="AU67" s="289"/>
-      <c r="AV67" s="289"/>
-      <c r="AW67" s="289"/>
-      <c r="AX67" s="289"/>
-      <c r="AY67" s="289"/>
+      <c r="AS67" s="290"/>
+      <c r="AT67" s="290"/>
+      <c r="AU67" s="290"/>
+      <c r="AV67" s="290"/>
+      <c r="AW67" s="290"/>
+      <c r="AX67" s="290"/>
+      <c r="AY67" s="290"/>
       <c r="AZ67" s="146"/>
       <c r="BA67" s="16"/>
       <c r="BB67" s="16"/>
@@ -17391,15 +17407,15 @@
       <c r="Y68" s="184"/>
       <c r="Z68" s="184"/>
       <c r="AA68" s="184"/>
-      <c r="AB68" s="306" t="str">
-        <f>IFERROR(AC38*V20,"")</f>
+      <c r="AB68" s="307" t="str">
+        <f>IF(AC38=0,"",AC38)</f>
         <v/>
       </c>
-      <c r="AC68" s="306"/>
-      <c r="AD68" s="306"/>
-      <c r="AE68" s="306"/>
-      <c r="AF68" s="306"/>
-      <c r="AG68" s="292" t="s">
+      <c r="AC68" s="307"/>
+      <c r="AD68" s="307"/>
+      <c r="AE68" s="307"/>
+      <c r="AF68" s="307"/>
+      <c r="AG68" s="293" t="s">
         <v>38</v>
       </c>
       <c r="AH68" s="185"/>
@@ -17439,7 +17455,7 @@
     </row>
     <row r="69" spans="1:67" s="36" customFormat="1" ht="15.75" customHeight="1">
       <c r="A69" s="190" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B69" s="191"/>
       <c r="C69" s="191"/>
@@ -17467,12 +17483,12 @@
       <c r="Y69" s="191"/>
       <c r="Z69" s="191"/>
       <c r="AA69" s="191"/>
-      <c r="AB69" s="307"/>
-      <c r="AC69" s="307"/>
-      <c r="AD69" s="307"/>
-      <c r="AE69" s="307"/>
-      <c r="AF69" s="307"/>
-      <c r="AG69" s="293"/>
+      <c r="AB69" s="308"/>
+      <c r="AC69" s="308"/>
+      <c r="AD69" s="308"/>
+      <c r="AE69" s="308"/>
+      <c r="AF69" s="308"/>
+      <c r="AG69" s="294"/>
       <c r="AH69" s="16"/>
       <c r="AI69" s="16"/>
       <c r="AJ69" s="146"/>
@@ -17538,14 +17554,14 @@
       <c r="Y70" s="8"/>
       <c r="Z70" s="8"/>
       <c r="AA70" s="8"/>
-      <c r="AB70" s="286" t="str">
+      <c r="AB70" s="287" t="str">
         <f>IFERROR((AB67+AB68)-AB66,"")</f>
         <v/>
       </c>
-      <c r="AC70" s="286"/>
-      <c r="AD70" s="286"/>
-      <c r="AE70" s="286"/>
-      <c r="AF70" s="286"/>
+      <c r="AC70" s="287"/>
+      <c r="AD70" s="287"/>
+      <c r="AE70" s="287"/>
+      <c r="AF70" s="287"/>
       <c r="AG70" s="9" t="s">
         <v>38</v>
       </c>
@@ -17560,24 +17576,24 @@
       <c r="AP70" s="16"/>
       <c r="AQ70" s="16"/>
       <c r="AR70" s="16"/>
-      <c r="AS70" s="287"/>
-      <c r="AT70" s="287"/>
-      <c r="AU70" s="287"/>
-      <c r="AV70" s="287"/>
-      <c r="AW70" s="287"/>
-      <c r="AX70" s="287"/>
-      <c r="AY70" s="287"/>
+      <c r="AS70" s="288"/>
+      <c r="AT70" s="288"/>
+      <c r="AU70" s="288"/>
+      <c r="AV70" s="288"/>
+      <c r="AW70" s="288"/>
+      <c r="AX70" s="288"/>
+      <c r="AY70" s="288"/>
       <c r="AZ70" s="146"/>
       <c r="BA70" s="16"/>
       <c r="BB70" s="146"/>
       <c r="BC70" s="16"/>
-      <c r="BD70" s="283"/>
-      <c r="BE70" s="283"/>
-      <c r="BF70" s="283"/>
-      <c r="BG70" s="283"/>
-      <c r="BH70" s="283"/>
-      <c r="BI70" s="283"/>
-      <c r="BJ70" s="283"/>
+      <c r="BD70" s="284"/>
+      <c r="BE70" s="284"/>
+      <c r="BF70" s="284"/>
+      <c r="BG70" s="284"/>
+      <c r="BH70" s="284"/>
+      <c r="BI70" s="284"/>
+      <c r="BJ70" s="284"/>
       <c r="BK70" s="145"/>
       <c r="BL70" s="16"/>
       <c r="BM70" s="16"/>
@@ -17614,14 +17630,14 @@
       <c r="Y71" s="25"/>
       <c r="Z71" s="25"/>
       <c r="AA71" s="25"/>
-      <c r="AB71" s="284" t="str">
+      <c r="AB71" s="285" t="str">
         <f>IF(AB70&gt;=0,"賃金改善額充当済み","賃金改善額充当不足")</f>
         <v>賃金改善額充当済み</v>
       </c>
-      <c r="AC71" s="284"/>
-      <c r="AD71" s="284"/>
-      <c r="AE71" s="284"/>
-      <c r="AF71" s="284"/>
+      <c r="AC71" s="285"/>
+      <c r="AD71" s="285"/>
+      <c r="AE71" s="285"/>
+      <c r="AF71" s="285"/>
       <c r="AG71" s="29"/>
       <c r="AH71" s="16"/>
       <c r="AI71" s="16"/>
@@ -17843,24 +17859,24 @@
       <c r="AP74" s="16"/>
       <c r="AQ74" s="16"/>
       <c r="AR74" s="16"/>
-      <c r="AS74" s="287"/>
-      <c r="AT74" s="287"/>
-      <c r="AU74" s="287"/>
-      <c r="AV74" s="287"/>
-      <c r="AW74" s="287"/>
-      <c r="AX74" s="287"/>
-      <c r="AY74" s="287"/>
+      <c r="AS74" s="288"/>
+      <c r="AT74" s="288"/>
+      <c r="AU74" s="288"/>
+      <c r="AV74" s="288"/>
+      <c r="AW74" s="288"/>
+      <c r="AX74" s="288"/>
+      <c r="AY74" s="288"/>
       <c r="AZ74" s="146"/>
       <c r="BA74" s="16"/>
       <c r="BB74" s="146"/>
       <c r="BC74" s="16"/>
-      <c r="BD74" s="283"/>
-      <c r="BE74" s="283"/>
-      <c r="BF74" s="283"/>
-      <c r="BG74" s="283"/>
-      <c r="BH74" s="283"/>
-      <c r="BI74" s="283"/>
-      <c r="BJ74" s="283"/>
+      <c r="BD74" s="284"/>
+      <c r="BE74" s="284"/>
+      <c r="BF74" s="284"/>
+      <c r="BG74" s="284"/>
+      <c r="BH74" s="284"/>
+      <c r="BI74" s="284"/>
+      <c r="BJ74" s="284"/>
       <c r="BK74" s="145"/>
       <c r="BL74" s="16"/>
       <c r="BM74" s="16"/>
@@ -17875,18 +17891,18 @@
         <v>16</v>
       </c>
       <c r="E75" s="2"/>
-      <c r="F75" s="233"/>
-      <c r="G75" s="233"/>
+      <c r="F75" s="234"/>
+      <c r="G75" s="234"/>
       <c r="H75" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="I75" s="233"/>
-      <c r="J75" s="233"/>
+      <c r="I75" s="234"/>
+      <c r="J75" s="234"/>
       <c r="K75" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="L75" s="233"/>
-      <c r="M75" s="233"/>
+      <c r="L75" s="234"/>
+      <c r="M75" s="234"/>
       <c r="N75" s="2" t="s">
         <v>19</v>
       </c>
@@ -17898,18 +17914,18 @@
       <c r="R75" s="2"/>
       <c r="S75" s="2"/>
       <c r="T75" s="2"/>
-      <c r="U75" s="285"/>
-      <c r="V75" s="285"/>
-      <c r="W75" s="285"/>
-      <c r="X75" s="285"/>
-      <c r="Y75" s="285"/>
-      <c r="Z75" s="285"/>
-      <c r="AA75" s="285"/>
-      <c r="AB75" s="285"/>
-      <c r="AC75" s="285"/>
-      <c r="AD75" s="285"/>
-      <c r="AE75" s="285"/>
-      <c r="AF75" s="285"/>
+      <c r="U75" s="286"/>
+      <c r="V75" s="286"/>
+      <c r="W75" s="286"/>
+      <c r="X75" s="286"/>
+      <c r="Y75" s="286"/>
+      <c r="Z75" s="286"/>
+      <c r="AA75" s="286"/>
+      <c r="AB75" s="286"/>
+      <c r="AC75" s="286"/>
+      <c r="AD75" s="286"/>
+      <c r="AE75" s="286"/>
+      <c r="AF75" s="286"/>
       <c r="AG75" s="2"/>
       <c r="AH75" s="162"/>
       <c r="AI75" s="16"/>
@@ -19267,7 +19283,7 @@
       <c r="AG110" s="23"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="TtkPDlV673OC6eHt6Z3RtAygcz2faZ4HXOWYLgKbp6w51W8wmcbisHHmuifClxmD/lfoy5Iyp03zkRqSS6OFfA==" saltValue="Bttvp1Aaj3XGb1Gm9J+rJg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="VhjqJ2AALzloGDTXgOB3wJGsD0Bn2VH7vTL70nPRwzYWIH3xxnqDAigDqwe7tuVztnFfxWSgFEuk9yCoUmhMMQ==" saltValue="Rv7x7XJYDOqNpwrCOsnCbQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="85">
     <mergeCell ref="AB68:AF69"/>
     <mergeCell ref="F75:G75"/>
@@ -19843,13 +19859,13 @@
         <f>別添2!E11</f>
         <v>0</v>
       </c>
-      <c r="E2" s="41" t="str">
+      <c r="E2" s="41">
         <f>別添2!$C$14</f>
-        <v>（選択してください）</v>
-      </c>
-      <c r="F2" s="41" t="str">
+        <v>0</v>
+      </c>
+      <c r="F2" s="41">
         <f>別添2!$C$15</f>
-        <v>（選択してください）</v>
+        <v>0</v>
       </c>
       <c r="G2" s="41" t="b">
         <f>別添2!$O$18</f>
@@ -20303,9 +20319,9 @@
         <f>'（別添2）_実績報告書・中間報告書 (調剤法人) '!$AB$67</f>
         <v/>
       </c>
-      <c r="DP2" s="42" t="e">
-        <f>'（別添2）_実績報告書・中間報告書 (調剤法人) '!#REF!</f>
-        <v>#REF!</v>
+      <c r="DP2" s="42" t="str">
+        <f>'（別添2）_実績報告書・中間報告書 (調剤法人) '!$AB$68</f>
+        <v/>
       </c>
       <c r="DQ2" s="42" t="str">
         <f>'（別添2）_実績報告書・中間報告書 (調剤法人) '!$AB$70</f>
@@ -21001,6 +21017,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7416dcb5-151a-428d-b9dd-c50cd68ce8a8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -21009,31 +21033,30 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100DEA2635F732F464D88FD0617849E9F69" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="07a4d2faf2f8f28b7a2f551c9ec83f9e">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="33f003c0-0d95-44a8-96ef-b6b435aaba2f" xmlns:ns3="263dbbe5-076b-4606-a03b-9598f5f2f35a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8a3684643123949165adbe6bede2192a" ns2:_="" ns3:_="">
-    <xsd:import namespace="33f003c0-0d95-44a8-96ef-b6b435aaba2f"/>
-    <xsd:import namespace="263dbbe5-076b-4606-a03b-9598f5f2f35a"/>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100A14803322066C74F9BE02317CD0CDCCD" ma:contentTypeVersion="125" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="c4d0cbc5c65bf0286e4b5d882495989e">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7416dcb5-151a-428d-b9dd-c50cd68ce8a8" xmlns:ns3="cc65c493-46e3-4a51-bdc3-517cdfaa7574" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="10bb90dc8f083b7d0038c94280cbf4fb" ns2:_="" ns3:_="">
+    <xsd:import namespace="7416dcb5-151a-428d-b9dd-c50cd68ce8a8"/>
+    <xsd:import namespace="cc65c493-46e3-4a51-bdc3-517cdfaa7574"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:Owner" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -21041,13 +21064,74 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="33f003c0-0d95-44a8-96ef-b6b435aaba2f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7416dcb5-151a-428d-b9dd-c50cd68ce8a8" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="Owner" ma:index="8" nillable="true" ma:displayName="所有者" ma:internalName="Owner">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="16" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="17" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="19" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:displayName="画像タグ_0" ma:hidden="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cc65c493-46e3-4a51-bdc3-517cdfaa7574" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="共有相手" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
-          <xsd:extension base="dms:User">
+          <xsd:extension base="dms:UserMulti">
             <xsd:sequence>
               <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
                 <xsd:complexType>
@@ -21063,84 +21147,12 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="12" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="15" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="画像タグ" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="0347f584-7be2-4218-8e94-402d99aedf0b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="19" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="20" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="共有相手の詳細情報" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="22" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="263dbbe5-076b-4606-a03b-9598f5f2f35a" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="18" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{6c0e5604-1e4d-437b-a747-9a4cb561c167}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="263dbbe5-076b-4606-a03b-9598f5f2f35a">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -21242,25 +21254,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="33f003c0-0d95-44a8-96ef-b6b435aaba2f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="263dbbe5-076b-4606-a03b-9598f5f2f35a" xsi:nil="true"/>
-    <Owner xmlns="33f003c0-0d95-44a8-96ef-b6b435aaba2f">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01CFBDB1-AF44-4309-8492-4D7EC15D1448}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="33f003c0-0d95-44a8-96ef-b6b435aaba2f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="263dbbe5-076b-4606-a03b-9598f5f2f35a"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{547EF172-0E57-4331-B246-3594E5181FA8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -21268,38 +21279,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DB6526E-646D-4E72-A01C-CBFB30E6A6A0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="33f003c0-0d95-44a8-96ef-b6b435aaba2f"/>
-    <ds:schemaRef ds:uri="263dbbe5-076b-4606-a03b-9598f5f2f35a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01CFBDB1-AF44-4309-8492-4D7EC15D1448}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="263dbbe5-076b-4606-a03b-9598f5f2f35a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="33f003c0-0d95-44a8-96ef-b6b435aaba2f"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{385628F1-2AE1-4940-B458-39B89EFE232E}"/>
 </file>